--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit e22e24d. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 49dabb0. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -14692,7 +14692,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Boot estimate 4.03M; REG + tipis = 66%.</t>
+          <t>Boot estimate 3.95M (fish corrected, ATT-25); REG + tipis = 68%.</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit e22e24d.</t>
+          <t>Built at commit 49dabb0.</t>
         </is>
       </c>
     </row>
@@ -17070,7 +17070,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>e22e24d</t>
+          <t>49dabb0</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -17697,7 +17697,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit e22e24d</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 49dabb0</t>
         </is>
       </c>
     </row>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>18 trout at 23,466 tris each as separate meshes; small fish instanced (32).</t>
+          <t>18 trout + 4 baby koi at 15,644 tris each as separate meshes (ATT-25); small fish instanced (32).</t>
         </is>
       </c>
       <c r="E11" s="5">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -37,15 +37,15 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'41_Globals'!$A$4:$G$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'42_Events'!$A$4:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'43_Services'!$A$4:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'44_Limbo_Calls'!$A$4:$G$205</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'50_Findings'!$A$4:$L$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'44_Limbo_Calls'!$A$4:$G$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'50_Findings'!$A$4:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'51_Assets'!$A$4:$W$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'52_Claims_vs_Verified'!$A$4:$F$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'52_Claims_vs_Verified'!$A$4:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 49dabb0. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 2854704. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2783,30 +2783,30 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>DOM id lookup</t>
+          <t>DOM CustomEvent</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>__boot_err</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>index.html:L36</t>
-        </is>
-      </c>
+          <t>anu:season-change</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>index.html:L38; index.html:L38</t>
+          <t>js/sanctuary/SanctuaryBraziers.js:L311</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Has receiver</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
+          <t>DEAF — listener never fired by live code</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Check for a renamed event or an ANU bus event with a similar name</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2816,30 +2816,30 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DOM id lookup</t>
+          <t>DOM CustomEvent</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>__boot_err_text</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>index.html:L62</t>
-        </is>
-      </c>
+          <t>sanctuary:buildings:changed</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>index.html:L55; index.html:L55</t>
+          <t>js/v2/BuildingPanelUI.js:L134</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Has receiver</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
+          <t>DEAF — listener never fired by live code</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Check for a renamed event or an ANU bus event with a similar name</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2849,30 +2849,30 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>DOM id lookup</t>
+          <t>DOM CustomEvent</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>action-log</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>SacredGame.Panel.html:L2796</t>
-        </is>
-      </c>
+          <t>v2-pip-zoom-change</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1796</t>
+          <t>js/v2/Orchestrator.js:L356</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Has receiver</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
+          <t>DEAF — listener never fired by live code</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Check for a renamed event or an ANU bus event with a similar name</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2887,17 +2887,17 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>action-zone</t>
+          <t>__boot_err</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2579; SacredGame.Panel.html:L2594; SacredGame.Panel.html:L2604; SacredGame.Panel.html:L2648; SacredGame.Panel.html:L2707</t>
+          <t>index.html:L36</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1664</t>
+          <t>index.html:L38; index.html:L38</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>adventure-row-top</t>
+          <t>__boot_err_text</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2116</t>
+          <t>index.html:L62</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1749</t>
+          <t>index.html:L55; index.html:L55</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>aria-announcer</t>
+          <t>action-log</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2290</t>
+          <t>SacredGame.Panel.html:L2796</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1621</t>
+          <t>SacredGame.Panel.html:L1796</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>aria-live-narrator</t>
+          <t>action-zone</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2817</t>
+          <t>SacredGame.Panel.html:L2579; SacredGame.Panel.html:L2594; SacredGame.Panel.html:L2604; SacredGame.Panel.html:L2648; SacredGame.Panel.html:L2707</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1800</t>
+          <t>SacredGame.Panel.html:L1664</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3019,17 +3019,17 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>avatar-static-fallback</t>
+          <t>adventure-row-top</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1921</t>
+          <t>SacredGame.Panel.html:L2116</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1674</t>
+          <t>SacredGame.Panel.html:L1749</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>bar-logic</t>
+          <t>aria-announcer</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L532; js/components/Component.LoadingModal.html:L560; js/components/Component.LoadingModal.html:L594</t>
+          <t>SacredGame.Panel.html:L2290</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L250</t>
+          <t>SacredGame.Panel.html:L1621</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>book-drag-handle</t>
+          <t>aria-live-narrator</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L275</t>
+          <t>SacredGame.Panel.html:L2817</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L203</t>
+          <t>SacredGame.Panel.html:L1800</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -3118,17 +3118,17 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>book-resize-handle</t>
+          <t>avatar-static-fallback</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L276</t>
+          <t>SacredGame.Panel.html:L1921</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L204</t>
+          <t>SacredGame.Panel.html:L1674</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>book-wrapper</t>
+          <t>bar-logic</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2315; SacredGame.Journal.html:L274; SacredGame.Journal.html:L340; SacredGame.Journal.html:L382; SacredGame.Journal.html:L391; SacredGame.Journal.html:L431; SacredGame.Journal.html:L447; SacredGame.Journal.html:L456; SacredGame.Journal.html:L465; SacredGame.Journal.html:L475; SacredGame.Journal.html:L485; SacredGame.Journal.html:L516; SacredGame.Journal.html:L559; SacredGame.Journal.html:L586; SacredGame.Journal.html:L612</t>
+          <t>js/components/Component.LoadingModal.html:L532; js/components/Component.LoadingModal.html:L560; js/components/Component.LoadingModal.html:L594</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L202</t>
+          <t>js/components/Component.LoadingModal.html:L250</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>btn-items</t>
+          <t>book-drag-handle</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2516</t>
+          <t>SacredGame.Journal.html:L275</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1680</t>
+          <t>SacredGame.Journal.html:L203</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -3217,17 +3217,17 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>btn-journal</t>
+          <t>book-resize-handle</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2099; SacredGame.Panel.html:L2110</t>
+          <t>SacredGame.Journal.html:L276</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1685</t>
+          <t>SacredGame.Journal.html:L204</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -3250,17 +3250,17 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>build-badge</t>
+          <t>book-wrapper</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>js/BuildBadge.js:L59</t>
+          <t>SacredGame.Panel.html:L2315; SacredGame.Journal.html:L274; SacredGame.Journal.html:L340; SacredGame.Journal.html:L382; SacredGame.Journal.html:L391; SacredGame.Journal.html:L431; SacredGame.Journal.html:L447; SacredGame.Journal.html:L456; SacredGame.Journal.html:L465; SacredGame.Journal.html:L475; SacredGame.Journal.html:L485; SacredGame.Journal.html:L516; SacredGame.Journal.html:L559; SacredGame.Journal.html:L586; SacredGame.Journal.html:L612</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>js/BuildBadge.js:L62; js/BuildBadge.js:L62</t>
+          <t>SacredGame.Journal.html:L202</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -3283,17 +3283,17 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>build-badge-copy</t>
+          <t>btn-items</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>js/BuildBadge.js:L136</t>
+          <t>SacredGame.Panel.html:L2516</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>js/BuildBadge.js:L134</t>
+          <t>SacredGame.Panel.html:L1680</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -3316,17 +3316,17 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>card-fish-btn</t>
+          <t>btn-journal</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2554</t>
+          <t>SacredGame.Panel.html:L2099; SacredGame.Panel.html:L2110</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1771</t>
+          <t>SacredGame.Panel.html:L1685</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -3349,17 +3349,17 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>card-gather-btn</t>
+          <t>build-badge</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2548</t>
+          <t>js/BuildBadge.js:L59</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1765</t>
+          <t>js/BuildBadge.js:L62; js/BuildBadge.js:L62</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -3382,17 +3382,17 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>card-log-btn</t>
+          <t>build-badge-copy</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2098; SacredGame.Panel.html:L2109</t>
+          <t>js/BuildBadge.js:L136</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1783</t>
+          <t>js/BuildBadge.js:L134</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -3415,17 +3415,17 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>card-quest-btn</t>
+          <t>card-fish-btn</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2124; SacredGame.Panel.html:L2198; SacredGame.Panel.html:L2252; SacredGame.Panel.html:L2483; SacredGame.Panel.html:L2505; SacredGame.Panel.html:L2512; SacredGame.Panel.html:L2539</t>
+          <t>SacredGame.Panel.html:L2554</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1756</t>
+          <t>SacredGame.Panel.html:L1771</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>card-search-btn</t>
+          <t>card-gather-btn</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2205; SacredGame.Panel.html:L2560</t>
+          <t>SacredGame.Panel.html:L2548</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1777</t>
+          <t>SacredGame.Panel.html:L1765</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>center-stack</t>
+          <t>card-log-btn</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2313</t>
+          <t>SacredGame.Panel.html:L2098; SacredGame.Panel.html:L2109</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1747</t>
+          <t>SacredGame.Panel.html:L1783</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>desc-quest</t>
+          <t>card-quest-btn</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2484; SacredGame.Panel.html:L2506</t>
+          <t>SacredGame.Panel.html:L2124; SacredGame.Panel.html:L2198; SacredGame.Panel.html:L2252; SacredGame.Panel.html:L2483; SacredGame.Panel.html:L2505; SacredGame.Panel.html:L2512; SacredGame.Panel.html:L2539</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1761</t>
+          <t>SacredGame.Panel.html:L1756</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>dynamic-font-override</t>
+          <t>card-search-btn</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L686</t>
+          <t>SacredGame.Panel.html:L2205; SacredGame.Panel.html:L2560</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L689; js/components/Component.NewJournal.html:L689</t>
+          <t>SacredGame.Panel.html:L1777</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -3580,17 +3580,17 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>event-log</t>
+          <t>center-stack</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2282; SacredGame.Panel.html:L2433</t>
+          <t>SacredGame.Panel.html:L2313</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1879</t>
+          <t>SacredGame.Panel.html:L1747</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -3613,17 +3613,17 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>font-size-display</t>
+          <t>desc-quest</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L676</t>
+          <t>SacredGame.Panel.html:L2484; SacredGame.Panel.html:L2506</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L573</t>
+          <t>SacredGame.Panel.html:L1761</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>guides-container</t>
+          <t>dynamic-font-override</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1945; SacredGame.Panel.html:L2096; SacredGame.Panel.html:L2107</t>
+          <t>js/components/Component.NewJournal.html:L686</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1754</t>
+          <t>js/components/Component.NewJournal.html:L689; js/components/Component.NewJournal.html:L689</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -3679,17 +3679,17 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>icon-logbook-axe</t>
+          <t>event-log</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L514; SacredGame.Journal.html:L551</t>
+          <t>SacredGame.Panel.html:L2282; SacredGame.Panel.html:L2433</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L210</t>
+          <t>SacredGame.Panel.html:L1879</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -3712,17 +3712,17 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>left-panel</t>
+          <t>font-size-display</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1985; SacredGame.Panel.html:L2004; SacredGame.Panel.html:L2114; SacredGame.Panel.html:L2314</t>
+          <t>js/components/Component.NewJournal.html:L676</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1642</t>
+          <t>js/components/Component.NewJournal.html:L573</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -3745,17 +3745,17 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>llm-input</t>
+          <t>guides-container</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2668; SacredGame.Panel.html:L2748; SacredGame.Panel.html:L2816; js/components/Component.NewJournal.html:L915</t>
+          <t>SacredGame.Panel.html:L1945; SacredGame.Panel.html:L2096; SacredGame.Panel.html:L2107</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L592</t>
+          <t>SacredGame.Panel.html:L1754</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -3778,17 +3778,17 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>loading</t>
+          <t>icon-logbook-axe</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L267; js/components/Component.LoadingModal.html:L640</t>
+          <t>SacredGame.Journal.html:L514; SacredGame.Journal.html:L551</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L221</t>
+          <t>SacredGame.Journal.html:L210</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>loading-log</t>
+          <t>left-panel</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L510</t>
+          <t>SacredGame.Panel.html:L1985; SacredGame.Panel.html:L2004; SacredGame.Panel.html:L2114; SacredGame.Panel.html:L2314</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L258</t>
+          <t>SacredGame.Panel.html:L1642</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>loading-video</t>
+          <t>llm-input</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L268</t>
+          <t>SacredGame.Panel.html:L2668; SacredGame.Panel.html:L2748; SacredGame.Panel.html:L2816; js/components/Component.NewJournal.html:L915</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L222</t>
+          <t>js/components/Component.NewJournal.html:L592</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>logbookFrame</t>
+          <t>loading</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L242; SacredGame.Journal.html:L260; SacredGame.Journal.html:L341; SacredGame.Journal.html:L381; SacredGame.Journal.html:L435; SacredGame.Journal.html:L468; SacredGame.Journal.html:L478; SacredGame.Journal.html:L488; SacredGame.Journal.html:L497; SacredGame.Journal.html:L507; SacredGame.Journal.html:L515; SacredGame.Journal.html:L565</t>
+          <t>js/components/Component.LoadingModal.html:L267; js/components/Component.LoadingModal.html:L640</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L205</t>
+          <t>js/components/Component.LoadingModal.html:L221</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>mobile-thumb-zone</t>
+          <t>loading-log</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1805</t>
+          <t>js/components/Component.LoadingModal.html:L510</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1644</t>
+          <t>js/components/Component.LoadingModal.html:L258</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -3943,17 +3943,17 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>p-logic</t>
+          <t>loading-video</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L538; js/components/Component.LoadingModal.html:L586</t>
+          <t>js/components/Component.LoadingModal.html:L268</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L247</t>
+          <t>js/components/Component.LoadingModal.html:L222</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -3976,17 +3976,17 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>p-logic-slot</t>
+          <t>logbookFrame</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L541; js/components/Component.LoadingModal.html:L583; js/components/Component.LoadingModal.html:L621</t>
+          <t>SacredGame.Journal.html:L242; SacredGame.Journal.html:L260; SacredGame.Journal.html:L341; SacredGame.Journal.html:L381; SacredGame.Journal.html:L435; SacredGame.Journal.html:L468; SacredGame.Journal.html:L478; SacredGame.Journal.html:L488; SacredGame.Journal.html:L497; SacredGame.Journal.html:L507; SacredGame.Journal.html:L515; SacredGame.Journal.html:L565</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L248</t>
+          <t>SacredGame.Journal.html:L205</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>page-content-left</t>
+          <t>mobile-thumb-zone</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L740</t>
+          <t>SacredGame.Panel.html:L1805</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L544</t>
+          <t>SacredGame.Panel.html:L1644</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -4042,17 +4042,17 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>page-content-right</t>
+          <t>p-logic</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L741</t>
+          <t>js/components/Component.LoadingModal.html:L538; js/components/Component.LoadingModal.html:L586</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L555</t>
+          <t>js/components/Component.LoadingModal.html:L247</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -4075,17 +4075,17 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>page-num-left</t>
+          <t>p-logic-slot</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L742</t>
+          <t>js/components/Component.LoadingModal.html:L541; js/components/Component.LoadingModal.html:L583; js/components/Component.LoadingModal.html:L621</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L546</t>
+          <t>js/components/Component.LoadingModal.html:L248</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -4108,17 +4108,17 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>page-num-right</t>
+          <t>page-content-left</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L743</t>
+          <t>js/components/Component.NewJournal.html:L740</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L562</t>
+          <t>js/components/Component.NewJournal.html:L544</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -4141,17 +4141,17 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>panel-frame</t>
+          <t>page-content-right</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L329; js/v2/UIModule.js:L223</t>
+          <t>js/components/Component.NewJournal.html:L741</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L209</t>
+          <t>js/components/Component.NewJournal.html:L555</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -4174,17 +4174,17 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>parser-feedback</t>
+          <t>page-num-left</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L916; js/components/Component.NewJournal.html:L1304; js/components/Component.NewJournal.html:L1330</t>
+          <t>js/components/Component.NewJournal.html:L742</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L596</t>
+          <t>js/components/Component.NewJournal.html:L546</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -4207,17 +4207,17 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>pip-click-zone</t>
+          <t>page-num-right</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L235</t>
+          <t>js/components/Component.NewJournal.html:L743</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L219</t>
+          <t>js/components/Component.NewJournal.html:L562</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -4240,17 +4240,17 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>res-indicator</t>
+          <t>panel-frame</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1207</t>
+          <t>SacredGame.Journal.html:L329; js/v2/UIModule.js:L223</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L600</t>
+          <t>js/v2/UIModule.js:L209</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -4273,17 +4273,17 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>right-panel</t>
+          <t>parser-feedback</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2115; SacredGame.Panel.html:L2608</t>
+          <t>js/components/Component.NewJournal.html:L916; js/components/Component.NewJournal.html:L1304; js/components/Component.NewJournal.html:L1330</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1663</t>
+          <t>js/components/Component.NewJournal.html:L596</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>sacred-logbook-engine</t>
+          <t>pip-click-zone</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L628; js/components/Component.NewJournal.html:L641</t>
+          <t>js/v2/UIModule.js:L235</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L508</t>
+          <t>js/v2/UIModule.js:L219</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -4339,17 +4339,17 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>sanctuary-welcome-guide-css</t>
+          <t>res-indicator</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryWelcomeGuide.js:L59</t>
+          <t>js/components/Component.NewJournal.html:L1207</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryWelcomeGuide.js:L61; js/sanctuary/SanctuaryWelcomeGuide.js:L61</t>
+          <t>js/components/Component.NewJournal.html:L600</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -4372,17 +4372,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>setup-modal</t>
+          <t>right-panel</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1601; SacredGame.Panel.html:L1615; SacredGame.Panel.html:L1617</t>
+          <t>SacredGame.Panel.html:L2115; SacredGame.Panel.html:L2608</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1606</t>
+          <t>SacredGame.Panel.html:L1663</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>sr-announcer</t>
+          <t>sacred-logbook-engine</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L631; js/components/Component.NewJournal.html:L644; js/components/Component.NewJournal.html:L678; js/components/Component.NewJournal.html:L747; js/components/Component.NewJournal.html:L983; js/components/Component.NewJournal.html:L1315</t>
+          <t>js/components/Component.NewJournal.html:L628; js/components/Component.NewJournal.html:L641</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L506</t>
+          <t>js/components/Component.NewJournal.html:L508</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>tab-log</t>
+          <t>sanctuary-welcome-guide-css</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L633</t>
+          <t>js/sanctuary/SanctuaryWelcomeGuide.js:L59</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L519</t>
+          <t>js/sanctuary/SanctuaryWelcomeGuide.js:L61; js/sanctuary/SanctuaryWelcomeGuide.js:L61</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>ui-layer</t>
+          <t>setup-modal</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2677</t>
+          <t>SacredGame.Panel.html:L1601; SacredGame.Panel.html:L1615; SacredGame.Panel.html:L1617</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1599</t>
+          <t>SacredGame.Panel.html:L1606</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>v2-anu-alert</t>
+          <t>sr-announcer</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L672</t>
+          <t>js/components/Component.NewJournal.html:L631; js/components/Component.NewJournal.html:L644; js/components/Component.NewJournal.html:L678; js/components/Component.NewJournal.html:L747; js/components/Component.NewJournal.html:L983; js/components/Component.NewJournal.html:L1315</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L40</t>
+          <t>js/components/Component.NewJournal.html:L506</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>v2-bench</t>
+          <t>tab-log</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L613</t>
+          <t>js/components/Component.NewJournal.html:L633</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L80</t>
+          <t>js/components/Component.NewJournal.html:L519</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -4570,17 +4570,17 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>v2-distance-pill</t>
+          <t>ui-layer</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L253</t>
+          <t>SacredGame.Panel.html:L2677</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L210</t>
+          <t>SacredGame.Panel.html:L1599</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -4603,17 +4603,17 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>v2-draws</t>
+          <t>v2-anu-alert</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L612</t>
+          <t>js/v2/OrchestratorHud.js:L672</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L41</t>
+          <t>js/v2/OrchestratorHud.js:L40</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>v2-font</t>
+          <t>v2-bench</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L96</t>
+          <t>js/v2/OrchestratorHud.js:L613</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L98; js/v2/OrchestratorHud.js:L98</t>
+          <t>js/v2/OrchestratorHud.js:L80</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -4669,17 +4669,17 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>v2-fps</t>
+          <t>v2-distance-pill</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L611</t>
+          <t>js/v2/UIModule.js:L253</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L34</t>
+          <t>js/v2/UIModule.js:L210</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -4702,17 +4702,17 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>v2-frame-graph</t>
+          <t>v2-draws</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L652</t>
+          <t>js/v2/OrchestratorHud.js:L612</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L36</t>
+          <t>js/v2/OrchestratorHud.js:L41</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>v2-hud-trace-label</t>
+          <t>v2-font</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L461</t>
+          <t>js/v2/OrchestratorHud.js:L96</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L47</t>
+          <t>js/v2/OrchestratorHud.js:L98; js/v2/OrchestratorHud.js:L98</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -4768,17 +4768,17 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>v2-hud-universe-label</t>
+          <t>v2-fps</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L205</t>
+          <t>js/v2/OrchestratorHud.js:L611</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L74</t>
+          <t>js/v2/OrchestratorHud.js:L34</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>v2-load</t>
+          <t>v2-frame-graph</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L650</t>
+          <t>js/v2/OrchestratorHud.js:L652</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L37</t>
+          <t>js/v2/OrchestratorHud.js:L36</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -4834,17 +4834,17 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>v2-load-detail</t>
+          <t>v2-hud-trace-label</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L651</t>
+          <t>js/v2/OrchestratorHud.js:L461</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L38</t>
+          <t>js/v2/OrchestratorHud.js:L47</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>v2-map-picker</t>
+          <t>v2-hud-universe-label</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L540</t>
+          <t>js/v2/OrchestratorHud.js:L205</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L85</t>
+          <t>js/v2/OrchestratorHud.js:L74</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -4900,17 +4900,17 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>v2-modules</t>
+          <t>v2-load</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L589</t>
+          <t>js/v2/OrchestratorHud.js:L650</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L79</t>
+          <t>js/v2/OrchestratorHud.js:L37</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -4933,17 +4933,17 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>v2-orchestrator-hud</t>
+          <t>v2-load-detail</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L478; js/v2/OrchestratorHud.js:L879; js/v2/OrchestratorHud.js:L938; index.html:L437; index.html:L868</t>
+          <t>js/v2/OrchestratorHud.js:L651</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L152; js/v2/OrchestratorHud.js:L152</t>
+          <t>js/v2/OrchestratorHud.js:L38</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -4966,17 +4966,17 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>v2-orchestrator-hud-mobile-css</t>
+          <t>v2-map-picker</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L108</t>
+          <t>js/v2/OrchestratorHud.js:L540</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L110; js/v2/OrchestratorHud.js:L110</t>
+          <t>js/v2/OrchestratorHud.js:L85</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -4999,17 +4999,17 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>v2-panels-pip</t>
+          <t>v2-modules</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L887; js/v2/OrchestratorHud.js:L939</t>
+          <t>js/v2/OrchestratorHud.js:L589</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L42; js/v2/UIModule.js:L42</t>
+          <t>js/v2/OrchestratorHud.js:L79</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -5032,17 +5032,17 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>v2-pip</t>
+          <t>v2-orchestrator-hud</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L637</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L478; js/v2/OrchestratorHud.js:L879; js/v2/OrchestratorHud.js:L938; index.html:L437; index.html:L868</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L42</t>
+          <t>js/v2/OrchestratorHud.js:L152; js/v2/OrchestratorHud.js:L152</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -5065,17 +5065,17 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>v2-pip-canvas</t>
+          <t>v2-orchestrator-hud-mobile-css</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1417; js/v2/UIModule.js:L226</t>
+          <t>js/v2/OrchestratorHud.js:L108</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L218</t>
+          <t>js/v2/OrchestratorHud.js:L110; js/v2/OrchestratorHud.js:L110</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -5098,17 +5098,17 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>v2-trace-accordion-body</t>
+          <t>v2-panels-pip</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L462</t>
+          <t>js/v2/OrchestratorHud.js:L887; js/v2/OrchestratorHud.js:L939</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L61</t>
+          <t>js/v2/UIModule.js:L42; js/v2/UIModule.js:L42</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>v2-trace-copy-pill</t>
+          <t>v2-pip</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L465</t>
+          <t>js/v2/OrchestratorHud.js:L637</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L56</t>
+          <t>js/v2/OrchestratorHud.js:L42</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -5164,17 +5164,17 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>v2-trace-dur</t>
+          <t>v2-pip-canvas</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L464</t>
+          <t>js/v2/Orchestrator.js:L1417; js/v2/UIModule.js:L226</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L54</t>
+          <t>js/v2/UIModule.js:L218</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -5197,17 +5197,17 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>v2-trace-spark</t>
+          <t>v2-trace-accordion-body</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L480</t>
+          <t>js/v2/OrchestratorHud.js:L462</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L62</t>
+          <t>js/v2/OrchestratorHud.js:L61</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>v2-trace-stats</t>
+          <t>v2-trace-copy-pill</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L474; js/v2/OrchestratorHud.js:L482</t>
+          <t>js/v2/OrchestratorHud.js:L465</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L66</t>
+          <t>js/v2/OrchestratorHud.js:L56</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -5263,17 +5263,17 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>v2-trace-toggle-icon</t>
+          <t>v2-trace-dur</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L463</t>
+          <t>js/v2/OrchestratorHud.js:L464</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L52</t>
+          <t>js/v2/OrchestratorHud.js:L54</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -5296,17 +5296,17 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>v2-universe-accordion-body</t>
+          <t>v2-trace-spark</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L206</t>
+          <t>js/v2/OrchestratorHud.js:L480</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L78</t>
+          <t>js/v2/OrchestratorHud.js:L62</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -5329,17 +5329,17 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>v2-universe-count</t>
+          <t>v2-trace-stats</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L590</t>
+          <t>js/v2/OrchestratorHud.js:L474; js/v2/OrchestratorHud.js:L482</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L76</t>
+          <t>js/v2/OrchestratorHud.js:L66</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>v2-universe-pct</t>
+          <t>v2-trace-toggle-icon</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L706</t>
+          <t>js/v2/OrchestratorHud.js:L463</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L75</t>
+          <t>js/v2/OrchestratorHud.js:L52</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>v2-universe-toggle-icon</t>
+          <t>v2-universe-accordion-body</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L207</t>
+          <t>js/v2/OrchestratorHud.js:L206</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L75</t>
+          <t>js/v2/OrchestratorHud.js:L78</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>v4-ambient-style</t>
+          <t>v2-universe-count</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryAmbient.js:L240</t>
+          <t>js/v2/OrchestratorHud.js:L590</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryAmbient.js:L170; js/sanctuary/SanctuaryAmbient.js:L170</t>
+          <t>js/v2/OrchestratorHud.js:L76</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>v4-banner</t>
+          <t>v2-universe-pct</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>index.html:L766</t>
+          <t>js/v2/OrchestratorHud.js:L706</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>index.html:L325</t>
+          <t>js/v2/OrchestratorHud.js:L75</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -5494,17 +5494,17 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>v4-btn-clear-scene</t>
+          <t>v2-universe-toggle-icon</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L460</t>
+          <t>js/v2/OrchestratorHud.js:L207</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L370; js/sanctuary/SanctuaryToolPalette.js:L370</t>
+          <t>js/v2/OrchestratorHud.js:L75</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -5527,17 +5527,17 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>v4-btn-gen-scene</t>
+          <t>v4-ambient-style</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L453</t>
+          <t>js/sanctuary/SanctuaryAmbient.js:L240</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L365; js/sanctuary/SanctuaryToolPalette.js:L365</t>
+          <t>js/sanctuary/SanctuaryAmbient.js:L170; js/sanctuary/SanctuaryAmbient.js:L170</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>v4-btn-journal</t>
+          <t>v4-banner</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L245</t>
+          <t>index.html:L766</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L171</t>
+          <t>index.html:L325</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -5593,17 +5593,17 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>v4-btn-panel</t>
+          <t>v4-btn-clear-scene</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L240</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L460</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L170</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L370; js/sanctuary/SanctuaryToolPalette.js:L370</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -5626,17 +5626,17 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>v4-btn-reset</t>
+          <t>v4-btn-gen-scene</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L254</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L453</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L174</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L365; js/sanctuary/SanctuaryToolPalette.js:L365</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -5659,17 +5659,17 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>v4-btn-save</t>
+          <t>v4-btn-journal</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L270</t>
+          <t>js/sanctuary/SanctuaryControls.js:L245</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L175</t>
+          <t>js/sanctuary/SanctuaryControls.js:L171</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
@@ -5692,17 +5692,17 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>v4-btn-top</t>
+          <t>v4-btn-panel</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L233</t>
+          <t>js/sanctuary/SanctuaryControls.js:L240</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L169</t>
+          <t>js/sanctuary/SanctuaryControls.js:L170</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>v4-canvas</t>
+          <t>v4-btn-reset</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>index.html:L430; index.html:L891</t>
+          <t>js/sanctuary/SanctuaryControls.js:L254</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>index.html:L291</t>
+          <t>js/sanctuary/SanctuaryControls.js:L174</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
@@ -5758,17 +5758,17 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>v4-confirm-cancel</t>
+          <t>v4-btn-save</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L257</t>
+          <t>js/sanctuary/SanctuaryControls.js:L270</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L187</t>
+          <t>js/sanctuary/SanctuaryControls.js:L175</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>v4-confirm-yes</t>
+          <t>v4-btn-top</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L260</t>
+          <t>js/sanctuary/SanctuaryControls.js:L233</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L188</t>
+          <t>js/sanctuary/SanctuaryControls.js:L169</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -5824,17 +5824,17 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>v4-controls</t>
+          <t>v4-canvas</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryAmbient.js:L189; js/sanctuary/SanctuaryDayNight.js:L89; js/sanctuary/SanctuaryWeather.js:L111</t>
+          <t>index.html:L430; index.html:L891</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L158; js/sanctuary/SanctuaryControls.js:L158</t>
+          <t>index.html:L291</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -5857,17 +5857,17 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>v4-controls-style</t>
+          <t>v4-confirm-cancel</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L149; js/sanctuary/SanctuaryControls.js:L364</t>
+          <t>js/sanctuary/SanctuaryControls.js:L257</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L151; js/sanctuary/SanctuaryControls.js:L151</t>
+          <t>js/sanctuary/SanctuaryControls.js:L187</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
@@ -5890,17 +5890,17 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>v4-fishing-pip-glass-style</t>
+          <t>v4-confirm-yes</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFishing.js:L1012</t>
+          <t>js/sanctuary/SanctuaryControls.js:L260</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFishing.js:L1014; js/sanctuary/SanctuaryFishing.js:L1014</t>
+          <t>js/sanctuary/SanctuaryControls.js:L188</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -5923,17 +5923,17 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>v4-inventory-style</t>
+          <t>v4-controls</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryInventory.js:L96; js/sanctuary/SanctuaryInventory.js:L224</t>
+          <t>js/sanctuary/SanctuaryAmbient.js:L189; js/sanctuary/SanctuaryDayNight.js:L89; js/sanctuary/SanctuaryWeather.js:L111</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryInventory.js:L98; js/sanctuary/SanctuaryInventory.js:L98</t>
+          <t>js/sanctuary/SanctuaryControls.js:L158; js/sanctuary/SanctuaryControls.js:L158</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
@@ -5956,17 +5956,17 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>v4-journal-frame</t>
+          <t>v4-controls-style</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>index.html:L676</t>
+          <t>js/sanctuary/SanctuaryControls.js:L149; js/sanctuary/SanctuaryControls.js:L364</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>index.html:L304</t>
+          <t>js/sanctuary/SanctuaryControls.js:L151; js/sanctuary/SanctuaryControls.js:L151</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -5989,17 +5989,17 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>v4-journal-overlay</t>
+          <t>v4-fishing-pip-glass-style</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryKeyboardLook.js:L276; index.html:L675; index.html:L699</t>
+          <t>js/sanctuary/SanctuaryFishing.js:L1012</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>index.html:L296</t>
+          <t>js/sanctuary/SanctuaryFishing.js:L1014; js/sanctuary/SanctuaryFishing.js:L1014</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -6022,17 +6022,17 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>v4-journal-overlay-close</t>
+          <t>v4-inventory-style</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>index.html:L697</t>
+          <t>js/sanctuary/SanctuaryInventory.js:L96; js/sanctuary/SanctuaryInventory.js:L224</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>index.html:L299</t>
+          <t>js/sanctuary/SanctuaryInventory.js:L98; js/sanctuary/SanctuaryInventory.js:L98</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -6055,17 +6055,17 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>v4-loading-iframe</t>
+          <t>v4-journal-frame</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>index.html:L67; index.html:L383; index.html:L410</t>
+          <t>index.html:L676</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>index.html:L285</t>
+          <t>index.html:L304</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
@@ -6088,17 +6088,17 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>v4-map-type-select</t>
+          <t>v4-journal-overlay</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L411</t>
+          <t>js/sanctuary/SanctuaryKeyboardLook.js:L276; index.html:L675; index.html:L699</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L308; js/sanctuary/SanctuaryToolPalette.js:L308</t>
+          <t>index.html:L296</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -6121,17 +6121,17 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>v4-panel-frame</t>
+          <t>v4-journal-overlay-close</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>index.html:L725</t>
+          <t>index.html:L697</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>index.html:L320</t>
+          <t>index.html:L299</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -6154,17 +6154,17 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>v4-tool-cursor-style</t>
+          <t>v4-loading-iframe</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryCursor.js:L66; js/sanctuary/SanctuaryCursor.js:L120</t>
+          <t>index.html:L67; index.html:L383; index.html:L410</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryCursor.js:L68; js/sanctuary/SanctuaryCursor.js:L68</t>
+          <t>index.html:L285</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -6187,17 +6187,17 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>v4-village-build-style</t>
+          <t>v4-map-type-select</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L274; js/sanctuary/SanctuaryToolPalette.js:L516</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L411</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L276; js/sanctuary/SanctuaryToolPalette.js:L276</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L308; js/sanctuary/SanctuaryToolPalette.js:L308</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -6220,17 +6220,17 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>v4-walk-hide-style</t>
+          <t>v4-panel-frame</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryKeyboardLook.js:L93</t>
+          <t>index.html:L725</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryKeyboardLook.js:L95; js/sanctuary/SanctuaryKeyboardLook.js:L95</t>
+          <t>index.html:L320</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Runtime service lookup</t>
+          <t>DOM id lookup</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>PipOrthoBranchClip</t>
+          <t>v4-tool-cursor-style</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1630</t>
+          <t>js/sanctuary/SanctuaryCursor.js:L66; js/sanctuary/SanctuaryCursor.js:L120</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/PipOrthoRingDiskClip.js:L44</t>
+          <t>js/sanctuary/SanctuaryCursor.js:L68; js/sanctuary/SanctuaryCursor.js:L68</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Runtime service lookup</t>
+          <t>DOM id lookup</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>WebFontsService</t>
+          <t>v4-village-build-style</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L92</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L274; js/sanctuary/SanctuaryToolPalette.js:L516</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L38</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L276; js/sanctuary/SanctuaryToolPalette.js:L276</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -6314,22 +6314,22 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Runtime service lookup</t>
+          <t>DOM id lookup</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>WorldPlayer</t>
+          <t>v4-walk-hide-style</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1411; js/v2/UIModule.js:L231; js/v2/UIModule.js:L248</t>
+          <t>js/sanctuary/SanctuaryKeyboardLook.js:L93</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryWorldPlayerShim.js:L44</t>
+          <t>js/sanctuary/SanctuaryKeyboardLook.js:L95; js/sanctuary/SanctuaryKeyboardLook.js:L95</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -6347,22 +6347,22 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>postMessage type</t>
+          <t>Runtime service lookup</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>ADD_PAGE</t>
+          <t>PipOrthoBranchClip</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2367; SacredGame.Panel.html:L2414</t>
+          <t>js/v2/Orchestrator.js:L1630</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1298; SacredGame.Journal.html:L504 (relay list)</t>
+          <t>js/v2/anu/PipOrthoRingDiskClip.js:L44</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -6370,11 +6370,7 @@
           <t>Has receiver</t>
         </is>
       </c>
-      <c r="G156" s="5" t="inlineStr">
-        <is>
-          <t>Receiver may sit in another frame; both frames scanned</t>
-        </is>
-      </c>
+      <c r="G156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -6384,22 +6380,22 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>postMessage type</t>
+          <t>Runtime service lookup</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>BOOT_ERROR</t>
+          <t>WebFontsService</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>index.html:L68</t>
+          <t>js/v2/OrchestratorHud.js:L92</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L500</t>
+          <t>js/v2/UIModule.js:L38</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -6407,11 +6403,7 @@
           <t>Has receiver</t>
         </is>
       </c>
-      <c r="G157" s="5" t="inlineStr">
-        <is>
-          <t>Receiver may sit in another frame; both frames scanned</t>
-        </is>
-      </c>
+      <c r="G157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -6421,22 +6413,22 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>postMessage type</t>
+          <t>Runtime service lookup</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>CANVAS_CLICK</t>
+          <t>WorldPlayer</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2896</t>
+          <t>js/v2/Orchestrator.js:L1411; js/v2/UIModule.js:L231; js/v2/UIModule.js:L248</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>index.html:L885</t>
+          <t>js/sanctuary/SanctuaryWorldPlayerShim.js:L44</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -6444,11 +6436,7 @@
           <t>Has receiver</t>
         </is>
       </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>Receiver may sit in another frame; both frames scanned</t>
-        </is>
-      </c>
+      <c r="G158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -6463,17 +6451,17 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>CLOSE_LOGBOOK</t>
+          <t>ADD_PAGE</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2067; SacredGame.Journal.html:L376</t>
+          <t>SacredGame.Panel.html:L2367; SacredGame.Panel.html:L2414</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>index.html:L716; SacredGame.Panel.html:L2065; SacredGame.Journal.html:L455</t>
+          <t>js/components/Component.NewJournal.html:L1298; SacredGame.Journal.html:L504 (relay list)</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
@@ -6500,17 +6488,17 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>DO_OPEN_FLIP</t>
+          <t>BOOT_ERROR</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L350; SacredGame.Journal.html:L357</t>
+          <t>index.html:L68</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1238; SacredGame.Journal.html:L504 (relay list)</t>
+          <t>js/components/Component.LoadingModal.html:L500</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -6537,17 +6525,17 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>FISH_ACTION</t>
+          <t>CANVAS_CLICK</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2553</t>
+          <t>SacredGame.Panel.html:L2896</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>index.html:L785</t>
+          <t>index.html:L885</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -6574,17 +6562,17 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>FORCE_OPEN_JOURNAL</t>
+          <t>CLOSE_LOGBOOK</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>index.html:L689</t>
+          <t>SacredGame.Panel.html:L2067; SacredGame.Journal.html:L376</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L430; SacredGame.Panel.html:L2224 (relay list)</t>
+          <t>index.html:L716; SacredGame.Panel.html:L2065; SacredGame.Journal.html:L455</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
@@ -6611,17 +6599,17 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>GO_TO_PAGE</t>
+          <t>DO_OPEN_FLIP</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2340; SacredGame.Journal.html:L436; SacredGame.Journal.html:L469; SacredGame.Journal.html:L479; SacredGame.Journal.html:L498</t>
+          <t>SacredGame.Journal.html:L350; SacredGame.Journal.html:L357</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1243; SacredGame.Journal.html:L504 (relay list)</t>
+          <t>js/components/Component.NewJournal.html:L1238; SacredGame.Journal.html:L504 (relay list)</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
@@ -6648,17 +6636,17 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>JOURNAL_CLOSED</t>
+          <t>FISH_ACTION</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L374</t>
+          <t>SacredGame.Panel.html:L2553</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryJournalBridge.js:L106; js/sanctuary/SanctuaryJournalBridge.js:L109; SacredGame.Panel.html:L2104</t>
+          <t>index.html:L785</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -6685,17 +6673,17 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>JOURNAL_OPENED</t>
+          <t>FORCE_OPEN_JOURNAL</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L364</t>
+          <t>index.html:L689</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryJournalBridge.js:L106; js/sanctuary/SanctuaryJournalBridge.js:L107; SacredGame.Panel.html:L2094</t>
+          <t>SacredGame.Journal.html:L430; SacredGame.Panel.html:L2224 (relay list)</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
@@ -6722,17 +6710,17 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>KEY_FORWARD</t>
+          <t>GO_TO_PAGE</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2024; SacredGame.Panel.html:L2731; SacredGame.Panel.html:L2740; SacredGame.Journal.html:L616; SacredGame.Journal.html:L620</t>
+          <t>SacredGame.Panel.html:L2340; SacredGame.Journal.html:L436; SacredGame.Journal.html:L469; SacredGame.Journal.html:L479; SacredGame.Journal.html:L498</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2459</t>
+          <t>js/components/Component.NewJournal.html:L1243; SacredGame.Journal.html:L504 (relay list)</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
@@ -6759,17 +6747,17 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>LOGBOOK_ASPECT</t>
+          <t>JOURNAL_CLOSED</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L244; SacredGame.Journal.html:L262</t>
+          <t>SacredGame.Journal.html:L374</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L504 (relay list)</t>
+          <t>js/sanctuary/SanctuaryJournalBridge.js:L106; js/sanctuary/SanctuaryJournalBridge.js:L109; SacredGame.Panel.html:L2104</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
@@ -6796,17 +6784,17 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>LOGBOOK_VISIBILITY</t>
+          <t>JOURNAL_OPENED</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L365; SacredGame.Journal.html:L375</t>
+          <t>SacredGame.Journal.html:L364</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryJournalBridge.js:L106</t>
+          <t>js/sanctuary/SanctuaryJournalBridge.js:L106; js/sanctuary/SanctuaryJournalBridge.js:L107; SacredGame.Panel.html:L2094</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
@@ -6833,17 +6821,17 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>OPEN_LOGBOOK</t>
+          <t>KEY_FORWARD</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2102</t>
+          <t>SacredGame.Panel.html:L2024; SacredGame.Panel.html:L2731; SacredGame.Panel.html:L2740; SacredGame.Journal.html:L616; SacredGame.Journal.html:L620</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L430</t>
+          <t>SacredGame.Panel.html:L2459</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
@@ -6870,17 +6858,17 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>QUEST_AUTOWALK</t>
+          <t>LOGBOOK_ASPECT</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2476</t>
+          <t>SacredGame.Journal.html:L244; SacredGame.Journal.html:L262</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2089</t>
+          <t>SacredGame.Journal.html:L504 (relay list)</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
@@ -6907,17 +6895,17 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>REQ_ALIGN_TIPI</t>
+          <t>LOGBOOK_VISIBILITY</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1143</t>
+          <t>SacredGame.Journal.html:L365; SacredGame.Journal.html:L375</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L558; SacredGame.Panel.html:L2469 (relay list)</t>
+          <t>js/sanctuary/SanctuaryJournalBridge.js:L106</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
@@ -6944,17 +6932,17 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>REQ_AUTOWALK_TO_ENTITY</t>
+          <t>OPEN_LOGBOOK</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2364</t>
+          <t>SacredGame.Panel.html:L2102</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2267</t>
+          <t>SacredGame.Journal.html:L430</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -6981,17 +6969,17 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>REQ_HIDE_AXE</t>
+          <t>QUEST_AUTOWALK</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L648; js/components/Component.NewJournal.html:L1152; js/components/Component.NewJournal.html:L1165</t>
+          <t>SacredGame.Panel.html:L2476</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L550; SacredGame.Panel.html:L2469 (relay list)</t>
+          <t>SacredGame.Panel.html:L2089</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
@@ -7018,17 +7006,17 @@
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>REQ_HIDE_TIPI</t>
+          <t>REQ_ALIGN_TIPI</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L377; js/components/Component.NewJournal.html:L647; js/components/Component.NewJournal.html:L1127; js/components/Component.NewJournal.html:L1145</t>
+          <t>js/components/Component.NewJournal.html:L1143</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L579; SacredGame.Panel.html:L2469 (relay list)</t>
+          <t>SacredGame.Journal.html:L558; SacredGame.Panel.html:L2469 (relay list)</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -7055,17 +7043,17 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>REQ_START_AUTO_WALK</t>
+          <t>REQ_AUTOWALK_TO_ENTITY</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2086; SacredGame.Panel.html:L2348</t>
+          <t>SacredGame.Panel.html:L2364</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>index.html:L901</t>
+          <t>SacredGame.Panel.html:L2267</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
@@ -7092,17 +7080,17 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>REQ_TOGGLE_JOURNAL</t>
+          <t>REQ_HIDE_AXE</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2571</t>
+          <t>js/components/Component.NewJournal.html:L648; js/components/Component.NewJournal.html:L1152; js/components/Component.NewJournal.html:L1165</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>index.html:L751</t>
+          <t>SacredGame.Journal.html:L550; SacredGame.Panel.html:L2469 (relay list)</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -7129,17 +7117,17 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>REQ_TOGGLE_LOGBOOK</t>
+          <t>REQ_HIDE_TIPI</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L650</t>
+          <t>SacredGame.Journal.html:L377; js/components/Component.NewJournal.html:L647; js/components/Component.NewJournal.html:L1127; js/components/Component.NewJournal.html:L1145</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>index.html:L717; SacredGame.Panel.html:L2261; SacredGame.Journal.html:L424</t>
+          <t>SacredGame.Journal.html:L579; SacredGame.Panel.html:L2469 (relay list)</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
@@ -7166,17 +7154,17 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>RETURN_TO_GAME</t>
+          <t>REQ_START_AUTO_WALK</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L651</t>
+          <t>SacredGame.Panel.html:L2086; SacredGame.Panel.html:L2348</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>index.html:L716</t>
+          <t>index.html:L901</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -7203,17 +7191,17 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>SWITCH_TAB</t>
+          <t>REQ_TOGGLE_JOURNAL</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2339; SacredGame.Panel.html:L2356; SacredGame.Panel.html:L2377; SacredGame.Panel.html:L2426; SacredGame.Journal.html:L489</t>
+          <t>SacredGame.Panel.html:L2571</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1250; SacredGame.Journal.html:L504 (relay list)</t>
+          <t>index.html:L751</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -7240,17 +7228,17 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>THUMB_MOVE</t>
+          <t>REQ_TOGGLE_LOGBOOK</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1841; SacredGame.Panel.html:L1855</t>
+          <t>js/components/Component.NewJournal.html:L650</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>index.html:L882</t>
+          <t>index.html:L717; SacredGame.Panel.html:L2261; SacredGame.Journal.html:L424</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -7277,17 +7265,17 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>TOGGLE_VIEW_MODE</t>
+          <t>RETURN_TO_GAME</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L233; js/components/Component.NewJournal.html:L815</t>
+          <t>js/components/Component.NewJournal.html:L651</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>index.html:L876</t>
+          <t>index.html:L716</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
@@ -7314,17 +7302,17 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>VIDEO_READY</t>
+          <t>SWITCH_TAB</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L275</t>
+          <t>SacredGame.Panel.html:L2339; SacredGame.Panel.html:L2356; SacredGame.Panel.html:L2377; SacredGame.Panel.html:L2426; SacredGame.Journal.html:L489</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>index.html:L417</t>
+          <t>js/components/Component.NewJournal.html:L1250; SacredGame.Journal.html:L504 (relay list)</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
@@ -7351,17 +7339,17 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>VISIBILITY_CHANGE</t>
+          <t>THUMB_MOVE</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>index.html:L690; index.html:L730; SacredGame.Journal.html:L351; SacredGame.Journal.html:L358; SacredGame.Journal.html:L370</t>
+          <t>SacredGame.Panel.html:L1841; SacredGame.Panel.html:L1855</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1225; SacredGame.Journal.html:L504 (relay list)</t>
+          <t>index.html:L882</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
@@ -7388,17 +7376,17 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>VOLUME_CHANGE</t>
+          <t>TOGGLE_VIEW_MODE</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2450; SacredGame.Panel.html:L2452</t>
+          <t>js/v2/UIModule.js:L233; js/components/Component.NewJournal.html:L815</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L2456</t>
+          <t>index.html:L876</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
@@ -7420,22 +7408,22 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>window.* function call</t>
+          <t>postMessage type</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>__regenerateBraziers</t>
+          <t>VIDEO_READY</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L438</t>
+          <t>js/components/Component.LoadingModal.html:L275</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryBraziers.js:L315</t>
+          <t>index.html:L417</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
@@ -7443,7 +7431,11 @@
           <t>Has receiver</t>
         </is>
       </c>
-      <c r="G185" s="5" t="inlineStr"/>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>Receiver may sit in another frame; both frames scanned</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -7453,22 +7445,22 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>window.* function call</t>
+          <t>postMessage type</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>__regenerateDock</t>
+          <t>VISIBILITY_CHANGE</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L448</t>
+          <t>index.html:L690; index.html:L730; SacredGame.Journal.html:L351; SacredGame.Journal.html:L358; SacredGame.Journal.html:L370</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryDock.js:L458</t>
+          <t>js/components/Component.NewJournal.html:L1225; SacredGame.Journal.html:L504 (relay list)</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
@@ -7476,7 +7468,11 @@
           <t>Has receiver</t>
         </is>
       </c>
-      <c r="G186" s="5" t="inlineStr"/>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>Receiver may sit in another frame; both frames scanned</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -7486,22 +7482,22 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>window.* function call</t>
+          <t>postMessage type</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>__regenerateTipiNpcs</t>
+          <t>VOLUME_CHANGE</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L433</t>
+          <t>SacredGame.Panel.html:L2450; SacredGame.Panel.html:L2452</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryTipiNpcs.js:L290</t>
+          <t>SacredGame.Panel.html:L2456</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
@@ -7509,7 +7505,11 @@
           <t>Has receiver</t>
         </is>
       </c>
-      <c r="G187" s="5" t="inlineStr"/>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>Receiver may sit in another frame; both frames scanned</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -7524,17 +7524,17 @@
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>__regenerateTipis</t>
+          <t>__regenerateBraziers</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L428</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L438</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryTipis.js:L336</t>
+          <t>js/sanctuary/SanctuaryBraziers.js:L315</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -7557,17 +7557,17 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>__sanctuaryFishingSpawnRipple</t>
+          <t>__regenerateDock</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFish.js:L1209; js/sanctuary/SanctuaryFish.js:L1258; js/sanctuary/SanctuaryFish.js:L1342; js/sanctuary/SanctuaryFishing.js:L2230</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L448</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFishing.js:L991</t>
+          <t>js/sanctuary/SanctuaryDock.js:L458</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
@@ -7590,17 +7590,17 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>__sanctuarySpawnBabyFish</t>
+          <t>__regenerateTipiNpcs</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFish.js:L604; js/sanctuary/SanctuaryFishing.js:L2439</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L433</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFish.js:L547</t>
+          <t>js/sanctuary/SanctuaryTipiNpcs.js:L290</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -7623,17 +7623,17 @@
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>_v4CancelClickToMove</t>
+          <t>__regenerateTipis</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFishing.js:L1521; js/sanctuary/SanctuaryFishing.js:L2641; js/sanctuary/SanctuaryKeyboardLook.js:L80; js/sanctuary/SanctuaryKeyboardLook.js:L136; js/sanctuary/SanctuaryKeyboardLook.js:L170; index.html:L828; index.html:L904</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L428</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryClickToMove.js:L223</t>
+          <t>js/sanctuary/SanctuaryTipis.js:L336</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>_v4SmartWalkTo</t>
+          <t>__sanctuaryFishingSpawnRipple</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>index.html:L854; index.html:L858</t>
+          <t>js/sanctuary/SanctuaryFish.js:L1209; js/sanctuary/SanctuaryFish.js:L1258; js/sanctuary/SanctuaryFish.js:L1342; js/sanctuary/SanctuaryFishing.js:L2230</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryClickToMove.js:L252</t>
+          <t>js/sanctuary/SanctuaryFishing.js:L991</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
@@ -7689,17 +7689,17 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>_v4StartFishing</t>
+          <t>__sanctuarySpawnBabyFish</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>index.html:L832</t>
+          <t>js/sanctuary/SanctuaryFish.js:L604; js/sanctuary/SanctuaryFishing.js:L2439</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFishing.js:L1272</t>
+          <t>js/sanctuary/SanctuaryFish.js:L547</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
@@ -7722,17 +7722,17 @@
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>_v4ToggleJournal</t>
+          <t>_v4CancelClickToMove</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L246; index.html:L294; index.html:L661</t>
+          <t>js/sanctuary/SanctuaryFishing.js:L1521; js/sanctuary/SanctuaryFishing.js:L2641; js/sanctuary/SanctuaryKeyboardLook.js:L80; js/sanctuary/SanctuaryKeyboardLook.js:L136; js/sanctuary/SanctuaryKeyboardLook.js:L170; index.html:L828; index.html:L904</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>index.html:L693</t>
+          <t>js/sanctuary/SanctuaryClickToMove.js:L223</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
@@ -7755,17 +7755,17 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>_v4TogglePanel</t>
+          <t>_v4SmartWalkTo</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L241; index.html:L313; index.html:L791</t>
+          <t>index.html:L854; index.html:L858</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>index.html:L736</t>
+          <t>js/sanctuary/SanctuaryClickToMove.js:L252</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>_v4ToggleTopDown</t>
+          <t>_v4StartFishing</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>index.html:L880</t>
+          <t>index.html:L832</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L278</t>
+          <t>js/sanctuary/SanctuaryFishing.js:L1272</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>_v4WalkTo</t>
+          <t>_v4ToggleJournal</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryClickToMove.js:L283; js/sanctuary/SanctuaryClickToMove.js:L323; index.html:L851</t>
+          <t>js/sanctuary/SanctuaryControls.js:L246; index.html:L294; index.html:L661</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryClickToMove.js:L236</t>
+          <t>index.html:L693</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
@@ -7854,17 +7854,17 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>addPage</t>
+          <t>_v4TogglePanel</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L862; js/components/Component.NewJournal.html:L1299</t>
+          <t>js/sanctuary/SanctuaryControls.js:L241; index.html:L313; index.html:L791</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L785</t>
+          <t>index.html:L736</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
@@ -7887,17 +7887,17 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>getPageFontIndex</t>
+          <t>_v4ToggleTopDown</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L670; js/components/Component.NewJournal.html:L683</t>
+          <t>index.html:L880</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L665</t>
+          <t>js/sanctuary/SanctuaryControls.js:L278</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
@@ -7920,17 +7920,17 @@
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>initPanelIcons</t>
+          <t>_v4WalkTo</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L73; SacredGame.Panel.html:L1939</t>
+          <t>js/sanctuary/SanctuaryClickToMove.js:L283; js/sanctuary/SanctuaryClickToMove.js:L323; index.html:L851</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Panel.html:L1898</t>
+          <t>js/sanctuary/SanctuaryClickToMove.js:L236</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
@@ -7953,17 +7953,17 @@
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>sanctuaryGrant</t>
+          <t>addPage</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFishing.js:L2446</t>
+          <t>js/components/Component.NewJournal.html:L862; js/components/Component.NewJournal.html:L1299</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryInventory.js:L155</t>
+          <t>js/components/Component.NewJournal.html:L785</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
@@ -7986,17 +7986,17 @@
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>sanctuaryPulse</t>
+          <t>getPageFontIndex</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/MoldPlantLily.js:L107; js/sanctuary/SanctuaryFish.js:L939; js/sanctuary/SanctuaryFish.js:L1011; js/sanctuary/SanctuaryFish.js:L1076; js/sanctuary/SanctuaryFish.js:L1146; js/sanctuary/SanctuaryFish.js:L1153; js/sanctuary/SanctuaryFish.js:L1396; js/sanctuary/SanctuaryFish.js:L1581; js/sanctuary/SanctuaryFishJumps.js:L152; js/sanctuary/SanctuaryFishJumps.js:L172; js/sanctuary/SanctuaryFishing.js:L2232; js/sanctuary/SanctuaryFrogs.js:L886</t>
+          <t>js/components/Component.NewJournal.html:L670; js/components/Component.NewJournal.html:L683</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryCircles.js:L191</t>
+          <t>js/components/Component.NewJournal.html:L665</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
@@ -8019,17 +8019,17 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>startGameSequence</t>
+          <t>initPanelIcons</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L1022; js/components/Component.NewJournal.html:L1094</t>
+          <t>SacredGame.Panel.html:L73; SacredGame.Panel.html:L1939</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L907</t>
+          <t>SacredGame.Panel.html:L1898</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
@@ -8052,17 +8052,17 @@
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>switchBookTab</t>
+          <t>sanctuaryGrant</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L799; js/components/Component.NewJournal.html:L869</t>
+          <t>js/sanctuary/SanctuaryFishing.js:L2446</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.NewJournal.html:L763</t>
+          <t>js/sanctuary/SanctuaryInventory.js:L155</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
@@ -8085,28 +8085,127 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
+          <t>sanctuaryPulse</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/MoldPlantLily.js:L107; js/sanctuary/SanctuaryFish.js:L939; js/sanctuary/SanctuaryFish.js:L1011; js/sanctuary/SanctuaryFish.js:L1076; js/sanctuary/SanctuaryFish.js:L1146; js/sanctuary/SanctuaryFish.js:L1153; js/sanctuary/SanctuaryFish.js:L1396; js/sanctuary/SanctuaryFish.js:L1581; js/sanctuary/SanctuaryFishJumps.js:L152; js/sanctuary/SanctuaryFishJumps.js:L172; js/sanctuary/SanctuaryFishing.js:L2232; js/sanctuary/SanctuaryFrogs.js:L886</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryCircles.js:L191</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>Has receiver</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>LMB-202</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>window.* function call</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>startGameSequence</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>js/components/Component.NewJournal.html:L1022; js/components/Component.NewJournal.html:L1094</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>js/components/Component.NewJournal.html:L907</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>Has receiver</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>LMB-203</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>window.* function call</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>switchBookTab</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>js/components/Component.NewJournal.html:L799; js/components/Component.NewJournal.html:L869</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>js/components/Component.NewJournal.html:L763</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>Has receiver</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>LMB-204</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>window.* function call</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
           <t>toggleLogbook</t>
         </is>
       </c>
-      <c r="D205" s="5" t="inlineStr">
+      <c r="D208" s="5" t="inlineStr">
         <is>
           <t>SacredGame.Panel.html:L2085; SacredGame.Panel.html:L2191; SacredGame.Panel.html:L2475; SacredGame.Panel.html:L2479; SacredGame.Panel.html:L2537; SacredGame.Journal.html:L425; SacredGame.Journal.html:L432; SacredGame.Journal.html:L449; SacredGame.Journal.html:L458; SacredGame.Journal.html:L466; SacredGame.Journal.html:L476; SacredGame.Journal.html:L486</t>
         </is>
       </c>
-      <c r="E205" s="5" t="inlineStr">
+      <c r="E208" s="5" t="inlineStr">
         <is>
           <t>SacredGame.Panel.html:L2565; SacredGame.Journal.html:L339</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
+      <c r="F208" s="5" t="inlineStr">
         <is>
           <t>Has receiver</t>
         </is>
       </c>
-      <c r="G205" s="5" t="inlineStr"/>
+      <c r="G208" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G205"/>
+  <autoFilter ref="A4:G208"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8117,7 +8216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10938,8 +11037,256 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>FND-45</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>SUB-05</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Mobile PiP reads pixels back synchronously every PiP frame</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Mobile PiP is cheap because it is 256² on the main context.</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>readRenderTargetPixels → gl.readPixels into client memory: the CPU waits for the GPU to finish everything queued (the whole main frame) before the next JS line runs. While fishing this happens every other frame; in top-down view every frame (no stride gate).</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js:L1737 · js/v2/Orchestrator.js:L1402</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>A full CPU–GPU sync point per PiP frame on phones; the stutter source the prompt describes. Not measured here (no phone/GPU).</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Playbook C-12: PBO + fenceSync + polled getBufferSubData (WebGL2), sync path kept as WebGL1 fallback.</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>PLN-22</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>FND-46</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>SUB-06</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Brazier night lights never turn on (deaf listener)</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Braziers listen to day/night and light up at night.</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Braziers listen on window for 'anu:season-change'; DayNight sends ANU_EVENTS.SEASON_CHANGE ('anu-season-change') on the InteractionBus only, which never fires a window event. limbo.py (new DEAF check) also lists 'sanctuary:buildings:changed' and 'v2-pip-zoom-change' as listeners nothing fires.</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryBraziers.js:L311 · js/sanctuary/SanctuaryDayNight.js:L121</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Feature silently off. If fixed with light.visible toggles, every lit material builds a new program variant on the first night (compile hitch) — the prompt's E15 point.</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Owner decision (playbook C-10 #9): wire to the bus, and pre-warm with renderer.compileAsync or keep lights visible at intensity 0 (costs 4 point lights in every lit pixel, always).</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>PLN-22</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>FND-47</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>SUB-05</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Mobile PiP flips scene.fog, forcing a program lookup for every fogged material twice per PiP frame</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Nulling fog for the PiP is free.</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>three r160 setProgram: material.fog &amp;&amp; materialProperties.fog !== fog → getProgram → getParameters + getProgramCacheKey (L30232, L29985–30018). Programs stay cached per material (no GL recompile), but on mobile the PiP shares the main renderer, so fog null → Fog → null runs that path for every fogged material each PiP frame. Desktop PiP has its own renderer and is unaffected. Fishing close-up (layer 2) also flips the light hash the same way on mobile.</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js:L1458 · vendor/three/three.module.js:L30232</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>CPU cost scales with material count (pool alone 108). Not measured here.</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Playbook C-11: keep the Fog object and push near/far out for the PiP pass (uniforms only).</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>PLN-22</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>FND-48</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>SUB-08</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Footprint trail draws all 50 instances, hidden ones at scale 0</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Unused footprints cost nothing.</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>InstancedMesh(…, 50) with frustumCulled = false; unused slots get a zero-scale matrix and are still drawn; a new Object3D is allocated per walking frame.</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryClickToMove.js:L487</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Small: one draw, 50 instances of vertex work, one allocation per frame while walking.</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Playbook C-13: mesh.count = printCount (the prompt's count clipping).</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>PLN-22</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L48"/>
+  <autoFilter ref="A4:L52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12307,7 +12654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13071,37 +13418,325 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>CLM-24</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hot paths are _refreshSegmentInstanceSourceAt, _tickUberCull, _tickSealedCull, _tickSuperSectionCull, _pipBlit, _compassionSample, _roomBillboardTrack.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>None exist in SacredAdventures. They are Origami Reality Engine names (only _pipBlit found: Origami-Release/js/v8/OniBaba8.js). The prompt targets a different engine.</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js:L1392</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>CLM-25</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Blocking GL calls (getError, getParameter, query reads) stall the hot loop.</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Game code has none of those, and both renderers set checkShaderErrors = false. One real sync point exists: mobile PiP readRenderTargetPixels (FND-45).</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Applies (1 site)</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js:L1737</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>CLM-26</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Use fenceSync / clientWaitSync instead of blocking reads.</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Applies only to FND-45 (PBO readback). No GPU queries are used anywhere.</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Applies (1 site)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js:L1737</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>CLM-27</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Lock VAOs; stream matrices with bufferSubData instead of reallocating.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>three r160 already does both: VAOs per geometry/program and bufferSubData on needsUpdate (vendor L13607–13644, L15132). Game code makes no raw GL buffer calls.</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Already true</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>vendor/three/three.module.js:L15132</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>CLM-28</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Never hide lights with .visible; scale intensity to 0 (E15).</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Mechanism true in r160 (light counts are in the program key). Only braziers toggle .visible, and that toggle never fires today (FND-46). Intensity 0 keeps 4 point lights in every lit pixel, so pre-warming is the cheaper fix.</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Partly applies</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryBraziers.js:L308</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>CLM-29</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Reuse shadow render targets when shadow resolution drops under load.</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Shadow map size is set once (512², SanctuaryGround) and never changed; governors only toggle shadowMap.autoUpdate.</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryGround.js:L719</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>CLM-30</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>PiP and secondary passes must not evaluate redundant geometry (layer audit).</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>PiP cameras enable layer 0, so they draw every default object (FND-44). Mobile PiP also flips fog per pass (FND-47).</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Applies</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js:L1161</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>CLM-31</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Clip instanced draws with mesh.count when frustumCulled = false.</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>One case: footprint trail (FND-48). Other per-frame instanced update is the 32-fish school (full upload of 2 KB, fine).</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Applies (low)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryClickToMove.js:L188</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>CLM-32</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Mobile culling master prompt</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Budget VRAM per screen pixel; delete GL objects eagerly.</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>VRAM here is fixed asset textures (FND-03), already capped at 256 px on mobile upload (ATT-14). Eager delete = dispose(); the real gap is the catch leak (FND-32).</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Not applicable as written</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js:L181</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>CLM-15</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Project description</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Village builder + hunting + fishing + crafting simulator.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Fishing and village shaping exist; hunting and crafting have no code in the live build.</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Partly true</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>js/sanctuary/SanctuaryInventory.js:L12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F27"/>
+  <autoFilter ref="A4:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13112,7 +13747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13944,43 +14579,83 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>PLN-22</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Mobile PiP sync + program churn (C-11..C-13)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>FND-45, FND-46, FND-47, FND-48</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js (_preparePipScene, _restorePipScene, mobile branch of _renderWithMask); js/sanctuary/SanctuaryClickToMove.js</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Phone Performance trace: no readPixels wait in PiP frames; no getProgram calls in PiP frames; PiP image unchanged.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>From the master-prompt applicability check (CLM-24..32). C-12 needs a phone to verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>PLN-15</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B26" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Correct README / CONTRIBUTING</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>FND-19</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>README.md; CONTRIBUTING.md; PROGRESS.md</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Docs match 10_System facts.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H25"/>
+  <autoFilter ref="A4:H26"/>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not started,In progress,Blocked,Awaiting approval,Done (code) — verify in browser,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15044,7 +15719,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 49dabb0.</t>
+          <t>Built at commit 2854704.</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16605,8 +17280,102 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>ATT-31</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Limbo tracer</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Check only senders without receivers</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Missed listeners nothing fires (brazier night lights); added DEAF check → 3 found</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>limbo.py</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Trace both directions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>ATT-32</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>User + Claude</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Apply the Origami 'Mobile WebGL Culling' master prompt to this repo</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Its named methods do not exist here; 4 of 9 ideas apply (FND-45..48), the rest are already true or not applicable (CLM-24..32)</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>CLM-24..32</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Check a prompt's names against the code before running its passes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I34"/>
+  <autoFilter ref="A4:I36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16617,7 +17386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17011,8 +17780,35 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>LOG-14</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Checked the mobile-culling master prompt against the code: CLM-24..32, FND-45..48, PLN-22, playbook cards C-11..C-13 + C-10 #9.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>PLN-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E17"/>
+  <autoFilter ref="A4:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17070,7 +17866,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>49dabb0</t>
+          <t>2854704</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -17280,7 +18076,7 @@
         </is>
       </c>
       <c r="B18" s="11">
-        <f>COUNTIF('44_Limbo_Calls'!$F$5:$F$205,"LIMBO*")</f>
+        <f>COUNTIF('44_Limbo_Calls'!$F$5:$F$208,"LIMBO*")</f>
         <v/>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -17376,7 +18172,7 @@
         </is>
       </c>
       <c r="B24" s="11">
-        <f>COUNTIF('50_Findings'!$B$5:$B$48,"Critical")+COUNTIF('50_Findings'!$B$5:$B$48,"High")</f>
+        <f>COUNTIF('50_Findings'!$B$5:$B$52,"Critical")+COUNTIF('50_Findings'!$B$5:$B$52,"High")</f>
         <v/>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -17392,7 +18188,7 @@
         </is>
       </c>
       <c r="B25" s="11">
-        <f>COUNTIF('60_Plan'!$G$5:$G$25,"Done*")&amp;" of "&amp;COUNTA('60_Plan'!$A$5:$A$25)</f>
+        <f>COUNTIF('60_Plan'!$G$5:$G$26,"Done*")&amp;" of "&amp;COUNTA('60_Plan'!$A$5:$A$26)</f>
         <v/>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -17697,7 +18493,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 49dabb0</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 2854704</t>
         </is>
       </c>
     </row>
@@ -19972,12 +20768,12 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>FND-04, FND-05, FND-06, FND-21, FND-22, FND-25, FND-26, FND-31, FND-44</t>
+          <t>FND-04, FND-05, FND-06, FND-21, FND-22, FND-25, FND-26, FND-31, FND-44, FND-45, FND-47</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>PLN-05, PLN-06, PLN-16, PLN-18, PLN-19</t>
+          <t>PLN-05, PLN-06, PLN-16, PLN-18, PLN-19, PLN-22</t>
         </is>
       </c>
     </row>
@@ -20021,12 +20817,12 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>FND-35, FND-36, FND-37, FND-38, FND-39, FND-40, FND-43</t>
+          <t>FND-35, FND-36, FND-37, FND-38, FND-39, FND-40, FND-43, FND-46</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>PLN-21</t>
+          <t>PLN-21, PLN-22</t>
         </is>
       </c>
     </row>
@@ -20119,12 +20915,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>FND-17, FND-29</t>
+          <t>FND-17, FND-29, FND-48</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>PLN-14, PLN-20</t>
+          <t>PLN-14, PLN-20, PLN-22</t>
         </is>
       </c>
     </row>
@@ -21671,7 +22467,11 @@
           <t>2026-05-29 feat(sanctuary): center-screen responsive welcome guide, organic shore, and mossy boulders</t>
         </is>
       </c>
-      <c r="X16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>FND-46</t>
+        </is>
+      </c>
       <c r="Y16" s="6" t="n">
         <v>400</v>
       </c>
@@ -21938,7 +22738,11 @@
           <t>2026-05-29 feat(sanctuary): center-screen responsive welcome guide, organic shore, and mossy boulders</t>
         </is>
       </c>
-      <c r="X19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr">
+        <is>
+          <t>FND-48</t>
+        </is>
+      </c>
       <c r="Y19" s="6" t="n">
         <v>558</v>
       </c>
@@ -22189,7 +22993,11 @@
           <t>2026-05-26 feat(pip): add branches back to pip and bump sw cache to v24</t>
         </is>
       </c>
-      <c r="X22" s="5" t="inlineStr"/>
+      <c r="X22" s="5" t="inlineStr">
+        <is>
+          <t>FND-46</t>
+        </is>
+      </c>
       <c r="Y22" s="6" t="n">
         <v>181</v>
       </c>
@@ -25592,7 +26400,7 @@
       </c>
       <c r="X63" s="5" t="inlineStr">
         <is>
-          <t>FND-03, FND-04, FND-05, FND-06, FND-07, FND-08, FND-09, FND-11, FND-14, FND-16, FND-20, FND-21, FND-22, FND-31, FND-44</t>
+          <t>FND-03, FND-04, FND-05, FND-06, FND-07, FND-08, FND-09, FND-11, FND-14, FND-16, FND-20, FND-21, FND-22, FND-31, FND-44, FND-45, FND-47</t>
         </is>
       </c>
       <c r="Y63" s="6" t="n">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'12_Frame_Loop'!$A$4:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'20_Subsystems'!$A$4:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'30_Modules'!$A$4:$X$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'40_Connections'!$A$4:$G$485</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'40_Connections'!$A$4:$G$487</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'41_Globals'!$A$4:$G$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'42_Events'!$A$4:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'43_Services'!$A$4:$E$9</definedName>
@@ -41,11 +41,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'50_Findings'!$A$4:$L$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'51_Assets'!$A$4:$W$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'52_Claims_vs_Verified'!$A$4:$F$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 49dabb0. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit b59e8a2. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L899; js/v2/OrchestratorHud.js:L940</t>
+          <t>js/v2/OrchestratorHud.js:L904; js/v2/OrchestratorHud.js:L945</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L486</t>
+          <t>js/components/Component.LoadingModal.html:L525</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
@@ -3057,12 +3057,12 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L532; js/components/Component.LoadingModal.html:L560; js/components/Component.LoadingModal.html:L594</t>
+          <t>js/components/Component.LoadingModal.html:L571; js/components/Component.LoadingModal.html:L599; js/components/Component.LoadingModal.html:L633</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L250</t>
+          <t>js/components/Component.LoadingModal.html:L289</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L267; js/components/Component.LoadingModal.html:L640</t>
+          <t>js/components/Component.LoadingModal.html:L306; js/components/Component.LoadingModal.html:L679</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L221</t>
+          <t>js/components/Component.LoadingModal.html:L256</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L510</t>
+          <t>js/components/Component.LoadingModal.html:L549</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L258</t>
+          <t>js/components/Component.LoadingModal.html:L297</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L268</t>
+          <t>js/components/Component.LoadingModal.html:L307</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L222</t>
+          <t>js/components/Component.LoadingModal.html:L257</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L538; js/components/Component.LoadingModal.html:L586</t>
+          <t>js/components/Component.LoadingModal.html:L577; js/components/Component.LoadingModal.html:L625</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L247</t>
+          <t>js/components/Component.LoadingModal.html:L286</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L541; js/components/Component.LoadingModal.html:L583; js/components/Component.LoadingModal.html:L621</t>
+          <t>js/components/Component.LoadingModal.html:L580; js/components/Component.LoadingModal.html:L622; js/components/Component.LoadingModal.html:L660</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L248</t>
+          <t>js/components/Component.LoadingModal.html:L287</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L672</t>
+          <t>js/v2/OrchestratorHud.js:L677</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L40</t>
+          <t>js/v2/OrchestratorHud.js:L43</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L613</t>
+          <t>js/v2/OrchestratorHud.js:L618</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L80</t>
+          <t>js/v2/OrchestratorHud.js:L83</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L612</t>
+          <t>js/v2/OrchestratorHud.js:L617</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L41</t>
+          <t>js/v2/OrchestratorHud.js:L44</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L96</t>
+          <t>js/v2/OrchestratorHud.js:L99</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L98; js/v2/OrchestratorHud.js:L98</t>
+          <t>js/v2/OrchestratorHud.js:L101; js/v2/OrchestratorHud.js:L101</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L611</t>
+          <t>js/v2/OrchestratorHud.js:L616</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L34</t>
+          <t>js/v2/OrchestratorHud.js:L36</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L652</t>
+          <t>js/v2/OrchestratorHud.js:L657</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L36</t>
+          <t>js/v2/OrchestratorHud.js:L39</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L461</t>
+          <t>js/v2/OrchestratorHud.js:L466</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L47</t>
+          <t>js/v2/OrchestratorHud.js:L50</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L205</t>
+          <t>js/v2/OrchestratorHud.js:L210</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L74</t>
+          <t>js/v2/OrchestratorHud.js:L77</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -4806,12 +4806,12 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L650</t>
+          <t>js/v2/OrchestratorHud.js:L655</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L37</t>
+          <t>js/v2/OrchestratorHud.js:L40</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L651</t>
+          <t>js/v2/OrchestratorHud.js:L656</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L38</t>
+          <t>js/v2/OrchestratorHud.js:L41</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L540</t>
+          <t>js/v2/OrchestratorHud.js:L545</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L85</t>
+          <t>js/v2/OrchestratorHud.js:L88</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L589</t>
+          <t>js/v2/OrchestratorHud.js:L594</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L79</t>
+          <t>js/v2/OrchestratorHud.js:L82</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L478; js/v2/OrchestratorHud.js:L879; js/v2/OrchestratorHud.js:L938; index.html:L437; index.html:L868</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L478; js/v2/OrchestratorHud.js:L884; js/v2/OrchestratorHud.js:L943; index.html:L437; index.html:L868</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L152; js/v2/OrchestratorHud.js:L152</t>
+          <t>js/v2/OrchestratorHud.js:L157; js/v2/OrchestratorHud.js:L157</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L108</t>
+          <t>js/v2/OrchestratorHud.js:L111</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L110; js/v2/OrchestratorHud.js:L110</t>
+          <t>js/v2/OrchestratorHud.js:L113; js/v2/OrchestratorHud.js:L113</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L887; js/v2/OrchestratorHud.js:L939</t>
+          <t>js/v2/OrchestratorHud.js:L892; js/v2/OrchestratorHud.js:L944</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L637</t>
+          <t>js/v2/OrchestratorHud.js:L642</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L42</t>
+          <t>js/v2/OrchestratorHud.js:L45</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L462</t>
+          <t>js/v2/OrchestratorHud.js:L467</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L61</t>
+          <t>js/v2/OrchestratorHud.js:L64</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L465</t>
+          <t>js/v2/OrchestratorHud.js:L470</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L56</t>
+          <t>js/v2/OrchestratorHud.js:L59</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L464</t>
+          <t>js/v2/OrchestratorHud.js:L469</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L54</t>
+          <t>js/v2/OrchestratorHud.js:L57</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L480</t>
+          <t>js/v2/OrchestratorHud.js:L485</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L62</t>
+          <t>js/v2/OrchestratorHud.js:L65</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L474; js/v2/OrchestratorHud.js:L482</t>
+          <t>js/v2/OrchestratorHud.js:L479; js/v2/OrchestratorHud.js:L487</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L66</t>
+          <t>js/v2/OrchestratorHud.js:L69</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L463</t>
+          <t>js/v2/OrchestratorHud.js:L468</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L52</t>
+          <t>js/v2/OrchestratorHud.js:L55</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L206</t>
+          <t>js/v2/OrchestratorHud.js:L211</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L78</t>
+          <t>js/v2/OrchestratorHud.js:L81</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L590</t>
+          <t>js/v2/OrchestratorHud.js:L595</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L76</t>
+          <t>js/v2/OrchestratorHud.js:L79</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L706</t>
+          <t>js/v2/OrchestratorHud.js:L711</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L75</t>
+          <t>js/v2/OrchestratorHud.js:L78</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L207</t>
+          <t>js/v2/OrchestratorHud.js:L212</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L75</t>
+          <t>js/v2/OrchestratorHud.js:L78</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js:L92</t>
+          <t>js/v2/OrchestratorHud.js:L95</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L500</t>
+          <t>js/components/Component.LoadingModal.html:L539</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>js/components/Component.LoadingModal.html:L275</t>
+          <t>js/components/Component.LoadingModal.html:L314</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -13112,7 +13112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13944,43 +13944,259 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>PLN-22</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 0 — ground-truth baseline</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>docs/mobile/PHASE0_BASELINE.md; tools/mobile/*</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Every row has file:line or measurement evidence.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>MOBILE_OPTIMIZATION_PROMPT.md Phase 0. 6 profiles + online simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>PLN-23</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 1 — one 'is mobile' source</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/deviceProfile.js (new); Orchestrator.js; AnuAdaptiveDpr.js; gltfLoaderSetup.js</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>UA regex only in deviceProfile.js; Phase 0 measurements unchanged.</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>4 live copies (not 6); Orchestrator.js:1086 copy is dead on mobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>PLN-24</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 2 — panel icon renderer + source images</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>js/components/Component.ThreeIcons.js; SacredGame.Panel.html; mobile variants of NPC.YB / flora/reeds (Avatar-New = PLN-20)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Phone: no 2nd-context texture &gt; 256 px; no 4096^2 source maps on mobile.</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Online phone: 2nd WebGL context holds ~172 MB; 384 MB of 4096^2 source pixels. Coordinate with PLN-20 / FIX_PROMPT task 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>PLN-25</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 3 — fluid UI for remaining panels</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>OrchestratorHud.js (landscape breakpoint); UIModule.js (distance pill); SacredGame.Panel.html (center-stack); hidden sheets</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>tests/v4-mobile-layout.spec.js passes on all 6 profiles.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>PLN-26</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 4 — minimap without readback</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>FND-04</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/Orchestrator.js (_renderWithMask mobile branch)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>No readRenderTargetPixels on the mobile live path.</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting approval</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Needs Mark's written approval (PiP protect rule).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>PLN-27</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 6 — self-host lucide / three / fonts</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>SacredGame.Panel.html; vendor/</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>All-external-blocked boot: zero page errors.</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Offline: lucide@latest failure leaves panel action handlers undefined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>PLN-15</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B31" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Correct README / CONTRIBUTING</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>FND-19</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>README.md; CONTRIBUTING.md; PROGRESS.md</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Docs match 10_System facts.</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H25"/>
+  <autoFilter ref="A4:H31"/>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not started,In progress,Blocked,Awaiting approval,Done (code) — verify in browser,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15044,7 +15260,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 49dabb0.</t>
+          <t>Built at commit b59e8a2.</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16605,8 +16821,196 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>ATT-31</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Run Playwright with the preinstalled /opt/pw-browsers/chromium (executablePath) + SwiftShader args</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Worked: game boots headless; ~6–13 frames per 3 s, so layout/geometry/network only</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>tools/mobile/p0probe.js</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Supersedes ATT-15 when a Chromium binary is present; never use for FPS claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>ATT-32</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>REG + tipi</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Runtime check of ATT-21 (lite swap) desktop + iPhone UA</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Lite + mobile GLBs load (200), REG seated with 6 clips; scene 4.12M → 1.62M desktop</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>docs/mobile/phase0-measurements.json</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Pose/scale by eye and real-phone memory still NEEDS DEVICE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>ATT-33</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>First probe: two python http.servers on one port (old one never died)</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Invalid run: branch measured as main; caught by identical numbers</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Check which process owns the port (readlink /proc/PID/cwd) before every run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ATT-34</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 0</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Measure 6 profiles + online simulation (CDN → vendor, lucide stub)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Done; findings in PHASE0_BASELINE.md</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>docs/mobile/PHASE0_BASELINE.md</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Sandbox (offline) runs hide the panel's 2nd WebGL context — always add the online simulation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I34"/>
+  <autoFilter ref="A4:I38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16617,7 +17021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17011,8 +17415,112 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>LOG-14</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1: Sacred Ones logo in loading modal, welcome guide (sized to tip height), FPS HUD; fluid loading modal + guide (320–1280 + landscape).</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>commit 8d1570e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>LOG-15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1: wrote MOBILE_OPTIMIZATION_PROMPT.md (7 phases, zero-trust).</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Downloads handoff folder</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>LOG-16</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1: Mobile Phase 0 baseline measured and written.</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>PLN-22; docs/mobile/PHASE0_BASELINE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>LOG-17</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>NEXT: Mark's go-ahead for mobile Phase 1; decide whether Phase 2 may touch js/components/Component.ThreeIcons.js + SacredGame.Panel.html; coordinate Avatar mobile variant with PLN-20.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E17"/>
+  <autoFilter ref="A4:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17070,7 +17578,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>49dabb0</t>
+          <t>b59e8a2</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -17392,7 +17900,7 @@
         </is>
       </c>
       <c r="B25" s="11">
-        <f>COUNTIF('60_Plan'!$G$5:$G$25,"Done*")&amp;" of "&amp;COUNTA('60_Plan'!$A$5:$A$25)</f>
+        <f>COUNTIF('60_Plan'!$G$5:$G$31,"Done*")&amp;" of "&amp;COUNTA('60_Plan'!$A$5:$A$31)</f>
         <v/>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -17697,7 +18205,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 49dabb0</t>
+          <t>Activation order in index.html · evidence re-located at build · commit b59e8a2</t>
         </is>
       </c>
     </row>
@@ -19977,7 +20485,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>PLN-05, PLN-06, PLN-16, PLN-18, PLN-19</t>
+          <t>PLN-05, PLN-06, PLN-16, PLN-18, PLN-19, PLN-26</t>
         </is>
       </c>
     </row>
@@ -24404,7 +24912,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>465 lines, 15.9 KB. No update(). Writes 1 globals.</t>
+          <t>539 lines, 19.1 KB. No update(). Writes 1 globals.</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr"/>
@@ -24423,7 +24931,11 @@
       <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>Assets/SacredOnes.Logo.160.png</t>
+        </is>
+      </c>
       <c r="T49" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -24431,16 +24943,16 @@
       </c>
       <c r="U49" s="5" t="inlineStr"/>
       <c r="V49" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-29 feat(sanctuary): center-screen responsive welcome guide, organic shore, and mossy boulders</t>
+          <t>2026-10-22 feat(ui): Sacred Ones logo in loading modal, welcome guide, FPS HUD + fluid panels</t>
         </is>
       </c>
       <c r="X49" s="5" t="inlineStr"/>
       <c r="Y49" s="6" t="n">
-        <v>465</v>
+        <v>539</v>
       </c>
     </row>
     <row r="50">
@@ -25635,7 +26147,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>972 lines, 40.6 KB. No update(). Writes 2 globals.</t>
+          <t>977 lines, 41.1 KB. No update(). Writes 2 globals.</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
@@ -25666,7 +26178,11 @@
         </is>
       </c>
       <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="5" t="inlineStr"/>
+      <c r="S64" s="5" t="inlineStr">
+        <is>
+          <t>Assets/SacredOnes.Logo.160.png</t>
+        </is>
+      </c>
       <c r="T64" s="5" t="inlineStr"/>
       <c r="U64" s="5" t="inlineStr">
         <is>
@@ -25674,16 +26190,16 @@
         </is>
       </c>
       <c r="V64" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W64" s="5" t="inlineStr">
         <is>
-          <t>2026-06-01 feat(mobile): village build panel → neumorphic bottom sheet + de-dupe map</t>
+          <t>2026-10-22 feat(ui): Sacred Ones logo in loading modal, welcome guide, FPS HUD + fluid panels</t>
         </is>
       </c>
       <c r="X64" s="5" t="inlineStr"/>
       <c r="Y64" s="6" t="n">
-        <v>972</v>
+        <v>977</v>
       </c>
     </row>
     <row r="65">
@@ -29381,7 +29897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G485"/>
+  <dimension ref="A1:G487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -35920,29 +36436,25 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>MOD-046</t>
+          <t>MOD-045</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryWorldPlayerShim.js</t>
+          <t>js/sanctuary/SanctuaryWelcomeGuide.js</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>Assets/SacredOnes.Logo.160.png</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr"/>
       <c r="G189" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -35957,7 +36469,7 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
@@ -35972,10 +36484,14 @@
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>window.WorldPhysics</t>
-        </is>
-      </c>
-      <c r="F190" s="5" t="inlineStr"/>
+          <t>MOD-061</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>RuntimeServices.js</t>
+        </is>
+      </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -36005,7 +36521,7 @@
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>window.WorldPlayer</t>
+          <t>window.WorldPhysics</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr"/>
@@ -36023,7 +36539,7 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>service-register</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
@@ -36038,7 +36554,7 @@
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
+          <t>window.WorldPlayer</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr"/>
@@ -36056,7 +36572,7 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>service-register</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
@@ -36089,32 +36605,28 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>MOD-047</t>
+          <t>MOD-046</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryWorldTemplate.js</t>
+          <t>js/sanctuary/SanctuaryWorldPlayerShim.js</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>MOD-027</t>
-        </is>
-      </c>
-      <c r="F194" s="5" t="inlineStr">
-        <is>
-          <t>SanctuaryGround.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr"/>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -36141,12 +36653,12 @@
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-027</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>SanctuaryGround.js</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -36178,12 +36690,12 @@
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
@@ -36215,12 +36727,12 @@
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -36237,7 +36749,7 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
@@ -36252,10 +36764,14 @@
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.SOMETHING</t>
-        </is>
-      </c>
-      <c r="F198" s="5" t="inlineStr"/>
+          <t>MOD-100</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>anuEvents.js</t>
+        </is>
+      </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -36270,7 +36786,7 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>postMessage</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
@@ -36285,7 +36801,7 @@
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>msg:MY_KID_WORLD_HELLO</t>
+          <t>ANU_EVENTS.SOMETHING</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr"/>
@@ -36318,7 +36834,7 @@
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>msg:YOUR_EVENT</t>
+          <t>msg:MY_KID_WORLD_HELLO</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr"/>
@@ -36336,28 +36852,28 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>postMessage</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>MOD-048</t>
+          <t>MOD-047</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryZoom.js</t>
+          <t>js/sanctuary/SanctuaryWorldTemplate.js</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryTopDownHeight</t>
+          <t>msg:YOUR_EVENT</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr"/>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -36384,7 +36900,7 @@
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryZoomFactor</t>
+          <t>window.__sanctuaryTopDownHeight</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr"/>
@@ -36402,29 +36918,25 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>MOD-049</t>
+          <t>MOD-048</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>js/v2/AnuModule.js</t>
+          <t>js/sanctuary/SanctuaryZoom.js</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F203" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>window.__sanctuaryZoomFactor</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr"/>
       <c r="G203" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -36454,12 +36966,12 @@
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
@@ -36491,12 +37003,12 @@
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>MOD-101</t>
+          <t>MOD-100</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>index.js</t>
+          <t>anuEvents.js</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
@@ -36528,12 +37040,12 @@
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>MOD-102</t>
+          <t>MOD-101</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>pipelineMemory.js</t>
+          <t>index.js</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
@@ -36565,12 +37077,12 @@
       </c>
       <c r="E207" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-102</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>pipelineMemory.js</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
@@ -36587,7 +37099,7 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
@@ -36602,10 +37114,14 @@
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>window.AnuUniverse</t>
-        </is>
-      </c>
-      <c r="F208" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -36620,7 +37136,7 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
@@ -36635,7 +37151,7 @@
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.FUZZY_PIPELINE_SENSOR</t>
+          <t>window.AnuUniverse</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr"/>
@@ -36668,7 +37184,7 @@
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.GOVERNANCE_SNAPSHOT</t>
+          <t>ANU_EVENTS.FUZZY_PIPELINE_SENSOR</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr"/>
@@ -36701,7 +37217,7 @@
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.WORLD_SENSORIUM</t>
+          <t>ANU_EVENTS.GOVERNANCE_SNAPSHOT</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr"/>
@@ -36719,32 +37235,28 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>MOD-050</t>
+          <t>MOD-049</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>js/v2/BuildMode.js</t>
+          <t>js/v2/AnuModule.js</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>MOD-057</t>
-        </is>
-      </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>MapsConfig.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.WORLD_SENSORIUM</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="inlineStr"/>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -36771,12 +37283,12 @@
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-057</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>MapsConfig.js</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
@@ -36808,12 +37320,12 @@
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>MOD-074</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>WorldMossyRock.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -36845,12 +37357,12 @@
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-074</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>WorldMossyRock.js</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
@@ -36882,12 +37394,12 @@
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -36904,7 +37416,7 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
@@ -36919,10 +37431,14 @@
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>window._v2BuildClear</t>
-        </is>
-      </c>
-      <c r="F217" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -36937,7 +37453,7 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
@@ -36952,7 +37468,7 @@
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>Assets/tree.glb</t>
+          <t>window._v2BuildClear</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr"/>
@@ -36970,29 +37486,25 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>MOD-052</t>
+          <t>MOD-050</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>js/v2/ClickToMoveMarker.js</t>
+          <t>js/v2/BuildMode.js</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F219" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>Assets/tree.glb</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr"/>
       <c r="G219" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -37022,12 +37534,12 @@
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -37044,7 +37556,7 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
@@ -37059,10 +37571,14 @@
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPhysics</t>
-        </is>
-      </c>
-      <c r="F221" s="5" t="inlineStr"/>
+          <t>MOD-098</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>SimulationController.js</t>
+        </is>
+      </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -37077,29 +37593,25 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>MOD-053</t>
+          <t>MOD-052</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>js/v2/ConfettiBurst.js</t>
+          <t>js/v2/ClickToMoveMarker.js</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
-        </is>
-      </c>
-      <c r="F222" s="5" t="inlineStr">
-        <is>
-          <t>SimulationController.js</t>
-        </is>
-      </c>
+          <t>service:WorldPhysics</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr"/>
       <c r="G222" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -37119,22 +37631,22 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>MOD-054</t>
+          <t>MOD-053</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Fauna.js</t>
+          <t>js/v2/ConfettiBurst.js</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
@@ -37166,12 +37678,12 @@
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>WorldTerrain.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
@@ -37203,12 +37715,12 @@
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
@@ -37240,12 +37752,12 @@
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
@@ -37262,7 +37774,7 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
@@ -37277,10 +37789,14 @@
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>service:AnuNatureAwareness</t>
-        </is>
-      </c>
-      <c r="F227" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -37310,7 +37826,7 @@
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPhysics</t>
+          <t>service:AnuNatureAwareness</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr"/>
@@ -37343,7 +37859,7 @@
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
+          <t>service:WorldPhysics</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr"/>
@@ -37361,7 +37877,7 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
@@ -37376,7 +37892,7 @@
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>Assets/rabbit.animated.glb</t>
+          <t>service:WorldPlayer</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr"/>
@@ -37394,29 +37910,25 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>MOD-055</t>
+          <t>MOD-054</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Flora.js</t>
+          <t>js/v2/Fauna.js</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>MOD-056</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>FloraLegacyTreeLayout.js</t>
-        </is>
-      </c>
+          <t>Assets/rabbit.animated.glb</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr"/>
       <c r="G231" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -37446,12 +37958,12 @@
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>MOD-057</t>
+          <t>MOD-056</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>MapsConfig.js</t>
+          <t>FloraLegacyTreeLayout.js</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
@@ -37483,12 +37995,12 @@
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-057</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>MapsConfig.js</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -37520,12 +38032,12 @@
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
@@ -37557,12 +38069,12 @@
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>MOD-094</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>PipOrthoRingDiskClip.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
@@ -37594,12 +38106,12 @@
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-094</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>PipOrthoRingDiskClip.js</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
@@ -37631,12 +38143,12 @@
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
@@ -37668,12 +38180,12 @@
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-100</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>anuEvents.js</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
@@ -37705,12 +38217,12 @@
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
@@ -37727,7 +38239,7 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>anu-event-subscribe</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
@@ -37742,10 +38254,14 @@
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.SEASON_CHANGE</t>
-        </is>
-      </c>
-      <c r="F240" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -37760,7 +38276,7 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>anu-event-subscribe</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
@@ -37775,7 +38291,7 @@
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPhysics</t>
+          <t>ANU_EVENTS.SEASON_CHANGE</t>
         </is>
       </c>
       <c r="F241" s="5" t="inlineStr"/>
@@ -37808,7 +38324,7 @@
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
+          <t>service:WorldPhysics</t>
         </is>
       </c>
       <c r="F242" s="5" t="inlineStr"/>
@@ -37826,7 +38342,7 @@
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
@@ -37841,7 +38357,7 @@
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>Assets/tree.glb</t>
+          <t>service:WorldPlayer</t>
         </is>
       </c>
       <c r="F243" s="5" t="inlineStr"/>
@@ -37859,29 +38375,25 @@
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>MOD-056</t>
+          <t>MOD-055</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>js/v2/FloraLegacyTreeLayout.js</t>
+          <t>js/v2/Flora.js</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
-        </is>
-      </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>constants.js</t>
-        </is>
-      </c>
+          <t>Assets/tree.glb</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="inlineStr"/>
       <c r="G244" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -37896,28 +38408,32 @@
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>MOD-057</t>
+          <t>MOD-056</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>js/v2/MapsConfig.js</t>
+          <t>js/v2/FloraLegacyTreeLayout.js</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>window._v2ActiveMap</t>
-        </is>
-      </c>
-      <c r="F245" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -37944,7 +38460,7 @@
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>window._v2ListMaps</t>
+          <t>window._v2ActiveMap</t>
         </is>
       </c>
       <c r="F246" s="5" t="inlineStr"/>
@@ -37977,7 +38493,7 @@
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>window._v2SetMap</t>
+          <t>window._v2ListMaps</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr"/>
@@ -37995,29 +38511,25 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>MOD-058</t>
+          <t>MOD-057</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>js/v2/NPCBehaviour.js</t>
+          <t>js/v2/MapsConfig.js</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
-        </is>
-      </c>
-      <c r="F248" s="5" t="inlineStr">
-        <is>
-          <t>InteractionBus.js</t>
-        </is>
-      </c>
+          <t>window._v2SetMap</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="inlineStr"/>
       <c r="G248" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -38047,12 +38559,12 @@
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
@@ -38084,12 +38596,12 @@
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-100</t>
         </is>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>anuEvents.js</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
@@ -38106,7 +38618,7 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
@@ -38121,10 +38633,14 @@
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.PLAYER_NPC_GREETING</t>
-        </is>
-      </c>
-      <c r="F251" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -38139,29 +38655,25 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>MOD-059</t>
+          <t>MOD-058</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js</t>
+          <t>js/v2/NPCBehaviour.js</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>MOD-060</t>
-        </is>
-      </c>
-      <c r="F252" s="5" t="inlineStr">
-        <is>
-          <t>OrchestratorHud.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.PLAYER_NPC_GREETING</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="inlineStr"/>
       <c r="G252" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -38191,12 +38703,12 @@
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-060</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>OrchestratorHud.js</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
@@ -38228,12 +38740,12 @@
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>MOD-086</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>AdaptiveRenderPolicy.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
@@ -38265,12 +38777,12 @@
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>MOD-087</t>
+          <t>MOD-086</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>AnuErrorAndStressLedger.js</t>
+          <t>AdaptiveRenderPolicy.js</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
@@ -38302,12 +38814,12 @@
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>MOD-090</t>
+          <t>MOD-087</t>
         </is>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>AnuNatureAwareness.js</t>
+          <t>AnuErrorAndStressLedger.js</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
@@ -38339,12 +38851,12 @@
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
+          <t>MOD-090</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>FrameBudget.js</t>
+          <t>AnuNatureAwareness.js</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
@@ -38376,12 +38888,12 @@
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-092</t>
         </is>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>FrameBudget.js</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
@@ -38413,12 +38925,12 @@
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>MOD-094</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>PipOrthoRingDiskClip.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
@@ -38450,12 +38962,12 @@
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>MOD-096</t>
+          <t>MOD-094</t>
         </is>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>RenderingGovernor.js</t>
+          <t>PipOrthoRingDiskClip.js</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
@@ -38487,12 +38999,12 @@
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>MOD-097</t>
+          <t>MOD-096</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>SceneModelInventory.js</t>
+          <t>RenderingGovernor.js</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
@@ -38524,12 +39036,12 @@
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-097</t>
         </is>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>SceneModelInventory.js</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
@@ -38561,12 +39073,12 @@
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-100</t>
         </is>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>anuEvents.js</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
@@ -38583,7 +39095,7 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
@@ -38598,10 +39110,14 @@
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>window.Orchestrator</t>
-        </is>
-      </c>
-      <c r="F264" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -38631,7 +39147,7 @@
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>window.__isRenderingPip</t>
+          <t>window.Orchestrator</t>
         </is>
       </c>
       <c r="F265" s="5" t="inlineStr"/>
@@ -38664,7 +39180,7 @@
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>window.__mobileTexCap</t>
+          <t>window.__isRenderingPip</t>
         </is>
       </c>
       <c r="F266" s="5" t="inlineStr"/>
@@ -38697,7 +39213,7 @@
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>window.anuOrchestrator</t>
+          <t>window.__mobileTexCap</t>
         </is>
       </c>
       <c r="F267" s="5" t="inlineStr"/>
@@ -38715,7 +39231,7 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
@@ -38730,7 +39246,7 @@
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.MODULE_ACTIVATED</t>
+          <t>window.anuOrchestrator</t>
         </is>
       </c>
       <c r="F268" s="5" t="inlineStr"/>
@@ -38763,7 +39279,7 @@
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.MODULE_DEACTIVATED</t>
+          <t>ANU_EVENTS.MODULE_ACTIVATED</t>
         </is>
       </c>
       <c r="F269" s="5" t="inlineStr"/>
@@ -38796,7 +39312,7 @@
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.ORCHESTRATOR_BENCH_COMPLETE</t>
+          <t>ANU_EVENTS.MODULE_DEACTIVATED</t>
         </is>
       </c>
       <c r="F270" s="5" t="inlineStr"/>
@@ -38814,7 +39330,7 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
@@ -38829,7 +39345,7 @@
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>service:PipOrthoBranchClip</t>
+          <t>ANU_EVENTS.ORCHESTRATOR_BENCH_COMPLETE</t>
         </is>
       </c>
       <c r="F271" s="5" t="inlineStr"/>
@@ -38862,7 +39378,7 @@
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
+          <t>service:PipOrthoBranchClip</t>
         </is>
       </c>
       <c r="F272" s="5" t="inlineStr"/>
@@ -38880,29 +39396,25 @@
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>MOD-060</t>
+          <t>MOD-059</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>js/v2/OrchestratorHud.js</t>
+          <t>js/v2/Orchestrator.js</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>MOD-057</t>
-        </is>
-      </c>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>MapsConfig.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr"/>
       <c r="G273" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -38932,12 +39444,12 @@
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-057</t>
         </is>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>MapsConfig.js</t>
         </is>
       </c>
       <c r="G274" s="5" t="inlineStr">
@@ -38969,12 +39481,12 @@
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>MOD-089</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
-          <t>AnuGovernanceRules.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G275" s="5" t="inlineStr">
@@ -39006,12 +39518,12 @@
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
+          <t>MOD-089</t>
         </is>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>FrameBudget.js</t>
+          <t>AnuGovernanceRules.js</t>
         </is>
       </c>
       <c r="G276" s="5" t="inlineStr">
@@ -39043,12 +39555,12 @@
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>MOD-096</t>
+          <t>MOD-092</t>
         </is>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>RenderingGovernor.js</t>
+          <t>FrameBudget.js</t>
         </is>
       </c>
       <c r="G277" s="5" t="inlineStr">
@@ -39080,12 +39592,12 @@
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-096</t>
         </is>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>RenderingGovernor.js</t>
         </is>
       </c>
       <c r="G278" s="5" t="inlineStr">
@@ -39102,7 +39614,7 @@
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
@@ -39117,10 +39629,14 @@
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>window._v2SyncVillageViewRightStack</t>
-        </is>
-      </c>
-      <c r="F279" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -39150,7 +39666,7 @@
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>window._v4GetPipelineTrace</t>
+          <t>window._v2SyncVillageViewRightStack</t>
         </is>
       </c>
       <c r="F280" s="5" t="inlineStr"/>
@@ -39168,7 +39684,7 @@
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C281" s="5" t="inlineStr">
@@ -39183,7 +39699,7 @@
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>service:WebFontsService</t>
+          <t>window._v4GetPipelineTrace</t>
         </is>
       </c>
       <c r="F281" s="5" t="inlineStr"/>
@@ -39201,29 +39717,25 @@
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>MOD-062</t>
+          <t>MOD-060</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>js/v2/TipiCampfire.js</t>
+          <t>js/v2/OrchestratorHud.js</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
-        </is>
-      </c>
-      <c r="F282" s="5" t="inlineStr">
-        <is>
-          <t>SimulationController.js</t>
-        </is>
-      </c>
+          <t>service:WebFontsService</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="inlineStr"/>
       <c r="G282" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -39238,29 +39750,25 @@
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>MOD-062</t>
+          <t>MOD-060</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>js/v2/TipiCampfire.js</t>
+          <t>js/v2/OrchestratorHud.js</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
-        </is>
-      </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>constants.js</t>
-        </is>
-      </c>
+          <t>Assets/SacredOnes.Logo.160.png</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr"/>
       <c r="G283" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -39280,27 +39788,27 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>MOD-063</t>
+          <t>MOD-062</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Trees.js</t>
+          <t>js/v2/TipiCampfire.js</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>MOD-055</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>Flora.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -39317,22 +39825,22 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>MOD-064</t>
+          <t>MOD-062</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js</t>
+          <t>js/v2/TipiCampfire.js</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G285" s="5" t="inlineStr">
@@ -39354,27 +39862,27 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>MOD-064</t>
+          <t>MOD-063</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js</t>
+          <t>js/v2/Trees.js</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
+          <t>MOD-055</t>
         </is>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>FrameBudget.js</t>
+          <t>Flora.js</t>
         </is>
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -39401,12 +39909,12 @@
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>MOD-106</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>pipCompassMath.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G287" s="5" t="inlineStr">
@@ -39423,7 +39931,7 @@
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>service-register</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
@@ -39438,10 +39946,14 @@
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>service:WebFontsService</t>
-        </is>
-      </c>
-      <c r="F288" s="5" t="inlineStr"/>
+          <t>MOD-092</t>
+        </is>
+      </c>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>FrameBudget.js</t>
+        </is>
+      </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -39456,7 +39968,7 @@
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
@@ -39471,10 +39983,14 @@
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
-        </is>
-      </c>
-      <c r="F289" s="5" t="inlineStr"/>
+          <t>MOD-106</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>pipCompassMath.js</t>
+        </is>
+      </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -39489,7 +40005,7 @@
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>postMessage</t>
+          <t>service-register</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
@@ -39504,7 +40020,7 @@
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>msg:TOGGLE_VIEW_MODE</t>
+          <t>service:WebFontsService</t>
         </is>
       </c>
       <c r="F290" s="5" t="inlineStr"/>
@@ -39522,32 +40038,28 @@
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>MOD-065</t>
+          <t>MOD-064</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UniverseModule.js</t>
+          <t>js/v2/UIModule.js</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>MOD-049</t>
-        </is>
-      </c>
-      <c r="F291" s="5" t="inlineStr">
-        <is>
-          <t>AnuModule.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr"/>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -39559,32 +40071,28 @@
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>postMessage</t>
         </is>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>MOD-067</t>
+          <t>MOD-064</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>js/v2/V2Panel.js</t>
+          <t>js/v2/UIModule.js</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F292" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>msg:TOGGLE_VIEW_MODE</t>
+        </is>
+      </c>
+      <c r="F292" s="5" t="inlineStr"/>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -39601,22 +40109,22 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>MOD-067</t>
+          <t>MOD-065</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>js/v2/V2Panel.js</t>
+          <t>js/v2/UniverseModule.js</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>MOD-066</t>
+          <t>MOD-049</t>
         </is>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>V2IconRenderer.js</t>
+          <t>AnuModule.js</t>
         </is>
       </c>
       <c r="G293" s="5" t="inlineStr">
@@ -39648,12 +40156,12 @@
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G294" s="5" t="inlineStr">
@@ -39685,12 +40193,12 @@
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-066</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>V2IconRenderer.js</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -39707,7 +40215,7 @@
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C296" s="5" t="inlineStr">
@@ -39722,10 +40230,14 @@
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>window.AXE_GLB_BASE64</t>
-        </is>
-      </c>
-      <c r="F296" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -39740,7 +40252,7 @@
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C297" s="5" t="inlineStr">
@@ -39755,10 +40267,14 @@
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>window.THREE</t>
-        </is>
-      </c>
-      <c r="F297" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -39788,7 +40304,7 @@
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>window.icons</t>
+          <t>window.AXE_GLB_BASE64</t>
         </is>
       </c>
       <c r="F298" s="5" t="inlineStr"/>
@@ -39806,7 +40322,7 @@
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C299" s="5" t="inlineStr">
@@ -39821,7 +40337,7 @@
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>service:WebFontsService</t>
+          <t>window.THREE</t>
         </is>
       </c>
       <c r="F299" s="5" t="inlineStr"/>
@@ -39839,7 +40355,7 @@
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C300" s="5" t="inlineStr">
@@ -39854,7 +40370,7 @@
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
+          <t>window.icons</t>
         </is>
       </c>
       <c r="F300" s="5" t="inlineStr"/>
@@ -39872,29 +40388,25 @@
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>MOD-068</t>
+          <t>MOD-067</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>js/v2/VillageBuilder.js</t>
+          <t>js/v2/V2Panel.js</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F301" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>service:WebFontsService</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="inlineStr"/>
       <c r="G301" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -39909,29 +40421,25 @@
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>MOD-068</t>
+          <t>MOD-067</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>js/v2/VillageBuilder.js</t>
+          <t>js/v2/V2Panel.js</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
-        </is>
-      </c>
-      <c r="F302" s="5" t="inlineStr">
-        <is>
-          <t>WorldTerrain.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F302" s="5" t="inlineStr"/>
       <c r="G302" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -39961,12 +40469,12 @@
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -39998,12 +40506,12 @@
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G304" s="5" t="inlineStr">
@@ -40035,12 +40543,12 @@
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -40057,7 +40565,7 @@
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C306" s="5" t="inlineStr">
@@ -40072,10 +40580,14 @@
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
-        </is>
-      </c>
-      <c r="F306" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -40090,7 +40602,7 @@
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C307" s="5" t="inlineStr">
@@ -40105,10 +40617,14 @@
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>Assets/Tipi.yellowbutterfly/tipi.yellowbutterfly.glb</t>
-        </is>
-      </c>
-      <c r="F307" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -40123,29 +40639,25 @@
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>MOD-069</t>
+          <t>MOD-068</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>js/v2/World.js</t>
+          <t>js/v2/VillageBuilder.js</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>MOD-052</t>
-        </is>
-      </c>
-      <c r="F308" s="5" t="inlineStr">
-        <is>
-          <t>ClickToMoveMarker.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F308" s="5" t="inlineStr"/>
       <c r="G308" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -40160,29 +40672,25 @@
       </c>
       <c r="B309" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>MOD-069</t>
+          <t>MOD-068</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>js/v2/World.js</t>
+          <t>js/v2/VillageBuilder.js</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>MOD-057</t>
-        </is>
-      </c>
-      <c r="F309" s="5" t="inlineStr">
-        <is>
-          <t>MapsConfig.js</t>
-        </is>
-      </c>
+          <t>Assets/Tipi.yellowbutterfly/tipi.yellowbutterfly.glb</t>
+        </is>
+      </c>
+      <c r="F309" s="5" t="inlineStr"/>
       <c r="G309" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -40212,12 +40720,12 @@
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-052</t>
         </is>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>ClickToMoveMarker.js</t>
         </is>
       </c>
       <c r="G310" s="5" t="inlineStr">
@@ -40249,12 +40757,12 @@
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>MOD-070</t>
+          <t>MOD-057</t>
         </is>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
-          <t>WorldAvatar.js</t>
+          <t>MapsConfig.js</t>
         </is>
       </c>
       <c r="G311" s="5" t="inlineStr">
@@ -40286,12 +40794,12 @@
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>MOD-071</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
-          <t>WorldCelestial.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G312" s="5" t="inlineStr">
@@ -40323,12 +40831,12 @@
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>MOD-075</t>
+          <t>MOD-070</t>
         </is>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>WorldNatureSpirit.js</t>
+          <t>WorldAvatar.js</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -40360,12 +40868,12 @@
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>MOD-076</t>
+          <t>MOD-071</t>
         </is>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
-          <t>WorldPhysics.js</t>
+          <t>WorldCelestial.js</t>
         </is>
       </c>
       <c r="G314" s="5" t="inlineStr">
@@ -40397,12 +40905,12 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>MOD-077</t>
+          <t>MOD-075</t>
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
-          <t>WorldPlayerController.js</t>
+          <t>WorldNatureSpirit.js</t>
         </is>
       </c>
       <c r="G315" s="5" t="inlineStr">
@@ -40434,12 +40942,12 @@
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>MOD-082</t>
+          <t>MOD-076</t>
         </is>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>WorldStructures.js</t>
+          <t>WorldPhysics.js</t>
         </is>
       </c>
       <c r="G316" s="5" t="inlineStr">
@@ -40471,12 +40979,12 @@
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-077</t>
         </is>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
-          <t>WorldTerrain.js</t>
+          <t>WorldPlayerController.js</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -40508,12 +41016,12 @@
       </c>
       <c r="E318" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-082</t>
         </is>
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>WorldStructures.js</t>
         </is>
       </c>
       <c r="G318" s="5" t="inlineStr">
@@ -40545,12 +41053,12 @@
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G319" s="5" t="inlineStr">
@@ -40582,12 +41090,12 @@
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G320" s="5" t="inlineStr">
@@ -40619,12 +41127,12 @@
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -40641,7 +41149,7 @@
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C322" s="5" t="inlineStr">
@@ -40656,10 +41164,14 @@
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
-          <t>window.WorldPhysics</t>
-        </is>
-      </c>
-      <c r="F322" s="5" t="inlineStr"/>
+          <t>MOD-100</t>
+        </is>
+      </c>
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>anuEvents.js</t>
+        </is>
+      </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -40674,7 +41186,7 @@
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C323" s="5" t="inlineStr">
@@ -40689,10 +41201,14 @@
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>window.WorldPlayer</t>
-        </is>
-      </c>
-      <c r="F323" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -40722,7 +41238,7 @@
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
-          <t>window._terrainHeightCache</t>
+          <t>window.WorldPhysics</t>
         </is>
       </c>
       <c r="F324" s="5" t="inlineStr"/>
@@ -40755,7 +41271,7 @@
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>window._v2StoneAxeInInventory</t>
+          <t>window.WorldPlayer</t>
         </is>
       </c>
       <c r="F325" s="5" t="inlineStr"/>
@@ -40773,7 +41289,7 @@
       </c>
       <c r="B326" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C326" s="5" t="inlineStr">
@@ -40788,7 +41304,7 @@
       </c>
       <c r="E326" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.PLAYER_JUMP</t>
+          <t>window._terrainHeightCache</t>
         </is>
       </c>
       <c r="F326" s="5" t="inlineStr"/>
@@ -40806,7 +41322,7 @@
       </c>
       <c r="B327" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C327" s="5" t="inlineStr">
@@ -40821,7 +41337,7 @@
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.PLAYER_STATE_SAMPLE</t>
+          <t>window._v2StoneAxeInInventory</t>
         </is>
       </c>
       <c r="F327" s="5" t="inlineStr"/>
@@ -40839,7 +41355,7 @@
       </c>
       <c r="B328" s="5" t="inlineStr">
         <is>
-          <t>service-register</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C328" s="5" t="inlineStr">
@@ -40854,7 +41370,7 @@
       </c>
       <c r="E328" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPhysics</t>
+          <t>ANU_EVENTS.PLAYER_JUMP</t>
         </is>
       </c>
       <c r="F328" s="5" t="inlineStr"/>
@@ -40872,7 +41388,7 @@
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>service-register</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C329" s="5" t="inlineStr">
@@ -40887,7 +41403,7 @@
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
+          <t>ANU_EVENTS.PLAYER_STATE_SAMPLE</t>
         </is>
       </c>
       <c r="F329" s="5" t="inlineStr"/>
@@ -40905,7 +41421,7 @@
       </c>
       <c r="B330" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>service-register</t>
         </is>
       </c>
       <c r="C330" s="5" t="inlineStr">
@@ -40920,7 +41436,7 @@
       </c>
       <c r="E330" s="5" t="inlineStr">
         <is>
-          <t>Assets/landscape-scenes/terrain/grass-seamless.png</t>
+          <t>service:WorldPhysics</t>
         </is>
       </c>
       <c r="F330" s="5" t="inlineStr"/>
@@ -40938,29 +41454,25 @@
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-register</t>
         </is>
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>MOD-070</t>
+          <t>MOD-069</t>
         </is>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldAvatar.js</t>
+          <t>js/v2/World.js</t>
         </is>
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
-        </is>
-      </c>
-      <c r="F331" s="5" t="inlineStr">
-        <is>
-          <t>InteractionBus.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F331" s="5" t="inlineStr"/>
       <c r="G331" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -40975,29 +41487,25 @@
       </c>
       <c r="B332" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>MOD-070</t>
+          <t>MOD-069</t>
         </is>
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldAvatar.js</t>
+          <t>js/v2/World.js</t>
         </is>
       </c>
       <c r="E332" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
-        </is>
-      </c>
-      <c r="F332" s="5" t="inlineStr">
-        <is>
-          <t>SimulationController.js</t>
-        </is>
-      </c>
+          <t>Assets/landscape-scenes/terrain/grass-seamless.png</t>
+        </is>
+      </c>
+      <c r="F332" s="5" t="inlineStr"/>
       <c r="G332" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41027,12 +41535,12 @@
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>MOD-099</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F333" s="5" t="inlineStr">
         <is>
-          <t>TravelFloorCircleMaterials.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G333" s="5" t="inlineStr">
@@ -41064,12 +41572,12 @@
       </c>
       <c r="E334" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G334" s="5" t="inlineStr">
@@ -41101,12 +41609,12 @@
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-099</t>
         </is>
       </c>
       <c r="F335" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>TravelFloorCircleMaterials.js</t>
         </is>
       </c>
       <c r="G335" s="5" t="inlineStr">
@@ -41138,12 +41646,12 @@
       </c>
       <c r="E336" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-100</t>
         </is>
       </c>
       <c r="F336" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>anuEvents.js</t>
         </is>
       </c>
       <c r="G336" s="5" t="inlineStr">
@@ -41160,7 +41668,7 @@
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C337" s="5" t="inlineStr">
@@ -41175,10 +41683,14 @@
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.PLAYER_AVATAR_ANIMATION</t>
-        </is>
-      </c>
-      <c r="F337" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F337" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G337" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41193,7 +41705,7 @@
       </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C338" s="5" t="inlineStr">
@@ -41208,10 +41720,14 @@
       </c>
       <c r="E338" s="5" t="inlineStr">
         <is>
-          <t>Assets/Avatar3.glb</t>
-        </is>
-      </c>
-      <c r="F338" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F338" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G338" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41226,7 +41742,7 @@
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C339" s="5" t="inlineStr">
@@ -41241,7 +41757,7 @@
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>Assets/npc/Avatar-New.glb</t>
+          <t>ANU_EVENTS.PLAYER_AVATAR_ANIMATION</t>
         </is>
       </c>
       <c r="F339" s="5" t="inlineStr"/>
@@ -41259,29 +41775,25 @@
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>MOD-071</t>
+          <t>MOD-070</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldCelestial.js</t>
+          <t>js/v2/WorldAvatar.js</t>
         </is>
       </c>
       <c r="E340" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
-        </is>
-      </c>
-      <c r="F340" s="5" t="inlineStr">
-        <is>
-          <t>InteractionBus.js</t>
-        </is>
-      </c>
+          <t>Assets/Avatar3.glb</t>
+        </is>
+      </c>
+      <c r="F340" s="5" t="inlineStr"/>
       <c r="G340" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41296,29 +41808,25 @@
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>MOD-071</t>
+          <t>MOD-070</t>
         </is>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldCelestial.js</t>
+          <t>js/v2/WorldAvatar.js</t>
         </is>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
-        </is>
-      </c>
-      <c r="F341" s="5" t="inlineStr">
-        <is>
-          <t>anuEvents.js</t>
-        </is>
-      </c>
+          <t>Assets/npc/Avatar-New.glb</t>
+        </is>
+      </c>
+      <c r="F341" s="5" t="inlineStr"/>
       <c r="G341" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41348,12 +41856,12 @@
       </c>
       <c r="E342" s="5" t="inlineStr">
         <is>
-          <t>MOD-105</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F342" s="5" t="inlineStr">
         <is>
-          <t>lunarPhase.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G342" s="5" t="inlineStr">
@@ -41370,7 +41878,7 @@
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>anu-event-subscribe</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C343" s="5" t="inlineStr">
@@ -41385,10 +41893,14 @@
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.LUNAR_PHASE</t>
-        </is>
-      </c>
-      <c r="F343" s="5" t="inlineStr"/>
+          <t>MOD-100</t>
+        </is>
+      </c>
+      <c r="F343" s="5" t="inlineStr">
+        <is>
+          <t>anuEvents.js</t>
+        </is>
+      </c>
       <c r="G343" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41403,7 +41915,7 @@
       </c>
       <c r="B344" s="5" t="inlineStr">
         <is>
-          <t>anu-event-subscribe</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C344" s="5" t="inlineStr">
@@ -41418,10 +41930,14 @@
       </c>
       <c r="E344" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.SEASON_CHANGE</t>
-        </is>
-      </c>
-      <c r="F344" s="5" t="inlineStr"/>
+          <t>MOD-105</t>
+        </is>
+      </c>
+      <c r="F344" s="5" t="inlineStr">
+        <is>
+          <t>lunarPhase.js</t>
+        </is>
+      </c>
       <c r="G344" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41436,29 +41952,25 @@
       </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-subscribe</t>
         </is>
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>MOD-072</t>
+          <t>MOD-071</t>
         </is>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldDistantPeaks.js</t>
+          <t>js/v2/WorldCelestial.js</t>
         </is>
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
-        </is>
-      </c>
-      <c r="F345" s="5" t="inlineStr">
-        <is>
-          <t>SimulationController.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.LUNAR_PHASE</t>
+        </is>
+      </c>
+      <c r="F345" s="5" t="inlineStr"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41473,29 +41985,25 @@
       </c>
       <c r="B346" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-subscribe</t>
         </is>
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>MOD-073</t>
+          <t>MOD-071</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldFishing.js</t>
+          <t>js/v2/WorldCelestial.js</t>
         </is>
       </c>
       <c r="E346" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F346" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.SEASON_CHANGE</t>
+        </is>
+      </c>
+      <c r="F346" s="5" t="inlineStr"/>
       <c r="G346" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41515,22 +42023,22 @@
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>MOD-073</t>
+          <t>MOD-072</t>
         </is>
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldFishing.js</t>
+          <t>js/v2/WorldDistantPeaks.js</t>
         </is>
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F347" s="5" t="inlineStr">
         <is>
-          <t>WorldTerrain.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -41562,12 +42070,12 @@
       </c>
       <c r="E348" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F348" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G348" s="5" t="inlineStr">
@@ -41599,12 +42107,12 @@
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F349" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
@@ -41621,7 +42129,7 @@
       </c>
       <c r="B350" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C350" s="5" t="inlineStr">
@@ -41636,10 +42144,14 @@
       </c>
       <c r="E350" s="5" t="inlineStr">
         <is>
-          <t>window._v2FishingActive</t>
-        </is>
-      </c>
-      <c r="F350" s="5" t="inlineStr"/>
+          <t>MOD-098</t>
+        </is>
+      </c>
+      <c r="F350" s="5" t="inlineStr">
+        <is>
+          <t>SimulationController.js</t>
+        </is>
+      </c>
       <c r="G350" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41654,7 +42166,7 @@
       </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C351" s="5" t="inlineStr">
@@ -41669,10 +42181,14 @@
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>window._v2FishingCameraOverride</t>
-        </is>
-      </c>
-      <c r="F351" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F351" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -41702,7 +42218,7 @@
       </c>
       <c r="E352" s="5" t="inlineStr">
         <is>
-          <t>window._v2FishingCameraReleased</t>
+          <t>window._v2FishingActive</t>
         </is>
       </c>
       <c r="F352" s="5" t="inlineStr"/>
@@ -41735,7 +42251,7 @@
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>window._v2FishingEngaged</t>
+          <t>window._v2FishingCameraOverride</t>
         </is>
       </c>
       <c r="F353" s="5" t="inlineStr"/>
@@ -41768,7 +42284,7 @@
       </c>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>window._v2FishingPoint</t>
+          <t>window._v2FishingCameraReleased</t>
         </is>
       </c>
       <c r="F354" s="5" t="inlineStr"/>
@@ -41801,7 +42317,7 @@
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>window._v2PoolFishTemplate</t>
+          <t>window._v2FishingEngaged</t>
         </is>
       </c>
       <c r="F355" s="5" t="inlineStr"/>
@@ -41819,7 +42335,7 @@
       </c>
       <c r="B356" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C356" s="5" t="inlineStr">
@@ -41834,7 +42350,7 @@
       </c>
       <c r="E356" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
+          <t>window._v2FishingPoint</t>
         </is>
       </c>
       <c r="F356" s="5" t="inlineStr"/>
@@ -41852,32 +42368,28 @@
       </c>
       <c r="B357" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C357" s="5" t="inlineStr">
         <is>
-          <t>MOD-074</t>
+          <t>MOD-073</t>
         </is>
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldMossyRock.js</t>
+          <t>js/v2/WorldFishing.js</t>
         </is>
       </c>
       <c r="E357" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
-        </is>
-      </c>
-      <c r="F357" s="5" t="inlineStr">
-        <is>
-          <t>WorldTerrain.js</t>
-        </is>
-      </c>
+          <t>window._v2PoolFishTemplate</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="inlineStr"/>
       <c r="G357" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -41889,32 +42401,28 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C358" s="5" t="inlineStr">
         <is>
-          <t>MOD-074</t>
+          <t>MOD-073</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldMossyRock.js</t>
+          <t>js/v2/WorldFishing.js</t>
         </is>
       </c>
       <c r="E358" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
-        </is>
-      </c>
-      <c r="F358" s="5" t="inlineStr">
-        <is>
-          <t>SimulationController.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F358" s="5" t="inlineStr"/>
       <c r="G358" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -41941,12 +42449,12 @@
       </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F359" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G359" s="5" t="inlineStr">
@@ -41963,7 +42471,7 @@
       </c>
       <c r="B360" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C360" s="5" t="inlineStr">
@@ -41978,10 +42486,14 @@
       </c>
       <c r="E360" s="5" t="inlineStr">
         <is>
-          <t>Assets/landscape-scenes/terrain/rock.mossy.glb</t>
-        </is>
-      </c>
-      <c r="F360" s="5" t="inlineStr"/>
+          <t>MOD-098</t>
+        </is>
+      </c>
+      <c r="F360" s="5" t="inlineStr">
+        <is>
+          <t>SimulationController.js</t>
+        </is>
+      </c>
       <c r="G360" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -42001,27 +42513,27 @@
       </c>
       <c r="C361" s="5" t="inlineStr">
         <is>
-          <t>MOD-075</t>
+          <t>MOD-074</t>
         </is>
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldNatureSpirit.js</t>
+          <t>js/v2/WorldMossyRock.js</t>
         </is>
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-104</t>
         </is>
       </c>
       <c r="F361" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>gltfLoaderSetup.js</t>
         </is>
       </c>
       <c r="G361" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -42033,32 +42545,28 @@
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
-          <t>MOD-075</t>
+          <t>MOD-074</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldNatureSpirit.js</t>
+          <t>js/v2/WorldMossyRock.js</t>
         </is>
       </c>
       <c r="E362" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
-        </is>
-      </c>
-      <c r="F362" s="5" t="inlineStr">
-        <is>
-          <t>SimulationController.js</t>
-        </is>
-      </c>
+          <t>Assets/landscape-scenes/terrain/rock.mossy.glb</t>
+        </is>
+      </c>
+      <c r="F362" s="5" t="inlineStr"/>
       <c r="G362" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -42085,12 +42593,12 @@
       </c>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F363" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G363" s="5" t="inlineStr">
@@ -42122,12 +42630,12 @@
       </c>
       <c r="E364" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F364" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G364" s="5" t="inlineStr">
@@ -42159,12 +42667,12 @@
       </c>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-100</t>
         </is>
       </c>
       <c r="F365" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>anuEvents.js</t>
         </is>
       </c>
       <c r="G365" s="5" t="inlineStr">
@@ -42181,7 +42689,7 @@
       </c>
       <c r="B366" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C366" s="5" t="inlineStr">
@@ -42196,10 +42704,14 @@
       </c>
       <c r="E366" s="5" t="inlineStr">
         <is>
-          <t>window.natureSpiritSystem</t>
-        </is>
-      </c>
-      <c r="F366" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F366" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G366" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42214,7 +42726,7 @@
       </c>
       <c r="B367" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C367" s="5" t="inlineStr">
@@ -42229,10 +42741,14 @@
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.NPC_ENTITY</t>
-        </is>
-      </c>
-      <c r="F367" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F367" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G367" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42247,7 +42763,7 @@
       </c>
       <c r="B368" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C368" s="5" t="inlineStr">
@@ -42262,7 +42778,7 @@
       </c>
       <c r="E368" s="5" t="inlineStr">
         <is>
-          <t>Assets/animated.stag.glb</t>
+          <t>window.natureSpiritSystem</t>
         </is>
       </c>
       <c r="F368" s="5" t="inlineStr"/>
@@ -42280,29 +42796,25 @@
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C369" s="5" t="inlineStr">
         <is>
-          <t>MOD-076</t>
+          <t>MOD-075</t>
         </is>
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldPhysics.js</t>
+          <t>js/v2/WorldNatureSpirit.js</t>
         </is>
       </c>
       <c r="E369" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
-        </is>
-      </c>
-      <c r="F369" s="5" t="inlineStr">
-        <is>
-          <t>constants.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.NPC_ENTITY</t>
+        </is>
+      </c>
+      <c r="F369" s="5" t="inlineStr"/>
       <c r="G369" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42317,22 +42829,22 @@
       </c>
       <c r="B370" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C370" s="5" t="inlineStr">
         <is>
-          <t>MOD-077</t>
+          <t>MOD-075</t>
         </is>
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldPlayerController.js</t>
+          <t>js/v2/WorldNatureSpirit.js</t>
         </is>
       </c>
       <c r="E370" s="5" t="inlineStr">
         <is>
-          <t>window._v2InputSuppressed</t>
+          <t>Assets/animated.stag.glb</t>
         </is>
       </c>
       <c r="F370" s="5" t="inlineStr"/>
@@ -42350,25 +42862,29 @@
       </c>
       <c r="B371" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
-          <t>MOD-077</t>
+          <t>MOD-076</t>
         </is>
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldPlayerController.js</t>
+          <t>js/v2/WorldPhysics.js</t>
         </is>
       </c>
       <c r="E371" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.PLAYER_KEY_EDGE</t>
-        </is>
-      </c>
-      <c r="F371" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F371" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G371" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42383,29 +42899,25 @@
       </c>
       <c r="B372" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C372" s="5" t="inlineStr">
         <is>
-          <t>MOD-078</t>
+          <t>MOD-077</t>
         </is>
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldPool2.js</t>
+          <t>js/v2/WorldPlayerController.js</t>
         </is>
       </c>
       <c r="E372" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F372" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>window._v2InputSuppressed</t>
+        </is>
+      </c>
+      <c r="F372" s="5" t="inlineStr"/>
       <c r="G372" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42420,29 +42932,25 @@
       </c>
       <c r="B373" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C373" s="5" t="inlineStr">
         <is>
-          <t>MOD-078</t>
+          <t>MOD-077</t>
         </is>
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldPool2.js</t>
+          <t>js/v2/WorldPlayerController.js</t>
         </is>
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>MOD-074</t>
-        </is>
-      </c>
-      <c r="F373" s="5" t="inlineStr">
-        <is>
-          <t>WorldMossyRock.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.PLAYER_KEY_EDGE</t>
+        </is>
+      </c>
+      <c r="F373" s="5" t="inlineStr"/>
       <c r="G373" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42472,12 +42980,12 @@
       </c>
       <c r="E374" s="5" t="inlineStr">
         <is>
-          <t>MOD-076</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F374" s="5" t="inlineStr">
         <is>
-          <t>WorldPhysics.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G374" s="5" t="inlineStr">
@@ -42509,12 +43017,12 @@
       </c>
       <c r="E375" s="5" t="inlineStr">
         <is>
-          <t>MOD-082</t>
+          <t>MOD-074</t>
         </is>
       </c>
       <c r="F375" s="5" t="inlineStr">
         <is>
-          <t>WorldStructures.js</t>
+          <t>WorldMossyRock.js</t>
         </is>
       </c>
       <c r="G375" s="5" t="inlineStr">
@@ -42546,12 +43054,12 @@
       </c>
       <c r="E376" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-076</t>
         </is>
       </c>
       <c r="F376" s="5" t="inlineStr">
         <is>
-          <t>WorldTerrain.js</t>
+          <t>WorldPhysics.js</t>
         </is>
       </c>
       <c r="G376" s="5" t="inlineStr">
@@ -42583,12 +43091,12 @@
       </c>
       <c r="E377" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-082</t>
         </is>
       </c>
       <c r="F377" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>WorldStructures.js</t>
         </is>
       </c>
       <c r="G377" s="5" t="inlineStr">
@@ -42620,12 +43128,12 @@
       </c>
       <c r="E378" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F378" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G378" s="5" t="inlineStr">
@@ -42657,12 +43165,12 @@
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F379" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G379" s="5" t="inlineStr">
@@ -42679,7 +43187,7 @@
       </c>
       <c r="B380" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C380" s="5" t="inlineStr">
@@ -42694,10 +43202,14 @@
       </c>
       <c r="E380" s="5" t="inlineStr">
         <is>
-          <t>window._v2FishingPoint</t>
-        </is>
-      </c>
-      <c r="F380" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F380" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42712,7 +43224,7 @@
       </c>
       <c r="B381" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C381" s="5" t="inlineStr">
@@ -42727,10 +43239,14 @@
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>window._v2PoolFish</t>
-        </is>
-      </c>
-      <c r="F381" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F381" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G381" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42760,7 +43276,7 @@
       </c>
       <c r="E382" s="5" t="inlineStr">
         <is>
-          <t>window._v2PoolFishTemplate</t>
+          <t>window._v2FishingPoint</t>
         </is>
       </c>
       <c r="F382" s="5" t="inlineStr"/>
@@ -42778,7 +43294,7 @@
       </c>
       <c r="B383" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C383" s="5" t="inlineStr">
@@ -42793,7 +43309,7 @@
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>service:AnuNatureAwareness</t>
+          <t>window._v2PoolFish</t>
         </is>
       </c>
       <c r="F383" s="5" t="inlineStr"/>
@@ -42811,7 +43327,7 @@
       </c>
       <c r="B384" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C384" s="5" t="inlineStr">
@@ -42826,7 +43342,7 @@
       </c>
       <c r="E384" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPhysics</t>
+          <t>window._v2PoolFishTemplate</t>
         </is>
       </c>
       <c r="F384" s="5" t="inlineStr"/>
@@ -42844,7 +43360,7 @@
       </c>
       <c r="B385" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C385" s="5" t="inlineStr">
@@ -42859,7 +43375,7 @@
       </c>
       <c r="E385" s="5" t="inlineStr">
         <is>
-          <t>Assets/fauna/animal-pack/deer.glb</t>
+          <t>service:AnuNatureAwareness</t>
         </is>
       </c>
       <c r="F385" s="5" t="inlineStr"/>
@@ -42877,29 +43393,25 @@
       </c>
       <c r="B386" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C386" s="5" t="inlineStr">
         <is>
-          <t>MOD-079</t>
+          <t>MOD-078</t>
         </is>
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldQuietGlade.js</t>
+          <t>js/v2/WorldPool2.js</t>
         </is>
       </c>
       <c r="E386" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
-        </is>
-      </c>
-      <c r="F386" s="5" t="inlineStr">
-        <is>
-          <t>WorldTerrain.js</t>
-        </is>
-      </c>
+          <t>service:WorldPhysics</t>
+        </is>
+      </c>
+      <c r="F386" s="5" t="inlineStr"/>
       <c r="G386" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42914,29 +43426,25 @@
       </c>
       <c r="B387" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C387" s="5" t="inlineStr">
         <is>
-          <t>MOD-079</t>
+          <t>MOD-078</t>
         </is>
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldQuietGlade.js</t>
+          <t>js/v2/WorldPool2.js</t>
         </is>
       </c>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
-        </is>
-      </c>
-      <c r="F387" s="5" t="inlineStr">
-        <is>
-          <t>SimulationController.js</t>
-        </is>
-      </c>
+          <t>Assets/fauna/animal-pack/deer.glb</t>
+        </is>
+      </c>
+      <c r="F387" s="5" t="inlineStr"/>
       <c r="G387" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -42966,12 +43474,12 @@
       </c>
       <c r="E388" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F388" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G388" s="5" t="inlineStr">
@@ -42993,12 +43501,12 @@
       </c>
       <c r="C389" s="5" t="inlineStr">
         <is>
-          <t>MOD-080</t>
+          <t>MOD-079</t>
         </is>
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldSacredPlatform.js</t>
+          <t>js/v2/WorldQuietGlade.js</t>
         </is>
       </c>
       <c r="E389" s="5" t="inlineStr">
@@ -43013,7 +43521,7 @@
       </c>
       <c r="G389" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -43030,12 +43538,12 @@
       </c>
       <c r="C390" s="5" t="inlineStr">
         <is>
-          <t>MOD-080</t>
+          <t>MOD-079</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldSacredPlatform.js</t>
+          <t>js/v2/WorldQuietGlade.js</t>
         </is>
       </c>
       <c r="E390" s="5" t="inlineStr">
@@ -43050,7 +43558,7 @@
       </c>
       <c r="G390" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -43067,27 +43575,27 @@
       </c>
       <c r="C391" s="5" t="inlineStr">
         <is>
-          <t>MOD-081</t>
+          <t>MOD-080</t>
         </is>
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldSkyFlock.js</t>
+          <t>js/v2/WorldSacredPlatform.js</t>
         </is>
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F391" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G391" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -43104,27 +43612,27 @@
       </c>
       <c r="C392" s="5" t="inlineStr">
         <is>
-          <t>MOD-081</t>
+          <t>MOD-080</t>
         </is>
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldSkyFlock.js</t>
+          <t>js/v2/WorldSacredPlatform.js</t>
         </is>
       </c>
       <c r="E392" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F392" s="5" t="inlineStr">
         <is>
-          <t>WorldTerrain.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G392" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -43151,12 +43659,12 @@
       </c>
       <c r="E393" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F393" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G393" s="5" t="inlineStr">
@@ -43173,7 +43681,7 @@
       </c>
       <c r="B394" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C394" s="5" t="inlineStr">
@@ -43188,10 +43696,14 @@
       </c>
       <c r="E394" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPlayer</t>
-        </is>
-      </c>
-      <c r="F394" s="5" t="inlineStr"/>
+          <t>MOD-083</t>
+        </is>
+      </c>
+      <c r="F394" s="5" t="inlineStr">
+        <is>
+          <t>WorldTerrain.js</t>
+        </is>
+      </c>
       <c r="G394" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -43211,27 +43723,27 @@
       </c>
       <c r="C395" s="5" t="inlineStr">
         <is>
-          <t>MOD-082</t>
+          <t>MOD-081</t>
         </is>
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldStructures.js</t>
+          <t>js/v2/WorldSkyFlock.js</t>
         </is>
       </c>
       <c r="E395" s="5" t="inlineStr">
         <is>
-          <t>MOD-058</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F395" s="5" t="inlineStr">
         <is>
-          <t>NPCBehaviour.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G395" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -43243,32 +43755,28 @@
       </c>
       <c r="B396" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C396" s="5" t="inlineStr">
         <is>
-          <t>MOD-082</t>
+          <t>MOD-081</t>
         </is>
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldStructures.js</t>
+          <t>js/v2/WorldSkyFlock.js</t>
         </is>
       </c>
       <c r="E396" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
-        </is>
-      </c>
-      <c r="F396" s="5" t="inlineStr">
-        <is>
-          <t>RuntimeServices.js</t>
-        </is>
-      </c>
+          <t>service:WorldPlayer</t>
+        </is>
+      </c>
+      <c r="F396" s="5" t="inlineStr"/>
       <c r="G396" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -43295,12 +43803,12 @@
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>MOD-062</t>
+          <t>MOD-058</t>
         </is>
       </c>
       <c r="F397" s="5" t="inlineStr">
         <is>
-          <t>TipiCampfire.js</t>
+          <t>NPCBehaviour.js</t>
         </is>
       </c>
       <c r="G397" s="5" t="inlineStr">
@@ -43332,12 +43840,12 @@
       </c>
       <c r="E398" s="5" t="inlineStr">
         <is>
-          <t>MOD-074</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F398" s="5" t="inlineStr">
         <is>
-          <t>WorldMossyRock.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G398" s="5" t="inlineStr">
@@ -43369,12 +43877,12 @@
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>MOD-080</t>
+          <t>MOD-062</t>
         </is>
       </c>
       <c r="F399" s="5" t="inlineStr">
         <is>
-          <t>WorldSacredPlatform.js</t>
+          <t>TipiCampfire.js</t>
         </is>
       </c>
       <c r="G399" s="5" t="inlineStr">
@@ -43406,12 +43914,12 @@
       </c>
       <c r="E400" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-074</t>
         </is>
       </c>
       <c r="F400" s="5" t="inlineStr">
         <is>
-          <t>WorldTerrain.js</t>
+          <t>WorldMossyRock.js</t>
         </is>
       </c>
       <c r="G400" s="5" t="inlineStr">
@@ -43443,12 +43951,12 @@
       </c>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>MOD-084</t>
+          <t>MOD-080</t>
         </is>
       </c>
       <c r="F401" s="5" t="inlineStr">
         <is>
-          <t>WorldTipiJournalBalloon.js</t>
+          <t>WorldSacredPlatform.js</t>
         </is>
       </c>
       <c r="G401" s="5" t="inlineStr">
@@ -43480,12 +43988,12 @@
       </c>
       <c r="E402" s="5" t="inlineStr">
         <is>
-          <t>MOD-094</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F402" s="5" t="inlineStr">
         <is>
-          <t>PipOrthoRingDiskClip.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G402" s="5" t="inlineStr">
@@ -43517,12 +44025,12 @@
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-084</t>
         </is>
       </c>
       <c r="F403" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>WorldTipiJournalBalloon.js</t>
         </is>
       </c>
       <c r="G403" s="5" t="inlineStr">
@@ -43554,12 +44062,12 @@
       </c>
       <c r="E404" s="5" t="inlineStr">
         <is>
-          <t>MOD-099</t>
+          <t>MOD-094</t>
         </is>
       </c>
       <c r="F404" s="5" t="inlineStr">
         <is>
-          <t>TravelFloorCircleMaterials.js</t>
+          <t>PipOrthoRingDiskClip.js</t>
         </is>
       </c>
       <c r="G404" s="5" t="inlineStr">
@@ -43591,12 +44099,12 @@
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F405" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G405" s="5" t="inlineStr">
@@ -43628,12 +44136,12 @@
       </c>
       <c r="E406" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-099</t>
         </is>
       </c>
       <c r="F406" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>TravelFloorCircleMaterials.js</t>
         </is>
       </c>
       <c r="G406" s="5" t="inlineStr">
@@ -43650,7 +44158,7 @@
       </c>
       <c r="B407" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C407" s="5" t="inlineStr">
@@ -43665,10 +44173,14 @@
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>window._tipiPlatformY</t>
-        </is>
-      </c>
-      <c r="F407" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F407" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G407" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -43683,7 +44195,7 @@
       </c>
       <c r="B408" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C408" s="5" t="inlineStr">
@@ -43698,10 +44210,14 @@
       </c>
       <c r="E408" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPhysics</t>
-        </is>
-      </c>
-      <c r="F408" s="5" t="inlineStr"/>
+          <t>MOD-104</t>
+        </is>
+      </c>
+      <c r="F408" s="5" t="inlineStr">
+        <is>
+          <t>gltfLoaderSetup.js</t>
+        </is>
+      </c>
       <c r="G408" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -43716,7 +44232,7 @@
       </c>
       <c r="B409" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C409" s="5" t="inlineStr">
@@ -43731,7 +44247,7 @@
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>Assets/NPC.BHG.glb</t>
+          <t>window._tipiPlatformY</t>
         </is>
       </c>
       <c r="F409" s="5" t="inlineStr"/>
@@ -43749,7 +44265,7 @@
       </c>
       <c r="B410" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C410" s="5" t="inlineStr">
@@ -43764,7 +44280,7 @@
       </c>
       <c r="E410" s="5" t="inlineStr">
         <is>
-          <t>Assets/NPC.YB.glb</t>
+          <t>service:WorldPhysics</t>
         </is>
       </c>
       <c r="F410" s="5" t="inlineStr"/>
@@ -43797,7 +44313,7 @@
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>Assets/Tipi.yellowbutterfly/tipi.yellowbutterfly.glb</t>
+          <t>Assets/NPC.BHG.glb</t>
         </is>
       </c>
       <c r="F411" s="5" t="inlineStr"/>
@@ -43830,7 +44346,7 @@
       </c>
       <c r="E412" s="5" t="inlineStr">
         <is>
-          <t>Assets/axe.glb</t>
+          <t>Assets/NPC.YB.glb</t>
         </is>
       </c>
       <c r="F412" s="5" t="inlineStr"/>
@@ -43848,29 +44364,25 @@
       </c>
       <c r="B413" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C413" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-082</t>
         </is>
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldTerrain.js</t>
+          <t>js/v2/WorldStructures.js</t>
         </is>
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>MOD-057</t>
-        </is>
-      </c>
-      <c r="F413" s="5" t="inlineStr">
-        <is>
-          <t>MapsConfig.js</t>
-        </is>
-      </c>
+          <t>Assets/Tipi.yellowbutterfly/tipi.yellowbutterfly.glb</t>
+        </is>
+      </c>
+      <c r="F413" s="5" t="inlineStr"/>
       <c r="G413" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -43885,29 +44397,25 @@
       </c>
       <c r="B414" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C414" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-082</t>
         </is>
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldTerrain.js</t>
+          <t>js/v2/WorldStructures.js</t>
         </is>
       </c>
       <c r="E414" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
-        </is>
-      </c>
-      <c r="F414" s="5" t="inlineStr">
-        <is>
-          <t>constants.js</t>
-        </is>
-      </c>
+          <t>Assets/axe.glb</t>
+        </is>
+      </c>
+      <c r="F414" s="5" t="inlineStr"/>
       <c r="G414" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -43927,22 +44435,22 @@
       </c>
       <c r="C415" s="5" t="inlineStr">
         <is>
-          <t>MOD-084</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldTipiJournalBalloon.js</t>
+          <t>js/v2/WorldTerrain.js</t>
         </is>
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-057</t>
         </is>
       </c>
       <c r="F415" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>MapsConfig.js</t>
         </is>
       </c>
       <c r="G415" s="5" t="inlineStr">
@@ -43964,27 +44472,27 @@
       </c>
       <c r="C416" s="5" t="inlineStr">
         <is>
-          <t>MOD-085</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldTraderJosh.js</t>
+          <t>js/v2/WorldTerrain.js</t>
         </is>
       </c>
       <c r="E416" s="5" t="inlineStr">
         <is>
-          <t>MOD-083</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F416" s="5" t="inlineStr">
         <is>
-          <t>WorldTerrain.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G416" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -44001,12 +44509,12 @@
       </c>
       <c r="C417" s="5" t="inlineStr">
         <is>
-          <t>MOD-085</t>
+          <t>MOD-084</t>
         </is>
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>js/v2/WorldTraderJosh.js</t>
+          <t>js/v2/WorldTipiJournalBalloon.js</t>
         </is>
       </c>
       <c r="E417" s="5" t="inlineStr">
@@ -44021,7 +44529,7 @@
       </c>
       <c r="G417" s="5" t="inlineStr">
         <is>
-          <t>Legacy/unused</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -44048,12 +44556,12 @@
       </c>
       <c r="E418" s="5" t="inlineStr">
         <is>
-          <t>MOD-104</t>
+          <t>MOD-083</t>
         </is>
       </c>
       <c r="F418" s="5" t="inlineStr">
         <is>
-          <t>gltfLoaderSetup.js</t>
+          <t>WorldTerrain.js</t>
         </is>
       </c>
       <c r="G418" s="5" t="inlineStr">
@@ -44070,7 +44578,7 @@
       </c>
       <c r="B419" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C419" s="5" t="inlineStr">
@@ -44085,10 +44593,14 @@
       </c>
       <c r="E419" s="5" t="inlineStr">
         <is>
-          <t>Assets/TraderJosh3d.glb</t>
-        </is>
-      </c>
-      <c r="F419" s="5" t="inlineStr"/>
+          <t>MOD-098</t>
+        </is>
+      </c>
+      <c r="F419" s="5" t="inlineStr">
+        <is>
+          <t>SimulationController.js</t>
+        </is>
+      </c>
       <c r="G419" s="5" t="inlineStr">
         <is>
           <t>Legacy/unused</t>
@@ -44108,27 +44620,27 @@
       </c>
       <c r="C420" s="5" t="inlineStr">
         <is>
-          <t>MOD-086</t>
+          <t>MOD-085</t>
         </is>
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AdaptiveRenderPolicy.js</t>
+          <t>js/v2/WorldTraderJosh.js</t>
         </is>
       </c>
       <c r="E420" s="5" t="inlineStr">
         <is>
-          <t>MOD-096</t>
+          <t>MOD-104</t>
         </is>
       </c>
       <c r="F420" s="5" t="inlineStr">
         <is>
-          <t>RenderingGovernor.js</t>
+          <t>gltfLoaderSetup.js</t>
         </is>
       </c>
       <c r="G420" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -44140,32 +44652,28 @@
       </c>
       <c r="B421" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C421" s="5" t="inlineStr">
         <is>
-          <t>MOD-086</t>
+          <t>MOD-085</t>
         </is>
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AdaptiveRenderPolicy.js</t>
+          <t>js/v2/WorldTraderJosh.js</t>
         </is>
       </c>
       <c r="E421" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
-        </is>
-      </c>
-      <c r="F421" s="5" t="inlineStr">
-        <is>
-          <t>constants.js</t>
-        </is>
-      </c>
+          <t>Assets/TraderJosh3d.glb</t>
+        </is>
+      </c>
+      <c r="F421" s="5" t="inlineStr"/>
       <c r="G421" s="5" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Legacy/unused</t>
         </is>
       </c>
     </row>
@@ -44182,22 +44690,22 @@
       </c>
       <c r="C422" s="5" t="inlineStr">
         <is>
-          <t>MOD-087</t>
+          <t>MOD-086</t>
         </is>
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuErrorAndStressLedger.js</t>
+          <t>js/v2/anu/AdaptiveRenderPolicy.js</t>
         </is>
       </c>
       <c r="E422" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
+          <t>MOD-096</t>
         </is>
       </c>
       <c r="F422" s="5" t="inlineStr">
         <is>
-          <t>FrameBudget.js</t>
+          <t>RenderingGovernor.js</t>
         </is>
       </c>
       <c r="G422" s="5" t="inlineStr">
@@ -44219,22 +44727,22 @@
       </c>
       <c r="C423" s="5" t="inlineStr">
         <is>
-          <t>MOD-087</t>
+          <t>MOD-086</t>
         </is>
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuErrorAndStressLedger.js</t>
+          <t>js/v2/anu/AdaptiveRenderPolicy.js</t>
         </is>
       </c>
       <c r="E423" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F423" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G423" s="5" t="inlineStr">
@@ -44266,12 +44774,12 @@
       </c>
       <c r="E424" s="5" t="inlineStr">
         <is>
-          <t>MOD-096</t>
+          <t>MOD-092</t>
         </is>
       </c>
       <c r="F424" s="5" t="inlineStr">
         <is>
-          <t>RenderingGovernor.js</t>
+          <t>FrameBudget.js</t>
         </is>
       </c>
       <c r="G424" s="5" t="inlineStr">
@@ -44303,12 +44811,12 @@
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F425" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G425" s="5" t="inlineStr">
@@ -44340,12 +44848,12 @@
       </c>
       <c r="E426" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-096</t>
         </is>
       </c>
       <c r="F426" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>RenderingGovernor.js</t>
         </is>
       </c>
       <c r="G426" s="5" t="inlineStr">
@@ -44362,7 +44870,7 @@
       </c>
       <c r="B427" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C427" s="5" t="inlineStr">
@@ -44377,10 +44885,14 @@
       </c>
       <c r="E427" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.MODULE_LOAD_ERROR</t>
-        </is>
-      </c>
-      <c r="F427" s="5" t="inlineStr"/>
+          <t>MOD-100</t>
+        </is>
+      </c>
+      <c r="F427" s="5" t="inlineStr">
+        <is>
+          <t>anuEvents.js</t>
+        </is>
+      </c>
       <c r="G427" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44395,7 +44907,7 @@
       </c>
       <c r="B428" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C428" s="5" t="inlineStr">
@@ -44410,10 +44922,14 @@
       </c>
       <c r="E428" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.ORCHESTRATOR_LOOP_ERROR</t>
-        </is>
-      </c>
-      <c r="F428" s="5" t="inlineStr"/>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="F428" s="5" t="inlineStr">
+        <is>
+          <t>constants.js</t>
+        </is>
+      </c>
       <c r="G428" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44443,7 +44959,7 @@
       </c>
       <c r="E429" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.PIPELINE_STRESS_LEVEL</t>
+          <t>ANU_EVENTS.MODULE_LOAD_ERROR</t>
         </is>
       </c>
       <c r="F429" s="5" t="inlineStr"/>
@@ -44461,29 +44977,25 @@
       </c>
       <c r="B430" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C430" s="5" t="inlineStr">
         <is>
-          <t>MOD-088</t>
+          <t>MOD-087</t>
         </is>
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuFuzzyPipelineSensor.js</t>
+          <t>js/v2/anu/AnuErrorAndStressLedger.js</t>
         </is>
       </c>
       <c r="E430" s="5" t="inlineStr">
         <is>
-          <t>MOD-087</t>
-        </is>
-      </c>
-      <c r="F430" s="5" t="inlineStr">
-        <is>
-          <t>AnuErrorAndStressLedger.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.ORCHESTRATOR_LOOP_ERROR</t>
+        </is>
+      </c>
+      <c r="F430" s="5" t="inlineStr"/>
       <c r="G430" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44498,29 +45010,25 @@
       </c>
       <c r="B431" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C431" s="5" t="inlineStr">
         <is>
-          <t>MOD-088</t>
+          <t>MOD-087</t>
         </is>
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuFuzzyPipelineSensor.js</t>
+          <t>js/v2/anu/AnuErrorAndStressLedger.js</t>
         </is>
       </c>
       <c r="E431" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
-        </is>
-      </c>
-      <c r="F431" s="5" t="inlineStr">
-        <is>
-          <t>FrameBudget.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.PIPELINE_STRESS_LEVEL</t>
+        </is>
+      </c>
+      <c r="F431" s="5" t="inlineStr"/>
       <c r="G431" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44550,12 +45058,12 @@
       </c>
       <c r="E432" s="5" t="inlineStr">
         <is>
-          <t>MOD-096</t>
+          <t>MOD-087</t>
         </is>
       </c>
       <c r="F432" s="5" t="inlineStr">
         <is>
-          <t>RenderingGovernor.js</t>
+          <t>AnuErrorAndStressLedger.js</t>
         </is>
       </c>
       <c r="G432" s="5" t="inlineStr">
@@ -44587,12 +45095,12 @@
       </c>
       <c r="E433" s="5" t="inlineStr">
         <is>
-          <t>MOD-097</t>
+          <t>MOD-092</t>
         </is>
       </c>
       <c r="F433" s="5" t="inlineStr">
         <is>
-          <t>SceneModelInventory.js</t>
+          <t>FrameBudget.js</t>
         </is>
       </c>
       <c r="G433" s="5" t="inlineStr">
@@ -44624,12 +45132,12 @@
       </c>
       <c r="E434" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-096</t>
         </is>
       </c>
       <c r="F434" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>RenderingGovernor.js</t>
         </is>
       </c>
       <c r="G434" s="5" t="inlineStr">
@@ -44651,22 +45159,22 @@
       </c>
       <c r="C435" s="5" t="inlineStr">
         <is>
-          <t>MOD-089</t>
+          <t>MOD-088</t>
         </is>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuGovernanceRules.js</t>
+          <t>js/v2/anu/AnuFuzzyPipelineSensor.js</t>
         </is>
       </c>
       <c r="E435" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-097</t>
         </is>
       </c>
       <c r="F435" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>SceneModelInventory.js</t>
         </is>
       </c>
       <c r="G435" s="5" t="inlineStr">
@@ -44688,22 +45196,22 @@
       </c>
       <c r="C436" s="5" t="inlineStr">
         <is>
-          <t>MOD-090</t>
+          <t>MOD-088</t>
         </is>
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuNatureAwareness.js</t>
+          <t>js/v2/anu/AnuFuzzyPipelineSensor.js</t>
         </is>
       </c>
       <c r="E436" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F436" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G436" s="5" t="inlineStr">
@@ -44725,22 +45233,22 @@
       </c>
       <c r="C437" s="5" t="inlineStr">
         <is>
-          <t>MOD-090</t>
+          <t>MOD-089</t>
         </is>
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuNatureAwareness.js</t>
+          <t>js/v2/anu/AnuGovernanceRules.js</t>
         </is>
       </c>
       <c r="E437" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="F437" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>SimulationController.js</t>
         </is>
       </c>
       <c r="G437" s="5" t="inlineStr">
@@ -44772,12 +45280,12 @@
       </c>
       <c r="E438" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F438" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G438" s="5" t="inlineStr">
@@ -44794,7 +45302,7 @@
       </c>
       <c r="B439" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C439" s="5" t="inlineStr">
@@ -44809,10 +45317,14 @@
       </c>
       <c r="E439" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.FAUNA_TICK</t>
-        </is>
-      </c>
-      <c r="F439" s="5" t="inlineStr"/>
+          <t>MOD-093</t>
+        </is>
+      </c>
+      <c r="F439" s="5" t="inlineStr">
+        <is>
+          <t>InteractionBus.js</t>
+        </is>
+      </c>
       <c r="G439" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44827,7 +45339,7 @@
       </c>
       <c r="B440" s="5" t="inlineStr">
         <is>
-          <t>service-register</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C440" s="5" t="inlineStr">
@@ -44842,10 +45354,14 @@
       </c>
       <c r="E440" s="5" t="inlineStr">
         <is>
-          <t>service:AnuNatureAwareness</t>
-        </is>
-      </c>
-      <c r="F440" s="5" t="inlineStr"/>
+          <t>MOD-100</t>
+        </is>
+      </c>
+      <c r="F440" s="5" t="inlineStr">
+        <is>
+          <t>anuEvents.js</t>
+        </is>
+      </c>
       <c r="G440" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44860,7 +45376,7 @@
       </c>
       <c r="B441" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C441" s="5" t="inlineStr">
@@ -44875,7 +45391,7 @@
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>service:AnuNatureAwareness</t>
+          <t>ANU_EVENTS.FAUNA_TICK</t>
         </is>
       </c>
       <c r="F441" s="5" t="inlineStr"/>
@@ -44893,7 +45409,7 @@
       </c>
       <c r="B442" s="5" t="inlineStr">
         <is>
-          <t>service-use</t>
+          <t>service-register</t>
         </is>
       </c>
       <c r="C442" s="5" t="inlineStr">
@@ -44908,7 +45424,7 @@
       </c>
       <c r="E442" s="5" t="inlineStr">
         <is>
-          <t>service:WorldPhysics</t>
+          <t>service:AnuNatureAwareness</t>
         </is>
       </c>
       <c r="F442" s="5" t="inlineStr"/>
@@ -44926,29 +45442,25 @@
       </c>
       <c r="B443" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C443" s="5" t="inlineStr">
         <is>
-          <t>MOD-091</t>
+          <t>MOD-090</t>
         </is>
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuWorldSensorium.js</t>
+          <t>js/v2/anu/AnuNatureAwareness.js</t>
         </is>
       </c>
       <c r="E443" s="5" t="inlineStr">
         <is>
-          <t>MOD-088</t>
-        </is>
-      </c>
-      <c r="F443" s="5" t="inlineStr">
-        <is>
-          <t>AnuFuzzyPipelineSensor.js</t>
-        </is>
-      </c>
+          <t>service:AnuNatureAwareness</t>
+        </is>
+      </c>
+      <c r="F443" s="5" t="inlineStr"/>
       <c r="G443" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -44963,29 +45475,25 @@
       </c>
       <c r="B444" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-use</t>
         </is>
       </c>
       <c r="C444" s="5" t="inlineStr">
         <is>
-          <t>MOD-091</t>
+          <t>MOD-090</t>
         </is>
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/AnuWorldSensorium.js</t>
+          <t>js/v2/anu/AnuNatureAwareness.js</t>
         </is>
       </c>
       <c r="E444" s="5" t="inlineStr">
         <is>
-          <t>MOD-089</t>
-        </is>
-      </c>
-      <c r="F444" s="5" t="inlineStr">
-        <is>
-          <t>AnuGovernanceRules.js</t>
-        </is>
-      </c>
+          <t>service:WorldPhysics</t>
+        </is>
+      </c>
+      <c r="F444" s="5" t="inlineStr"/>
       <c r="G444" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45015,12 +45523,12 @@
       </c>
       <c r="E445" s="5" t="inlineStr">
         <is>
-          <t>MOD-097</t>
+          <t>MOD-088</t>
         </is>
       </c>
       <c r="F445" s="5" t="inlineStr">
         <is>
-          <t>SceneModelInventory.js</t>
+          <t>AnuFuzzyPipelineSensor.js</t>
         </is>
       </c>
       <c r="G445" s="5" t="inlineStr">
@@ -45052,12 +45560,12 @@
       </c>
       <c r="E446" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-089</t>
         </is>
       </c>
       <c r="F446" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>AnuGovernanceRules.js</t>
         </is>
       </c>
       <c r="G446" s="5" t="inlineStr">
@@ -45079,22 +45587,22 @@
       </c>
       <c r="C447" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
+          <t>MOD-091</t>
         </is>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/FrameBudget.js</t>
+          <t>js/v2/anu/AnuWorldSensorium.js</t>
         </is>
       </c>
       <c r="E447" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-097</t>
         </is>
       </c>
       <c r="F447" s="5" t="inlineStr">
         <is>
-          <t>constants.js</t>
+          <t>SceneModelInventory.js</t>
         </is>
       </c>
       <c r="G447" s="5" t="inlineStr">
@@ -45111,25 +45619,29 @@
       </c>
       <c r="B448" s="5" t="inlineStr">
         <is>
-          <t>global-write</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C448" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
+          <t>MOD-091</t>
         </is>
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/FrameBudget.js</t>
+          <t>js/v2/anu/AnuWorldSensorium.js</t>
         </is>
       </c>
       <c r="E448" s="5" t="inlineStr">
         <is>
-          <t>window.AnuUniverse</t>
-        </is>
-      </c>
-      <c r="F448" s="5" t="inlineStr"/>
+          <t>MOD-098</t>
+        </is>
+      </c>
+      <c r="F448" s="5" t="inlineStr">
+        <is>
+          <t>SimulationController.js</t>
+        </is>
+      </c>
       <c r="G448" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45149,22 +45661,22 @@
       </c>
       <c r="C449" s="5" t="inlineStr">
         <is>
-          <t>MOD-094</t>
+          <t>MOD-092</t>
         </is>
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/PipOrthoRingDiskClip.js</t>
+          <t>js/v2/anu/FrameBudget.js</t>
         </is>
       </c>
       <c r="E449" s="5" t="inlineStr">
         <is>
-          <t>MOD-061</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F449" s="5" t="inlineStr">
         <is>
-          <t>RuntimeServices.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G449" s="5" t="inlineStr">
@@ -45181,22 +45693,22 @@
       </c>
       <c r="B450" s="5" t="inlineStr">
         <is>
-          <t>service-register</t>
+          <t>global-write</t>
         </is>
       </c>
       <c r="C450" s="5" t="inlineStr">
         <is>
-          <t>MOD-094</t>
+          <t>MOD-092</t>
         </is>
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/PipOrthoRingDiskClip.js</t>
+          <t>js/v2/anu/FrameBudget.js</t>
         </is>
       </c>
       <c r="E450" s="5" t="inlineStr">
         <is>
-          <t>service:PipOrthoBranchClip</t>
+          <t>window.AnuUniverse</t>
         </is>
       </c>
       <c r="F450" s="5" t="inlineStr"/>
@@ -45219,22 +45731,22 @@
       </c>
       <c r="C451" s="5" t="inlineStr">
         <is>
-          <t>MOD-095</t>
+          <t>MOD-094</t>
         </is>
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/PipRenderStrategy.js</t>
+          <t>js/v2/anu/PipOrthoRingDiskClip.js</t>
         </is>
       </c>
       <c r="E451" s="5" t="inlineStr">
         <is>
-          <t>MOD-106</t>
+          <t>MOD-061</t>
         </is>
       </c>
       <c r="F451" s="5" t="inlineStr">
         <is>
-          <t>pipCompassMath.js</t>
+          <t>RuntimeServices.js</t>
         </is>
       </c>
       <c r="G451" s="5" t="inlineStr">
@@ -45251,29 +45763,25 @@
       </c>
       <c r="B452" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>service-register</t>
         </is>
       </c>
       <c r="C452" s="5" t="inlineStr">
         <is>
-          <t>MOD-096</t>
+          <t>MOD-094</t>
         </is>
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/RenderingGovernor.js</t>
+          <t>js/v2/anu/PipOrthoRingDiskClip.js</t>
         </is>
       </c>
       <c r="E452" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
-        </is>
-      </c>
-      <c r="F452" s="5" t="inlineStr">
-        <is>
-          <t>constants.js</t>
-        </is>
-      </c>
+          <t>service:PipOrthoBranchClip</t>
+        </is>
+      </c>
+      <c r="F452" s="5" t="inlineStr"/>
       <c r="G452" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45293,22 +45801,22 @@
       </c>
       <c r="C453" s="5" t="inlineStr">
         <is>
-          <t>MOD-097</t>
+          <t>MOD-095</t>
         </is>
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/SceneModelInventory.js</t>
+          <t>js/v2/anu/PipRenderStrategy.js</t>
         </is>
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-106</t>
         </is>
       </c>
       <c r="F453" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>pipCompassMath.js</t>
         </is>
       </c>
       <c r="G453" s="5" t="inlineStr">
@@ -45330,22 +45838,22 @@
       </c>
       <c r="C454" s="5" t="inlineStr">
         <is>
-          <t>MOD-097</t>
+          <t>MOD-096</t>
         </is>
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/SceneModelInventory.js</t>
+          <t>js/v2/anu/RenderingGovernor.js</t>
         </is>
       </c>
       <c r="E454" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-103</t>
         </is>
       </c>
       <c r="F454" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>constants.js</t>
         </is>
       </c>
       <c r="G454" s="5" t="inlineStr">
@@ -45362,7 +45870,7 @@
       </c>
       <c r="B455" s="5" t="inlineStr">
         <is>
-          <t>anu-event-dispatch</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C455" s="5" t="inlineStr">
@@ -45377,10 +45885,14 @@
       </c>
       <c r="E455" s="5" t="inlineStr">
         <is>
-          <t>ANU_EVENTS.SCENE_INVENTORY_TICK</t>
-        </is>
-      </c>
-      <c r="F455" s="5" t="inlineStr"/>
+          <t>MOD-093</t>
+        </is>
+      </c>
+      <c r="F455" s="5" t="inlineStr">
+        <is>
+          <t>InteractionBus.js</t>
+        </is>
+      </c>
       <c r="G455" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45400,22 +45912,22 @@
       </c>
       <c r="C456" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-097</t>
         </is>
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/SimulationController.js</t>
+          <t>js/v2/anu/SceneModelInventory.js</t>
         </is>
       </c>
       <c r="E456" s="5" t="inlineStr">
         <is>
-          <t>MOD-097</t>
+          <t>MOD-100</t>
         </is>
       </c>
       <c r="F456" s="5" t="inlineStr">
         <is>
-          <t>SceneModelInventory.js</t>
+          <t>anuEvents.js</t>
         </is>
       </c>
       <c r="G456" s="5" t="inlineStr">
@@ -45432,29 +45944,25 @@
       </c>
       <c r="B457" s="5" t="inlineStr">
         <is>
-          <t>import</t>
+          <t>anu-event-dispatch</t>
         </is>
       </c>
       <c r="C457" s="5" t="inlineStr">
         <is>
-          <t>MOD-101</t>
+          <t>MOD-097</t>
         </is>
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/index.js</t>
+          <t>js/v2/anu/SceneModelInventory.js</t>
         </is>
       </c>
       <c r="E457" s="5" t="inlineStr">
         <is>
-          <t>MOD-086</t>
-        </is>
-      </c>
-      <c r="F457" s="5" t="inlineStr">
-        <is>
-          <t>AdaptiveRenderPolicy.js</t>
-        </is>
-      </c>
+          <t>ANU_EVENTS.SCENE_INVENTORY_TICK</t>
+        </is>
+      </c>
+      <c r="F457" s="5" t="inlineStr"/>
       <c r="G457" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45474,22 +45982,22 @@
       </c>
       <c r="C458" s="5" t="inlineStr">
         <is>
-          <t>MOD-101</t>
+          <t>MOD-098</t>
         </is>
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/index.js</t>
+          <t>js/v2/anu/SimulationController.js</t>
         </is>
       </c>
       <c r="E458" s="5" t="inlineStr">
         <is>
-          <t>MOD-087</t>
+          <t>MOD-097</t>
         </is>
       </c>
       <c r="F458" s="5" t="inlineStr">
         <is>
-          <t>AnuErrorAndStressLedger.js</t>
+          <t>SceneModelInventory.js</t>
         </is>
       </c>
       <c r="G458" s="5" t="inlineStr">
@@ -45521,12 +46029,12 @@
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>MOD-088</t>
+          <t>MOD-086</t>
         </is>
       </c>
       <c r="F459" s="5" t="inlineStr">
         <is>
-          <t>AnuFuzzyPipelineSensor.js</t>
+          <t>AdaptiveRenderPolicy.js</t>
         </is>
       </c>
       <c r="G459" s="5" t="inlineStr">
@@ -45558,12 +46066,12 @@
       </c>
       <c r="E460" s="5" t="inlineStr">
         <is>
-          <t>MOD-089</t>
+          <t>MOD-087</t>
         </is>
       </c>
       <c r="F460" s="5" t="inlineStr">
         <is>
-          <t>AnuGovernanceRules.js</t>
+          <t>AnuErrorAndStressLedger.js</t>
         </is>
       </c>
       <c r="G460" s="5" t="inlineStr">
@@ -45595,12 +46103,12 @@
       </c>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>MOD-091</t>
+          <t>MOD-088</t>
         </is>
       </c>
       <c r="F461" s="5" t="inlineStr">
         <is>
-          <t>AnuWorldSensorium.js</t>
+          <t>AnuFuzzyPipelineSensor.js</t>
         </is>
       </c>
       <c r="G461" s="5" t="inlineStr">
@@ -45632,12 +46140,12 @@
       </c>
       <c r="E462" s="5" t="inlineStr">
         <is>
-          <t>MOD-092</t>
+          <t>MOD-089</t>
         </is>
       </c>
       <c r="F462" s="5" t="inlineStr">
         <is>
-          <t>FrameBudget.js</t>
+          <t>AnuGovernanceRules.js</t>
         </is>
       </c>
       <c r="G462" s="5" t="inlineStr">
@@ -45669,12 +46177,12 @@
       </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>MOD-093</t>
+          <t>MOD-091</t>
         </is>
       </c>
       <c r="F463" s="5" t="inlineStr">
         <is>
-          <t>InteractionBus.js</t>
+          <t>AnuWorldSensorium.js</t>
         </is>
       </c>
       <c r="G463" s="5" t="inlineStr">
@@ -45706,12 +46214,12 @@
       </c>
       <c r="E464" s="5" t="inlineStr">
         <is>
-          <t>MOD-095</t>
+          <t>MOD-092</t>
         </is>
       </c>
       <c r="F464" s="5" t="inlineStr">
         <is>
-          <t>PipRenderStrategy.js</t>
+          <t>FrameBudget.js</t>
         </is>
       </c>
       <c r="G464" s="5" t="inlineStr">
@@ -45743,12 +46251,12 @@
       </c>
       <c r="E465" s="5" t="inlineStr">
         <is>
-          <t>MOD-096</t>
+          <t>MOD-093</t>
         </is>
       </c>
       <c r="F465" s="5" t="inlineStr">
         <is>
-          <t>RenderingGovernor.js</t>
+          <t>InteractionBus.js</t>
         </is>
       </c>
       <c r="G465" s="5" t="inlineStr">
@@ -45780,12 +46288,12 @@
       </c>
       <c r="E466" s="5" t="inlineStr">
         <is>
-          <t>MOD-097</t>
+          <t>MOD-095</t>
         </is>
       </c>
       <c r="F466" s="5" t="inlineStr">
         <is>
-          <t>SceneModelInventory.js</t>
+          <t>PipRenderStrategy.js</t>
         </is>
       </c>
       <c r="G466" s="5" t="inlineStr">
@@ -45817,12 +46325,12 @@
       </c>
       <c r="E467" s="5" t="inlineStr">
         <is>
-          <t>MOD-098</t>
+          <t>MOD-096</t>
         </is>
       </c>
       <c r="F467" s="5" t="inlineStr">
         <is>
-          <t>SimulationController.js</t>
+          <t>RenderingGovernor.js</t>
         </is>
       </c>
       <c r="G467" s="5" t="inlineStr">
@@ -45854,12 +46362,12 @@
       </c>
       <c r="E468" s="5" t="inlineStr">
         <is>
-          <t>MOD-100</t>
+          <t>MOD-097</t>
         </is>
       </c>
       <c r="F468" s="5" t="inlineStr">
         <is>
-          <t>anuEvents.js</t>
+          <t>SceneModelInventory.js</t>
         </is>
       </c>
       <c r="G468" s="5" t="inlineStr">
@@ -45876,25 +46384,29 @@
       </c>
       <c r="B469" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C469" s="5" t="inlineStr">
         <is>
-          <t>MOD-102</t>
+          <t>MOD-101</t>
         </is>
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/pipelineMemory.js</t>
+          <t>js/v2/anu/index.js</t>
         </is>
       </c>
       <c r="E469" s="5" t="inlineStr">
         <is>
-          <t>Assets/&lt;NAME&gt;.glb</t>
-        </is>
-      </c>
-      <c r="F469" s="5" t="inlineStr"/>
+          <t>MOD-098</t>
+        </is>
+      </c>
+      <c r="F469" s="5" t="inlineStr">
+        <is>
+          <t>SimulationController.js</t>
+        </is>
+      </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45909,25 +46421,29 @@
       </c>
       <c r="B470" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>import</t>
         </is>
       </c>
       <c r="C470" s="5" t="inlineStr">
         <is>
-          <t>MOD-102</t>
+          <t>MOD-101</t>
         </is>
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>js/v2/anu/pipelineMemory.js</t>
+          <t>js/v2/anu/index.js</t>
         </is>
       </c>
       <c r="E470" s="5" t="inlineStr">
         <is>
-          <t>Assets/Avatar3.glb</t>
-        </is>
-      </c>
-      <c r="F470" s="5" t="inlineStr"/>
+          <t>MOD-100</t>
+        </is>
+      </c>
+      <c r="F470" s="5" t="inlineStr">
+        <is>
+          <t>anuEvents.js</t>
+        </is>
+      </c>
       <c r="G470" s="5" t="inlineStr">
         <is>
           <t>Live</t>
@@ -45957,7 +46473,7 @@
       </c>
       <c r="E471" s="5" t="inlineStr">
         <is>
-          <t>Assets/NPC.BHG.glb</t>
+          <t>Assets/&lt;NAME&gt;.glb</t>
         </is>
       </c>
       <c r="F471" s="5" t="inlineStr"/>
@@ -45990,7 +46506,7 @@
       </c>
       <c r="E472" s="5" t="inlineStr">
         <is>
-          <t>Assets/NPC.YB.glb</t>
+          <t>Assets/Avatar3.glb</t>
         </is>
       </c>
       <c r="F472" s="5" t="inlineStr"/>
@@ -46023,7 +46539,7 @@
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>Assets/Tipi.yellowbutterfly/tipi.yellowbutterfly.glb</t>
+          <t>Assets/NPC.BHG.glb</t>
         </is>
       </c>
       <c r="F473" s="5" t="inlineStr"/>
@@ -46056,7 +46572,7 @@
       </c>
       <c r="E474" s="5" t="inlineStr">
         <is>
-          <t>Assets/[removed]/little_pond__fish/scene.gltf</t>
+          <t>Assets/NPC.YB.glb</t>
         </is>
       </c>
       <c r="F474" s="5" t="inlineStr"/>
@@ -46089,7 +46605,7 @@
       </c>
       <c r="E475" s="5" t="inlineStr">
         <is>
-          <t>Assets/animated.deer/source/[deer+3d+model].glb</t>
+          <t>Assets/Tipi.yellowbutterfly/tipi.yellowbutterfly.glb</t>
         </is>
       </c>
       <c r="F475" s="5" t="inlineStr"/>
@@ -46122,7 +46638,7 @@
       </c>
       <c r="E476" s="5" t="inlineStr">
         <is>
-          <t>Assets/animated.stag.glb</t>
+          <t>Assets/[removed]/little_pond__fish/scene.gltf</t>
         </is>
       </c>
       <c r="F476" s="5" t="inlineStr"/>
@@ -46155,7 +46671,7 @@
       </c>
       <c r="E477" s="5" t="inlineStr">
         <is>
-          <t>Assets/bush.glb</t>
+          <t>Assets/animated.deer/source/[deer+3d+model].glb</t>
         </is>
       </c>
       <c r="F477" s="5" t="inlineStr"/>
@@ -46188,7 +46704,7 @@
       </c>
       <c r="E478" s="5" t="inlineStr">
         <is>
-          <t>Assets/flora/reeds.glb</t>
+          <t>Assets/animated.stag.glb</t>
         </is>
       </c>
       <c r="F478" s="5" t="inlineStr"/>
@@ -46221,7 +46737,7 @@
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>Assets/landscape-scenes/terrain/rock.mossy.glb</t>
+          <t>Assets/bush.glb</t>
         </is>
       </c>
       <c r="F479" s="5" t="inlineStr"/>
@@ -46254,7 +46770,7 @@
       </c>
       <c r="E480" s="5" t="inlineStr">
         <is>
-          <t>Assets/pond1.glb</t>
+          <t>Assets/flora/reeds.glb</t>
         </is>
       </c>
       <c r="F480" s="5" t="inlineStr"/>
@@ -46287,7 +46803,7 @@
       </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>Assets/rabbit.animated.glb</t>
+          <t>Assets/landscape-scenes/terrain/rock.mossy.glb</t>
         </is>
       </c>
       <c r="F481" s="5" t="inlineStr"/>
@@ -46320,7 +46836,7 @@
       </c>
       <c r="E482" s="5" t="inlineStr">
         <is>
-          <t>Assets/tree.glb</t>
+          <t>Assets/pond1.glb</t>
         </is>
       </c>
       <c r="F482" s="5" t="inlineStr"/>
@@ -46338,7 +46854,7 @@
       </c>
       <c r="B483" s="5" t="inlineStr">
         <is>
-          <t>postMessage</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="C483" s="5" t="inlineStr">
@@ -46353,7 +46869,7 @@
       </c>
       <c r="E483" s="5" t="inlineStr">
         <is>
-          <t>msg:REQ_AUTOWALK_TO_ENTITY</t>
+          <t>Assets/rabbit.animated.glb</t>
         </is>
       </c>
       <c r="F483" s="5" t="inlineStr"/>
@@ -46376,17 +46892,17 @@
       </c>
       <c r="C484" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-102</t>
         </is>
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>js/v2/constants.js</t>
+          <t>js/v2/anu/pipelineMemory.js</t>
         </is>
       </c>
       <c r="E484" s="5" t="inlineStr">
         <is>
-          <t>Assets/NPC.YB.glb</t>
+          <t>Assets/tree.glb</t>
         </is>
       </c>
       <c r="F484" s="5" t="inlineStr"/>
@@ -46404,22 +46920,22 @@
       </c>
       <c r="B485" s="5" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>postMessage</t>
         </is>
       </c>
       <c r="C485" s="5" t="inlineStr">
         <is>
-          <t>MOD-103</t>
+          <t>MOD-102</t>
         </is>
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>js/v2/constants.js</t>
+          <t>js/v2/anu/pipelineMemory.js</t>
         </is>
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>Assets/tree.glb</t>
+          <t>msg:REQ_AUTOWALK_TO_ENTITY</t>
         </is>
       </c>
       <c r="F485" s="5" t="inlineStr"/>
@@ -46429,8 +46945,74 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" s="5" t="inlineStr">
+        <is>
+          <t>EDG-0482</t>
+        </is>
+      </c>
+      <c r="B486" s="5" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="C486" s="5" t="inlineStr">
+        <is>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="D486" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/constants.js</t>
+        </is>
+      </c>
+      <c r="E486" s="5" t="inlineStr">
+        <is>
+          <t>Assets/NPC.YB.glb</t>
+        </is>
+      </c>
+      <c r="F486" s="5" t="inlineStr"/>
+      <c r="G486" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="5" t="inlineStr">
+        <is>
+          <t>EDG-0483</t>
+        </is>
+      </c>
+      <c r="B487" s="5" t="inlineStr">
+        <is>
+          <t>asset</t>
+        </is>
+      </c>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>MOD-103</t>
+        </is>
+      </c>
+      <c r="D487" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/constants.js</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="inlineStr">
+        <is>
+          <t>Assets/tree.glb</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="inlineStr"/>
+      <c r="G487" s="5" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G485"/>
+  <autoFilter ref="A4:G487"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -42,10 +42,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'51_Assets'!$A$4:$W$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'52_Claims_vs_Verified'!$A$4:$F$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 2854704. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 3dd0fd0. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L237; js/v2/UIModule.js:L302</t>
+          <t>js/v2/UIModule.js:L462; js/v2/UIModule.js:L539</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>SacredGame.Journal.html:L329; js/v2/UIModule.js:L223</t>
+          <t>SacredGame.Journal.html:L329; js/v2/UIModule.js:L433</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L209</t>
+          <t>js/v2/UIModule.js:L406</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L235</t>
+          <t>js/v2/UIModule.js:L447</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L219</t>
+          <t>js/v2/UIModule.js:L415</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L253</t>
+          <t>js/v2/UIModule.js:L478</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L210</t>
+          <t>js/v2/UIModule.js:L407</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L42; js/v2/UIModule.js:L42</t>
+          <t>js/v2/UIModule.js:L83; js/v2/UIModule.js:L83</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1417; js/v2/UIModule.js:L226</t>
+          <t>js/v2/Orchestrator.js:L1417; js/v2/UIModule.js:L438</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L218</t>
+          <t>js/v2/UIModule.js:L409</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L38</t>
+          <t>js/v2/UIModule.js:L80</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1411; js/v2/UIModule.js:L231; js/v2/UIModule.js:L248</t>
+          <t>js/v2/Orchestrator.js:L1411; js/v2/UIModule.js:L443; js/v2/UIModule.js:L473</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>js/v2/UIModule.js:L233; js/components/Component.NewJournal.html:L815</t>
+          <t>js/v2/UIModule.js:L445; js/components/Component.NewJournal.html:L815</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>.cursor/rules/sacred-pip-map-protect.mdc:L10 · js/v2/UIModule.js:L218</t>
+          <t>.cursor/rules/sacred-pip-map-protect.mdc:L10 · js/v2/UIModule.js:L409</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -14669,7 +14669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15182,32 +15182,59 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>DEC-19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Compass: restore the May-10 design, keep today's ids</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>User: 'the design was far superior then'; 'align them center in each radial'.</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>#pip-compass-wrapper, #v2-pip-canvas, #pip-click-zone, .compass-outer-ring and #v2-distance-pill unchanged, so Orchestrator, OrchestratorHud and the fishing glass CSS keep working; map render path untouched (PiP protect rule).</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>DEC-10</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Use per-pixel rasterization for low-poly previews</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Centroid sampling made big triangles look blotchy and would mislead.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>raster.py vs render.py side by side.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>FND-01, FND-02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E22"/>
+  <autoFilter ref="A4:E23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15719,7 +15746,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 2854704.</t>
+          <t>Built at commit 3dd0fd0.</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17374,8 +17401,55 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>ATT-33</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>User + Claude</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Restore the May-10 compass dial (moon-phase ring, thin bronze rim, glass lens, pointer) with every letter and moon centred on its own track</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Done in code: tracks no longer overlap; letters and moons measured 0 px off their midlines at 1280, 800 and phone widths and inside the real game; pill never clipped</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>js/v2/UIModule.js; tests/v4-pip-align.spec.js</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Geometry lives in CSS variables on #v2-panels-pip; the game sets box-sizing:border-box globally, so radii subtract the 1px wrapper border.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I36"/>
+  <autoFilter ref="A4:I37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17386,7 +17460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17807,8 +17881,35 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>LOG-15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Compass restored to the May-10 design with centred tracks (ATT-33, DEC-19). Movement bug still open: waiting for access to Coder 1's local copy.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Done (code)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>ATT-33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E18"/>
+  <autoFilter ref="A4:E19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17866,7 +17967,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2854704</t>
+          <t>3dd0fd0</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -18493,7 +18594,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 2854704</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 3dd0fd0</t>
         </is>
       </c>
     </row>
@@ -26749,7 +26850,7 @@
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>307 lines, 11.2 KB. update() at L246 (28 lines, every 10f). Per-frame hazards: dom_query×1, dom_write×1.</t>
+          <t>544 lines, 23.7 KB. update() at L471 (30 lines, every 10f, every 600f). Per-frame hazards: dom_query×1, dom_write×1.</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -26797,7 +26898,7 @@
         </is>
       </c>
       <c r="Y68" s="6" t="n">
-        <v>307</v>
+        <v>544</v>
       </c>
     </row>
     <row r="69">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -44,8 +44,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 6b8cf51. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 2fd8deb. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryTipis.js:L28 · js/v2/gltfLoaderSetup.js:L51</t>
+          <t>js/sanctuary/SanctuaryTipis.js:L28 · js/v2/gltfLoaderSetup.js:L56</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>js/v2/deviceProfile.js:L37 · js/v2/Orchestrator.js:L106 · js/v2/gltfLoaderSetup.js:L66</t>
+          <t>js/v2/deviceProfile.js:L37 · js/v2/Orchestrator.js:L106 · js/v2/gltfLoaderSetup.js:L74</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>js/v2/gltfLoaderSetup.js:L53</t>
+          <t>js/v2/gltfLoaderSetup.js:L58</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 6b8cf51.</t>
+          <t>Built at commit 2fd8deb.</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17099,8 +17099,55 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>ATT-37</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Remove all Antigravity hooks (owner directive: Antigravity is no longer used after it attacked the codebase): ANTIGRAVITY_GOVERNANCE rule + its hardcoded-true check, .agents/workflows/agent_mesh_protocol.md (shared agent mailbox), test outputs written into ~/.gemini/antigravity/brain (now test-results/), BuildBadge name match</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Done; check:v2 passes; history (manifesto, tmp/ handoffs, commit log) kept as record</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>AnuGovernanceRules.js, tests/v4-*.spec.js, BuildBadge.js</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Do not re-add Antigravity rules, workflows or output paths.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I40"/>
+  <autoFilter ref="A4:I41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17111,7 +17158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17659,8 +17706,62 @@
       </c>
       <c r="E23" s="5" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>LOG-20</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Anu falsification review (ANU_FALSIFICATION_REVIEW.md in the handoff folder): behaviour defects in DPR control, frame timing, fuzzy scores and alerts; always-true and dead checks.</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Done (review)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>ANU_FALSIFICATION_REVIEW.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>LOG-21</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Removed every Antigravity hook from code, tests and agent workflows (ATT-37).</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Done (code)</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>63_Attempts_Ledger</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E23"/>
+  <autoFilter ref="A4:E25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17718,7 +17819,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6b8cf51</t>
+          <t>2fd8deb</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -18345,7 +18446,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 6b8cf51</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 2fd8deb</t>
         </is>
       </c>
     </row>
@@ -21466,11 +21567,11 @@
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
       <c r="V6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-01 fix(mobile): stop iOS OOM crash ("Can't open this page") — cap texture memory</t>
+          <t>2026-10-22 perf(mobile): Phase 1 — one source of truth for "is mobile"</t>
         </is>
       </c>
       <c r="X6" s="5" t="inlineStr">
@@ -26235,11 +26336,11 @@
         </is>
       </c>
       <c r="V63" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W63" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 perf(pip,fishing): drop limbo PIP_FRAME relay, skip dead fishing scan, no transmission pass</t>
+          <t>2026-10-22 perf(mobile): Phase 1 — one source of truth for "is mobile"</t>
         </is>
       </c>
       <c r="X63" s="5" t="inlineStr">
@@ -28620,7 +28721,7 @@
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>162 lines, 5.1 KB. No update().</t>
+          <t>143 lines, 4.5 KB. No update().</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -28660,7 +28761,7 @@
       </c>
       <c r="X93" s="5" t="inlineStr"/>
       <c r="Y93" s="6" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94">
@@ -29804,9 +29905,13 @@
         </is>
       </c>
       <c r="V108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W108" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22 perf(mobile): Phase 1 — one source of truth for "is mobile"</t>
+        </is>
+      </c>
       <c r="X108" s="5" t="inlineStr">
         <is>
           <t>FND-20</t>
@@ -29852,7 +29957,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>86 lines, 3.9 KB. No update().</t>
+          <t>94 lines, 4.5 KB. No update().</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
@@ -29879,11 +29984,11 @@
         </is>
       </c>
       <c r="V109" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W109" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 perf(assets): lite REG + tipi models (PLN-01, PLN-02)</t>
+          <t>2026-10-22 perf(mobile): Phase 2 part 1 — texture-only phone models + capped panel icon renderer</t>
         </is>
       </c>
       <c r="X109" s="5" t="inlineStr">
@@ -29892,7 +29997,7 @@
         </is>
       </c>
       <c r="Y109" s="6" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="110">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -38,14 +38,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'42_Events'!$A$4:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'43_Services'!$A$4:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'44_Limbo_Calls'!$A$4:$G$208</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'50_Findings'!$A$4:$L$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'50_Findings'!$A$4:$L$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'51_Assets'!$A$4:$W$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'52_Claims_vs_Verified'!$A$4:$F$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 3dd0fd0. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 58a3569. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11285,8 +11285,70 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>FND-49</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>SUB-13</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Clicks and keyboard focus depend on an unpinned internet copy of lucide</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>The side panel is decoration; the game canvas gets clicks.</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>#v4-panel-frame covers the whole screen with pointer-events:auto (index.html L225-234), so every ground click lands in the panel iframe. The panel forwards it as CANVAS_CLICK and hands focus back to the game from one script block (SacredGame.Panel.html L1955-2903) whose first line is lucide.createIcons(), loaded from https://unpkg.com/lucide@latest (L10). If that download fails (offline, blocked, CDN down) the block never runs: clicks are swallowed and focus stays in the iframe, so keys stop after the first click. Proven in Node/Chromium: without lucide the click hit iframe#v4-panel-frame and moved 0 m. lucide@latest changes almost daily (1.56 to 1.61 between 2026-10-13 and 10-21); 1.61.0 still defines lucide.createIcons.</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>SacredGame.Panel.html:L10 · SacredGame.Panel.html:L2897 · index.html:L233</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Movement dies whenever unpkg is unreachable; the game is meant to be offline-first.</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Load vendor/lucide/lucide.min.js (already in the repo, v1.11.0) and guard lucide.createIcons() so a missing icon library can never take the click relay down with it.</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>PLN-17</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L52"/>
+  <autoFilter ref="A4:L53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15746,7 +15808,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 3dd0fd0.</t>
+          <t>Built at commit 58a3569.</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17448,8 +17510,55 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ATT-34</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Forensic: 'click-to-move and keys dead since Coder 1'</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Not reproduced. In the owner's Chrome on Coder 1's copy (claude/mobile-optimization @2fd8deb, Live Server :5505, 60 FPS): one ground click walked 5.15 m; W held 1.2 s walked 5.94 m; left arrow 0.6 s turned 1.46 rad; all 43 modules active, no input flag set. Coder 1's code diffs (welcome guide, loading modal, HUD logo, deviceProfile, mobile GLB variants) do not touch input on desktop.</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>movement_probe.mjs; owner Chrome session</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Ground clicks reach the game only through the panel iframe's CANVAS_CLICK relay, and focus returns only through the same script block (FND-49). Reproduce with the exact steps before changing code.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I37"/>
+  <autoFilter ref="A4:I38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17460,7 +17569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17908,8 +18017,35 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>LOG-16</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Movement forensic: not reproduced in the owner's Chrome on Coder 1's copy (ATT-34); found the lucide single point of failure (FND-49). Compass patch applied to the owner's local copy (uncommitted) and verified live.</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>ATT-34, FND-49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E19"/>
+  <autoFilter ref="A4:E20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17967,7 +18103,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3dd0fd0</t>
+          <t>58a3569</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -18273,7 +18409,7 @@
         </is>
       </c>
       <c r="B24" s="11">
-        <f>COUNTIF('50_Findings'!$B$5:$B$52,"Critical")+COUNTIF('50_Findings'!$B$5:$B$52,"High")</f>
+        <f>COUNTIF('50_Findings'!$B$5:$B$53,"Critical")+COUNTIF('50_Findings'!$B$5:$B$53,"High")</f>
         <v/>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -18594,7 +18730,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 3dd0fd0</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 58a3569</t>
         </is>
       </c>
     </row>
@@ -21253,7 +21389,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>FND-23</t>
+          <t>FND-23, FND-49</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -26885,11 +27021,11 @@
         </is>
       </c>
       <c r="V68" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-31 refactor(pip): rename 'moondial' -&gt; 'pip-compass' (it is a compass, not a moondial)</t>
+          <t>2026-10-22 feat(pip): restore May-10 compass dial with centred moon-phase and compass tracks</t>
         </is>
       </c>
       <c r="X68" s="5" t="inlineStr">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -44,8 +44,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 2fd8deb. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 91193ac. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 2fd8deb.</t>
+          <t>Built at commit 91193ac.</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17146,8 +17146,55 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>ATT-38</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Phase 2</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Texture-only phone variants (Avatar-New, NPC.YB, reeds; 4096 -&gt; 1024, byte-identical geometry) + panel ThreeIcons texture cap 512 + mobile avatar URL</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Done: panel 2nd context 172.2 -&gt; 4.3 MB; phone source pixels 481 -&gt; 121 MB; phone GLB 27.1 -&gt; 16.6 MB; desktop identical; screenshots same</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>docs/mobile/PHASE2_REPORT.md</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Phone GPU cap 256 makes 1024 and 4096 sources upload identically — shrink sources, never geometry, for memory without visual loss.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I41"/>
+  <autoFilter ref="A4:I42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17158,7 +17205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17760,8 +17807,58 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>LOG-22</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1: Mobile Phase 2 done (b56549a code + report).</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>PLN-24; docs/mobile/PHASE2_REPORT.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>LOG-23</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>NEXT: Coder 1 starts FIX_ANTIGRAVITY_DAMAGE_PROMPT (Phase A questions to Mark, Phase B fixes) on fix/antigravity-damage.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E25"/>
+  <autoFilter ref="A4:E27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17819,7 +17916,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2fd8deb</t>
+          <t>91193ac</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -18446,7 +18543,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 2fd8deb</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 91193ac</t>
         </is>
       </c>
     </row>
@@ -21486,11 +21583,11 @@
       <c r="T5" s="5" t="inlineStr"/>
       <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-29 feat(pipeline): build-signature badge — show which AI's build is live</t>
+          <t>2026-10-22 chore(security): remove all Antigravity hooks (ATT-37)</t>
         </is>
       </c>
       <c r="X5" s="5" t="inlineStr"/>
@@ -28752,11 +28849,11 @@
         </is>
       </c>
       <c r="V93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-24 Fix compass PIP letters rightside up and register Antigravity in Anu governance</t>
+          <t>2026-10-22 chore(security): remove all Antigravity hooks (ATT-37)</t>
         </is>
       </c>
       <c r="X93" s="5" t="inlineStr"/>

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -44,8 +44,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'70_Session_Log'!$A$4:$E$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -593,7 +593,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 0887cb6. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 8926a2e. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>index.html:L799</t>
+          <t>index.html:L803</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr"/>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryToolPalette.js:L478; js/v2/OrchestratorHud.js:L884; js/v2/OrchestratorHud.js:L943; index.html:L436; index.html:L866</t>
+          <t>js/sanctuary/SanctuaryToolPalette.js:L478; js/v2/OrchestratorHud.js:L884; js/v2/OrchestratorHud.js:L943; index.html:L436; index.html:L870</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1403; js/v2/UIModule.js:L226</t>
+          <t>js/v2/Orchestrator.js:L1401; js/v2/UIModule.js:L226</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>index.html:L764</t>
+          <t>index.html:L768</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>index.html:L429; index.html:L889</t>
+          <t>index.html:L429; index.html:L893</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>index.html:L674</t>
+          <t>index.html:L678</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryKeyboardLook.js:L276; index.html:L673; index.html:L697</t>
+          <t>js/sanctuary/SanctuaryKeyboardLook.js:L276; index.html:L677; index.html:L701</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>index.html:L695</t>
+          <t>index.html:L699</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>index.html:L723</t>
+          <t>index.html:L727</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1397; js/v2/UIModule.js:L231; js/v2/UIModule.js:L248</t>
+          <t>js/v2/Orchestrator.js:L1395; js/v2/UIModule.js:L231; js/v2/UIModule.js:L248</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>index.html:L883</t>
+          <t>index.html:L887</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>index.html:L714; SacredGame.Panel.html:L2065; SacredGame.Journal.html:L455</t>
+          <t>index.html:L718; SacredGame.Panel.html:L2065; SacredGame.Journal.html:L455</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>index.html:L783</t>
+          <t>index.html:L787</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>index.html:L687</t>
+          <t>index.html:L691</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>index.html:L899</t>
+          <t>index.html:L903</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>index.html:L749</t>
+          <t>index.html:L753</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>index.html:L715; SacredGame.Panel.html:L2261; SacredGame.Journal.html:L424</t>
+          <t>index.html:L719; SacredGame.Panel.html:L2261; SacredGame.Journal.html:L424</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>index.html:L714</t>
+          <t>index.html:L718</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>index.html:L880</t>
+          <t>index.html:L884</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>index.html:L874</t>
+          <t>index.html:L878</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>index.html:L688; index.html:L728; SacredGame.Journal.html:L351; SacredGame.Journal.html:L358; SacredGame.Journal.html:L370</t>
+          <t>index.html:L692; index.html:L732; SacredGame.Journal.html:L351; SacredGame.Journal.html:L358; SacredGame.Journal.html:L370</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryFishing.js:L1588; js/sanctuary/SanctuaryFishing.js:L2708; js/sanctuary/SanctuaryKeyboardLook.js:L80; js/sanctuary/SanctuaryKeyboardLook.js:L136; js/sanctuary/SanctuaryKeyboardLook.js:L170; index.html:L826; index.html:L902</t>
+          <t>js/sanctuary/SanctuaryFishing.js:L1588; js/sanctuary/SanctuaryFishing.js:L2708; js/sanctuary/SanctuaryKeyboardLook.js:L80; js/sanctuary/SanctuaryKeyboardLook.js:L136; js/sanctuary/SanctuaryKeyboardLook.js:L170; index.html:L830; index.html:L906</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>index.html:L852; index.html:L856</t>
+          <t>index.html:L856; index.html:L860</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>index.html:L830</t>
+          <t>index.html:L834</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -7667,12 +7667,12 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L246; index.html:L294; index.html:L659</t>
+          <t>js/sanctuary/SanctuaryControls.js:L246; index.html:L294; index.html:L663</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>index.html:L691</t>
+          <t>index.html:L695</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L241; index.html:L313; index.html:L789</t>
+          <t>js/sanctuary/SanctuaryControls.js:L241; index.html:L313; index.html:L793</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>index.html:L734</t>
+          <t>index.html:L738</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>index.html:L878</t>
+          <t>index.html:L882</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryClickToMove.js:L283; js/sanctuary/SanctuaryClickToMove.js:L323; index.html:L849</t>
+          <t>js/sanctuary/SanctuaryClickToMove.js:L283; js/sanctuary/SanctuaryClickToMove.js:L323; index.html:L853</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryTipis.js:L28 · js/v2/gltfLoaderSetup.js:L56</t>
+          <t>js/sanctuary/SanctuaryTipis.js:L28 · js/v2/gltfLoaderSetup.js:L60</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1392</t>
+          <t>js/v2/Orchestrator.js:L1390</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1451 · js/v2/Orchestrator.js:L1526 · js/v2/Orchestrator.js:L1305</t>
+          <t>js/v2/Orchestrator.js:L1449 · js/v2/Orchestrator.js:L1524 · js/v2/Orchestrator.js:L1305</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>index.html:L627 · js/v2/Orchestrator.js:L455</t>
+          <t>index.html:L631 · js/v2/Orchestrator.js:L455</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>js/v2/deviceProfile.js:L37 · js/v2/Orchestrator.js:L105 · js/v2/gltfLoaderSetup.js:L74</t>
+          <t>js/v2/deviceProfile.js:L37 · js/v2/Orchestrator.js:L105 · js/v2/gltfLoaderSetup.js:L78</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1429</t>
+          <t>js/v2/Orchestrator.js:L1427</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1578 · js/v2/Orchestrator.js:L1276</t>
+          <t>js/v2/Orchestrator.js:L1579 · js/v2/Orchestrator.js:L1276</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>index.html:L799</t>
+          <t>index.html:L803</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1523</t>
+          <t>js/v2/Orchestrator.js:L1521</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryPool.js:L1697</t>
+          <t>js/sanctuary/SanctuaryPool.js:L1852</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryPool.js:L1320</t>
+          <t>js/sanctuary/SanctuaryPool.js:L1475</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryPool.js:L857 · js/sanctuary/SanctuaryDock.js:L439</t>
+          <t>js/sanctuary/SanctuaryPool.js:L1012 · js/sanctuary/SanctuaryDock.js:L439</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryPool.js:L1766 · js/sanctuary/SanctuaryPool.js:L180</t>
+          <t>js/sanctuary/SanctuaryPool.js:L1921 · js/sanctuary/SanctuaryPool.js:L180</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1392</t>
+          <t>js/v2/Orchestrator.js:L1390</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1429</t>
+          <t>js/v2/Orchestrator.js:L1427</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1578</t>
+          <t>js/v2/Orchestrator.js:L1579</t>
         </is>
       </c>
     </row>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>js/v2/Orchestrator.js:L1472</t>
+          <t>js/v2/Orchestrator.js:L1470</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>js/v2/gltfLoaderSetup.js:L58</t>
+          <t>js/v2/gltfLoaderSetup.js:L62</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>index.html:L450</t>
+          <t>index.html:L454</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 0887cb6.</t>
+          <t>Built at commit 8926a2e.</t>
         </is>
       </c>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryPool.js:L1789</t>
+          <t>js/sanctuary/SanctuaryPool.js:L1944</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15312,7 +15312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17751,8 +17751,192 @@
       </c>
       <c r="I56" s="5" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>ATT-54</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Mobile memory (Q21) / B14</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Phones render at deviceProfile.dprCap (1.0) instead of a hard 1.5 in index.html</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Done e636515 (Mark Q21: 'we need memory for mobiles'); iPhone 3x framebuffer 5.7 -&gt; 2.5 MB</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>fix/antigravity-damage e636515</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>ATT-55</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Mobile memory (Q21)</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Phone avatar 246k -&gt; 100k tris (lite.mjs; 41 joints, 9 clips intact), 1024 px maps</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Done cdb3410: geometry buffers game 20.9 -&gt; 15.4 MB, panel badge 11.7 -&gt; 6.2 MB; close-up 1.76 % px differ</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>docs/mobile/img/avatar_phone_246k_vs_100k.jpg</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>60k changed the mouth/face: rejected. 100k is the floor for looks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>ATT-56</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Pond (Q22) / B5</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Turtle on the visible floor + new carapace texture (top-down UVs, scutes, R=height G=roughness detail map)</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Done c728235: turtle was 0.8-1.4 m under the terrain (placed from the water line); now sanctuaryGroundY + 0.2 m; texture 6-9 ms</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>docs/pond/img/turtle_*.jpg</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>SphereGeometry UVs wrap the dome; draw top-down only with remapped UVs. Avoid getImageData in boot-time canvas work (210-700 ms).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>ATT-57</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Fishing minimap (Q17) / A5</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Cull the fishing PiP to the ring; keep every other frame</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Done 8926a2e: draws were already ring-only (37 draws, 288k tris, 98 % koi); skipped the redundant whole-scene matrix update: CPU 1.2 -&gt; 0.4 ms; A/B image identical</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>fix/antigravity-damage 8926a2e</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Pruning layer-2-free groups gave no gain. Phone cost is the 18 x 15.6k-tri koi: lighter minimap fish needs Mark.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I56"/>
+  <autoFilter ref="A4:I60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17763,7 +17947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18465,8 +18649,35 @@
       </c>
       <c r="E29" s="5" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>LOG-27</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1: Q21 phone memory (e636515, cdb3410), Q22 turtle (c728235), Q17 fishing minimap (8926a2e) committed and pushed. Found: a72ef50's x1.18 basin floor/drain/rocks lie under the terrain (Mark decides). LOG-26/ATT-53 reserved for the grass rows at merge.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>ATT-54..57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E29"/>
+  <autoFilter ref="A4:E30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18524,7 +18735,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0887cb6</t>
+          <t>8926a2e</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -19151,7 +19362,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 0887cb6</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 8926a2e</t>
         </is>
       </c>
     </row>
@@ -19219,7 +19430,7 @@
       <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>index.html:L495</t>
+          <t>index.html:L499</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19461,7 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>index.html:L498</t>
+          <t>index.html:L502</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19492,7 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>index.html:L501</t>
+          <t>index.html:L505</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19523,7 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>index.html:L504</t>
+          <t>index.html:L508</t>
         </is>
       </c>
     </row>
@@ -19343,7 +19554,7 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>index.html:L507</t>
+          <t>index.html:L511</t>
         </is>
       </c>
     </row>
@@ -19374,7 +19585,7 @@
       <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>index.html:L510</t>
+          <t>index.html:L514</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19616,7 @@
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>index.html:L513</t>
+          <t>index.html:L517</t>
         </is>
       </c>
     </row>
@@ -19436,7 +19647,7 @@
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>index.html:L526</t>
+          <t>index.html:L530</t>
         </is>
       </c>
     </row>
@@ -19471,7 +19682,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>index.html:L529</t>
+          <t>index.html:L533</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19713,7 @@
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>index.html:L532</t>
+          <t>index.html:L536</t>
         </is>
       </c>
     </row>
@@ -19533,7 +19744,7 @@
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>index.html:L535</t>
+          <t>index.html:L539</t>
         </is>
       </c>
     </row>
@@ -19568,7 +19779,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>index.html:L538</t>
+          <t>index.html:L542</t>
         </is>
       </c>
     </row>
@@ -19603,7 +19814,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>index.html:L541</t>
+          <t>index.html:L545</t>
         </is>
       </c>
     </row>
@@ -19638,7 +19849,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>index.html:L544</t>
+          <t>index.html:L548</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19884,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>index.html:L547</t>
+          <t>index.html:L551</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19919,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>index.html:L550</t>
+          <t>index.html:L554</t>
         </is>
       </c>
     </row>
@@ -19743,7 +19954,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>index.html:L553</t>
+          <t>index.html:L557</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19989,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>index.html:L554</t>
+          <t>index.html:L558</t>
         </is>
       </c>
     </row>
@@ -19813,7 +20024,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>index.html:L555</t>
+          <t>index.html:L559</t>
         </is>
       </c>
     </row>
@@ -19848,7 +20059,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>index.html:L556</t>
+          <t>index.html:L560</t>
         </is>
       </c>
     </row>
@@ -19883,7 +20094,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>index.html:L559</t>
+          <t>index.html:L563</t>
         </is>
       </c>
     </row>
@@ -19918,7 +20129,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>index.html:L562</t>
+          <t>index.html:L566</t>
         </is>
       </c>
     </row>
@@ -19953,7 +20164,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>index.html:L563</t>
+          <t>index.html:L567</t>
         </is>
       </c>
     </row>
@@ -19988,7 +20199,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>index.html:L566</t>
+          <t>index.html:L570</t>
         </is>
       </c>
     </row>
@@ -20023,7 +20234,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>index.html:L569</t>
+          <t>index.html:L573</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20265,7 @@
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>index.html:L572</t>
+          <t>index.html:L576</t>
         </is>
       </c>
     </row>
@@ -20089,7 +20300,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>index.html:L575</t>
+          <t>index.html:L579</t>
         </is>
       </c>
     </row>
@@ -20124,7 +20335,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>index.html:L578</t>
+          <t>index.html:L582</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20370,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>index.html:L581</t>
+          <t>index.html:L585</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20405,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>index.html:L584</t>
+          <t>index.html:L588</t>
         </is>
       </c>
     </row>
@@ -20225,7 +20436,7 @@
       <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>index.html:L587</t>
+          <t>index.html:L591</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20467,7 @@
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>index.html:L590</t>
+          <t>index.html:L594</t>
         </is>
       </c>
     </row>
@@ -20287,7 +20498,7 @@
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>index.html:L593</t>
+          <t>index.html:L597</t>
         </is>
       </c>
     </row>
@@ -20322,7 +20533,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>index.html:L596</t>
+          <t>index.html:L600</t>
         </is>
       </c>
     </row>
@@ -20357,7 +20568,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>index.html:L599</t>
+          <t>index.html:L603</t>
         </is>
       </c>
     </row>
@@ -20392,7 +20603,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>index.html:L602</t>
+          <t>index.html:L606</t>
         </is>
       </c>
     </row>
@@ -20427,7 +20638,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>index.html:L605</t>
+          <t>index.html:L609</t>
         </is>
       </c>
     </row>
@@ -20458,7 +20669,7 @@
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>index.html:L609</t>
+          <t>index.html:L613</t>
         </is>
       </c>
     </row>
@@ -20493,7 +20704,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>index.html:L612</t>
+          <t>index.html:L616</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20739,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>index.html:L615</t>
+          <t>index.html:L619</t>
         </is>
       </c>
     </row>
@@ -20559,7 +20770,7 @@
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>index.html:L618</t>
+          <t>index.html:L622</t>
         </is>
       </c>
     </row>
@@ -20590,7 +20801,7 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>index.html:L621</t>
+          <t>index.html:L625</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20832,7 @@
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>index.html:L624</t>
+          <t>index.html:L628</t>
         </is>
       </c>
     </row>
@@ -20642,7 +20853,7 @@
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>index.html:L523</t>
+          <t>index.html:L527</t>
         </is>
       </c>
     </row>
@@ -25004,7 +25215,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>2116 lines, 84.9 KB. update() at L1997 (90 lines). Writes 2 globals.</t>
+          <t>2272 lines, 93.8 KB. update() at L2152 (90 lines). Writes 2 globals.</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -25031,11 +25242,11 @@
       <c r="T39" s="5" t="inlineStr"/>
       <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W39" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 fix(pool): remove the turtle belly plate re-added by 1f4e275 (AUDIT 2, B6)</t>
+          <t>2026-10-22 fix(pool): turtle sits on the visible pond floor + new carapace texture (Q22, B5)</t>
         </is>
       </c>
       <c r="X39" s="5" t="inlineStr">
@@ -25044,7 +25255,7 @@
         </is>
       </c>
       <c r="Y39" s="6" t="n">
-        <v>2116</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="40">
@@ -26990,7 +27201,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>1813 lines, 76.6 KB. No update(). Writes 4 globals.</t>
+          <t>1826 lines, 77.3 KB. No update(). Writes 4 globals.</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -27029,11 +27240,11 @@
         </is>
       </c>
       <c r="V63" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W63" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 refactor(pip): delete the hollow PipOrthoRingDiskClip module emptied by b0b4575 (AUDIT 3, B11)</t>
+          <t>2026-10-22 perf(pip): fishing minimap skips the whole-map matrix update; keep every other frame (Q17, A5)</t>
         </is>
       </c>
       <c r="X63" s="5" t="inlineStr">
@@ -27042,7 +27253,7 @@
         </is>
       </c>
       <c r="Y63" s="6" t="n">
-        <v>1813</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="64">
@@ -30571,7 +30782,7 @@
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>94 lines, 4.5 KB. No update().</t>
+          <t>98 lines, 4.8 KB. No update().</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -30598,11 +30809,11 @@
         </is>
       </c>
       <c r="V108" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W108" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 perf(mobile): Phase 2 part 1 — texture-only phone models + capped panel icon renderer</t>
+          <t>2026-10-22 perf(mobile): phone avatar 246k -&gt; 100k triangles, rig intact (Q21)</t>
         </is>
       </c>
       <c r="X108" s="5" t="inlineStr">
@@ -30611,7 +30822,7 @@
         </is>
       </c>
       <c r="Y108" s="6" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="109">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -45,13 +45,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'51_Assets'!$A$4:$W$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'52_Claims_vs_Verified'!$A$4:$F$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'64_Next_Plan'!$A$4:$L$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'65_Team_Seats'!$A$4:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'66_Owner_Decisions'!$A$4:$F$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'70_Session_Log'!$A$4:$E$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'70_Session_Log'!$A$4:$E$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -623,7 +623,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit c1943c4. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 467b9e9. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -15029,12 +15029,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Awaiting approval</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Same pipeline as PLN-01.</t>
+          <t>3536dc8 (ATT-85): 245,991 → 119,993 tris with the face, hair and headdress locked (Mark: 'without destroying her beauty'); ≤ 50k would change her face. Mark decides whether 120k closes this step.</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16283,221 +16283,275 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>DEC-26</t>
+          <t>DEC-20</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Village builder: keep the farm loop, drop every layer that sells time</t>
+          <t>Keyboard and pointer controls standard (Mark, 2026-10-22)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>The best-selling farm and village games earn from layers around the loop (skip timers, energy, gem currencies, loot boxes, limited-time offers, ads, trading, chat); regulators act on the same list (FTC v. Epic 2022, FTC v. HoYoverse 2025, Brazil's loot-box ban 2026, Roblox age-checked chat 2026).</t>
+          <t>W/S walk, and walking forward for more than 2 s becomes a run (1.6x, 0.5 s ramp). A/D and Left/Right turn (Q/E too). Shift + A/D (or Shift + Left/Right) strafes. Space jumps. Enter attacks, or interacts with / confirms the open modal; Esc closes it. Mouse or one-finger drag looks; the on-screen up/level/down buttons and PageUp/Home/PageDown tilt the view.</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Research report claude/village-farm-sim-research.md §1-4; every figure dated and sourced.</t>
+          <t>SanctuaryKeyboardLook.js (turn/strafe/run/jump; jump height now added after the avatar ground snap), SanctuaryClickToMove.js (click-walk runs after 2 s), SanctuaryAvatar.js (walk cycle speeds up when running), SanctuaryWelcomeGuide.js (help text), drag-look. Committed 86c161a on Mark's OK (2026-10-22). Enter is not wired yet: there is no interact or attack system.</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>PLN-34..37</t>
+          <t>DRAG-LOOK, village builder Phase 4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>DEC-27</t>
+          <t>DEC-21</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Growth and processing run on play time only: no offline growth, no clock that ends play, no energy bar</t>
+          <t>Every menu and modal uses the panel (guidebook) structure (Mark, 2026-10-22)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Children under about 7 do not reliably understand minutes and hours; real-time growth is a come-back-tomorrow lure; Stardew's day clock and energy bar are its most-cited stress.</t>
+          <t>One shared dialog pattern for all menus so each is keyboard-operable and WCAG 2.2 AAA: focus moves into the dialog and back out, logical Tab order, Enter = primary action, Esc = close, targets of at least 44 x 44 CSS px, text for every icon, nothing traps focus. The top-down builder's side panels (BUILD &amp; MAP tool palette, VILLAGE BUILDINGS list, bottom TOP-DOWN/SAVE/RESET bar) must be rebuilt to it.</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Research §2 and §6; P2-4 clock spec (the tick advances only while the page is visible).</t>
+          <t>Reference: the Welcome Guide (#sanctuary-welcome-guide, role=dialog, Prev/Skip/Next) and the side panel (SacredGame.Panel.html). The builder panels do not follow it today (village-builder-plan section 1). The Welcome Guide itself still has 36-39 px buttons and a 14 px checkbox (browser test 2026-10-22).</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>Village builder Phase 4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>DEC-28</t>
+          <t>DEC-26</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Drying rack, food cache, garden and cooking fire start at 10 slots; each level adds one, so +10% per level is literal</t>
+          <t>Village builder: keep the farm loop, drop every layer that sells time</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Mark: +10% per level up to level 10. Ten-frames match how young children count, and nothing on screen counts past ten.</t>
+          <t>The best-selling farm and village games earn from layers around the loop (skip timers, energy, gem currencies, loot boxes, limited-time offers, ads, trading, chat); regulators act on the same list (FTC v. Epic 2022, FTC v. HoYoverse 2025, Brazil's loot-box ban 2026, Roblox age-checked chat 2026).</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Research §3; P3-1 table; multiplier 1 + 0.10 x (level - 1) = 1.9 at level 10.</t>
+          <t>Research report claude/village-farm-sim-research.md §1-4; every figure dated and sourced.</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>PLN-37, PLN-38</t>
+          <t>PLN-34..37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>DEC-29</t>
+          <t>DEC-27</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Reserve Yellow Butterfly's lodge ground from Phase 1; the 2x lodge stands on tile (2, 0)'s centre on maps 1, 3, 4 and 5</t>
+          <t>Growth and processing run on play time only: no offline growth, no clock that ends play, no energy bar</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Measured: in place, a 2x lodge reaches 3.3 m into the pond and overlaps tipi 4 by 2.1 m; at (21.72, 0) with a 7.5 m platform it clears both by about 2.2 m. Built buildings never move (Q7), so the ground must be kept free first.</t>
+          <t>Children under about 7 do not reliably understand minutes and hours; real-time growth is a come-back-tomorrow lure; Stardew's day clock and energy bar are its most-cited stress.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Measured on 68dcab1: V2_HEX_CIRCUMRADIUS 6.27, platform 4.7 m, tipi GLB 5.5 x 6.4 m at 7.2 m tall. Default until Mark decides (roadmap #3).</t>
+          <t>Research §2 and §6; P2-4 clock spec (the tick advances only while the page is visible).</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>PLN-31, PLN-39</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>DEC-30</t>
+          <t>DEC-28</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Cultural gates for the village builder</t>
+          <t>Drying rack, food cache, garden and cooking fire start at 10 slots; each level adds one, so +10% per level is literal</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>A partner community reviews every name, word, picture and line; a permission ledger in data; 'drying rack', not 'fishery'; no 'Three Sisters' label or sunflowers by default; tobacco, medicines, sage, sweetgrass, cedar, songs, offerings and ceremonies never become mechanics; generosity is never scored.</t>
+          <t>Mark: +10% per level up to level 10. Ten-frames match how young children count, and nothing on screen counts past ten.</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Research reports claude/village-builder-research.md §2 and claude/village-farm-sim-research.md §5 (Looking Horse Proclamation, MIAC 2024 on wild rice, Hoċokata Ṫi).</t>
+          <t>Research §3; P3-1 table; multiplier 1 + 0.10 x (level - 1) = 1.9 at level 10.</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>PLN-31..39</t>
+          <t>PLN-37, PLN-38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>DEC-31</t>
+          <t>DEC-29</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>The village-phases specs replace older village-builder defaults</t>
+          <t>Reserve Yellow Butterfly's lodge ground from Phase 1; the 2x lodge stands on tile (2, 0)'s centre on maps 1, 3, 4 and 5</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Mark's 22 Oct brief (a Tier-2 lodge; levels to 10) and the research: levels 1-10 replace the plan's L1-L3; 60° turns and a fixed tray replace 45° and floating buttons; the coder pack's §10 'later' section is superseded for Phases 2-3.</t>
+          <t>Measured: in place, a 2x lodge reaches 3.3 m into the pond and overlaps tipi 4 by 2.1 m; at (21.72, 0) with a 7.5 m platform it clears both by about 2.2 m. Built buildings never move (Q7), so the ground must be kept free first.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Each spec lists what it overrides; P1-3 builds on coder pack W6 instead of redoing it.</t>
+          <t>Measured on 68dcab1: V2_HEX_CIRCUMRADIUS 6.27, platform 4.7 m, tipi GLB 5.5 x 6.4 m at 7.2 m tall. Default until Mark decides (roadmap #3).</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>PLN-31..39</t>
+          <t>PLN-31, PLN-39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>DEC-32</t>
+          <t>DEC-30</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>The Decision Engine gold has one owner: Claude (village researcher)</t>
+          <t>Cultural gates for the village builder</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Mark, 2026-10-22: 'you control the decision-engine gold now'. The rebuild had failed since ffbd558 (KeyError 'status') and a preview build sat uncommitted over the tracked workbook.</t>
+          <t>A partner community reviews every name, word, picture and line; a permission ledger in data; 'drying rack', not 'fishery'; no 'Three Sisters' label or sunflowers by default; tobacco, medicines, sage, sweetgrass, cedar, songs, offerings and ceremonies never become mechanics; generosity is never scored.</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>The owner rebuilds from a HEAD snapshot outside the repo and alone commits Decision_Engine.xlsx and data/*.json. Everyone else reserves IDs on tmp/handoff.md, commits rows only (build_engine.py, rows_*.py) through a temporary index, and builds previews outside the repo.</t>
+          <t>Research reports claude/village-builder-research.md §2 and claude/village-farm-sim-research.md §5 (Looking Horse Proclamation, MIAC 2024 on wild rice, Hoċokata Ṫi).</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>PLN-41, LOG-41</t>
+          <t>PLN-31..39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>DEC-31</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>The village-phases specs replace older village-builder defaults</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Mark's 22 Oct brief (a Tier-2 lodge; levels to 10) and the research: levels 1-10 replace the plan's L1-L3; 60° turns and a fixed tray replace 45° and floating buttons; the coder pack's §10 'later' section is superseded for Phases 2-3.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Each spec lists what it overrides; P1-3 builds on coder pack W6 instead of redoing it.</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>PLN-31..39</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>DEC-32</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>The Decision Engine gold has one owner: Claude (village researcher)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Mark, 2026-10-22: 'you control the decision-engine gold now'. The rebuild had failed since ffbd558 (KeyError 'status') and a preview build sat uncommitted over the tracked workbook.</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>The owner rebuilds from a HEAD snapshot outside the repo and alone commits Decision_Engine.xlsx and data/*.json. Everyone else reserves IDs on tmp/handoff.md, commits rows only (build_engine.py, rows_*.py) through a temporary index, and builds previews outside the repo.</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>PLN-41, LOG-41</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>DEC-33</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>The village builder, Phases 1-3, is the next plan</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Mark, 2026-10-22: 'move the plans into the decision engine as our next plan'. The specs, the model plan and the five-seat prompt pack are written; all 25 owner questions have defaults, so building can start before he answers.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>64_Next_Plan holds 66 items in the team protocol's landing order (§6), each with its spec section, dependencies, files, proof and gate; every build prints any dependency that would land after its item.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>PLN-31..41</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E30"/>
+  <autoFilter ref="A4:E32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17009,7 +17063,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit c1943c4.</t>
+          <t>Built at commit 467b9e9.</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20993,8 +21047,196 @@
       </c>
       <c r="I87" s="5" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>ATT-69</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Claude researcher + Coder 1</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Controls (Mark: turn / strafe / run / jump)</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>86c161a: A/D and the arrows turn (Q/E too); Shift + A/D (or Shift + arrows) strafe; walking forward &gt; 2 s runs (0.5 s ramp to 1.6x; keys, joystick or click-walk); the jump height is kept and added after the avatar's ground snap; the walk cycle speeds up while running; Welcome Guide help text</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Done: Mark's M1 Chrome: D turns 1.21 rad in 0.5 s without moving; Shift+D moves 2.36 m without turning; Space peaks 0.65 m; W walks 5.0 m/s and runs 8.1 m/s after 2.5 s; no stuck keys. Mark: 'okay go'</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryKeyboardLook.js, SanctuaryClickToMove.js, SanctuaryAvatar.js, SanctuaryWelcomeGuide.js, index.html</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Written by the researcher at 18:08 (controls-turn-strafe-run-jump.patch); committed by Coder 1 from the tree through a temporary index after Mark's OK. Enter (interact / attack) is not wired yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>ATT-85</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Avatar (Mark: 'reduce the amount of triangles on her model ... without destroying her beauty')</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>3536dc8: Avatar-New.glb 245,991 -&gt; 119,993 triangles (-51 %), 142,394 -&gt; 73,546 vertices; every vertex the Head bone drives (face, hair, headdress: 52,465) is locked; textures byte-identical, same 41 joints and 9 clips. tools/models/simplify-keep-textures.mjs (weld, meshoptimizer simplifyWithAttributes with normals + UV weighted, Draco) rebuilds the file byte for byte</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Done: Mark's M1 Chrome: outline over 9 clips x 3 times x 2 views, median 0.45 % of outline pixels differ, worst 0.77 % (swimming); face, hands and body close-ups match. Avatar alone, timer queries, 40 renders per query: main-pass vertex work 0.55 -&gt; 0.36 ms, shadow pass 0.41 -&gt; 0.30 ms; one scene render from the game camera 4.15 -&gt; 3.88 ms</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Assets/npc/Avatar-New.glb, tools/models/simplify-keep-textures.mjs; claude/LOCKS.md</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>FND-53's 3.5 ms shadow pass was not reproduced (0.3-0.5 ms measured). A 30k shadow-only proxy gains about nothing in three r160: it is also drawn in the main pass. PLN-20 (&lt;= 50k) would cost her face; 120k with the head locked is the beauty-first point. Phones keep Avatar-New.mobile.glb (100k, 1024 px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>ATT-88</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>UI overlay blur (FND-51; Mark: '1. yes - your recomendations')</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>20b826a + 67038a9: every backdrop-filter over the game canvas in normal play replaced by static frost (a little more tint, no blur): control buttons, FPS panel, build badge, D-pad, thumb buttons, avatar circle, the 5 cards, chat pill, #v4-banner, compass bracket. Kept: the Welcome Guide blur (Mark) and the modals</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Done: Mark's M1 Chrome, test tab 1048x1603, Welcome Guide skipped: before, most frames 33.3 ms (HUD 24 fps); after part 1, 49-50 fps, 80 % of frames &lt; 20 ms, p95 33.4 ms; after part 2, 57.6-60 fps, 97-100 % &lt; 20 ms, p95 18.6 ms</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>claude/finding-live-blur-fps.md; SacredGame.css, js/v2/OrchestratorHud.js, js/BuildBadge.js, SacredGame.Panel.html, index.html, js/v2/UIModule.js</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>One live blur over the WebGL canvas keeps most M1 frames at two vsyncs whatever the scene costs, so culling shows no gain while one is on screen. The hidden Welcome Guide (opacity 0 after Skip) measured no cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>ATT-89</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Camera (Mark: 'when walking move cam 1 foot above avatar head when walkbehind')</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>f30283d: while she walks (any input; her real ground speed &gt; 0.5 m/s, held 0.35 s) the camera follows close behind her (1.2 m target) at the top of her head + 0.3048 m, looking ahead over her head; the head top is measured once from the model (1.66 m for Avatar-New, feathers included); standing or turning keeps the chase view. Replaces the May-19 W view (3 ft in front at eye height); WALK_CAMERA = 'front' restores it</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Done: Mark's M1 Chrome: walking at 5 m/s, camera 1.97 m above her feet, 1.85-1.89 m behind (the follow smoothing trails a little), centred; after stopping, 5.0 m behind / 2.6 m up again</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryKeyboardLook.js</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Committed through a temporary index next to the researcher's then-uncommitted controls hunks (they landed in 86c161a).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I87"/>
+  <autoFilter ref="A4:I91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24990,7 +25232,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>c1943c4</t>
+          <t>467b9e9</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -26624,7 +26866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27650,8 +27892,62 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>LOG-34</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Controls (Mark: turn / strafe / run / jump): written by the researcher (18:08), committed by Coder 1 on Mark's 'okay go' (86c161a); decisions DEC-20 (controls standard) and DEC-21 (every menu uses the panel / guidebook structure).</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>ATT-69, DEC-20, DEC-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>LOG-38</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Coder 1: lighter avatar (3536dc8), blur part 2 (67038a9), walking camera (f30283d), the researcher's controls on Mark's OK (86c161a); all pushed, GitHub = Mark's clone. Low-end research published (claude/compassionate-ui-lowend-culling-research.md); its tier part is the Compassion holder's deviceCheck.js.</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>ATT-69, ATT-85, ATT-88, ATT-89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E41"/>
+  <autoFilter ref="A4:E43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27881,7 +28177,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit c1943c4</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 467b9e9</t>
         </is>
       </c>
     </row>
@@ -30362,7 +30658,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Loads Avatar-New.glb (246k tris, 2×4096² maps) by default; Avatar3 only with ?avatar=old.</t>
+          <t>Loads Avatar-New.glb (119,993 tris since 3536dc8, 2×4096² maps) by default; Avatar3 only with ?avatar=old.</t>
         </is>
       </c>
       <c r="E12" s="5">
@@ -30411,7 +30707,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Ambient only; REG is 1.94M tris on desktop and skipped on mobile.</t>
+          <t>Ambient only; REG loads on every device as NPC.REG.lite.glb (60,410 tris; phones 31,096) since PLN-01, not the 1.94M original.</t>
         </is>
       </c>
       <c r="E13" s="5">
@@ -30460,7 +30756,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Mold tools place flora/hills/rocks/tipis; building panel is list-only; 3 tipi clones of a 246k-tri model.</t>
+          <t>Mold tools place flora/hills/rocks/tipis; building panel is list-only; 3 tipi clones of the 40,000-tri lite model (phones 14,998) since PLN-02.</t>
         </is>
       </c>
       <c r="E14" s="5">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -47,9 +47,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'60_Plan'!$A$4:$H$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'64_Next_Plan'!$A$4:$L$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'65_Team_Seats'!$A$4:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'64_Next_Plan'!$A$4:$L$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'65_Team_Seats'!$A$4:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'66_Owner_Decisions'!$A$4:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'70_Session_Log'!$A$4:$E$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
@@ -623,7 +623,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 467b9e9. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit a88d9b2. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L330; js/sanctuary/SanctuaryControls.js:L349</t>
+          <t>js/sanctuary/SanctuaryControls.js:L335; js/sanctuary/SanctuaryControls.js:L354</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryControls.js:L149; js/sanctuary/SanctuaryControls.js:L364</t>
+          <t>js/sanctuary/SanctuaryControls.js:L149; js/sanctuary/SanctuaryControls.js:L369</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit 467b9e9.</t>
+          <t>Built at commit a88d9b2.</t>
         </is>
       </c>
     </row>
@@ -17175,7 +17175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21235,8 +21235,55 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>ATT-95</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Claude (researcher / coder 3)</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Camera (Mark: 'make sure avatar is always centered in top down')</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>b88798a: in Village View the camera sits straight above her every frame (SanctuaryKeyboardLook update, after Avatar and ClickToMove), at SanctuaryZoom's height with the old 0.1 m offset and north-up view; opening Village View starts above her instead of (0, 0) (SanctuaryControls._toggleTopDown). No easing, no allocation.</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Done: headless Chromium 153 (SwiftShader) on Mark's tree: she projects to screen centre (0.000, 0.000) right after opening Village View 15 m from the origin and after moving 25 m; no page errors. Not yet seen by Mark.</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/SanctuaryKeyboardLook.js, js/sanctuary/SanctuaryControls.js</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Village View can no longer show the far side of the village without walking there; P1-T7's recentre button becomes unnecessary unless a free pan is added later.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I91"/>
+  <autoFilter ref="A4:I92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21247,7 +21294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21575,7 +21622,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>P1-H1</t>
+          <t>UA-1</t>
         </is>
       </c>
       <c r="B9" s="19" t="n">
@@ -21583,7 +21630,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
@@ -21591,12 +21638,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Hex math module</t>
+          <t>Three style frames: Village View with the Tier-1 set (code-built prototypes), the Build drawer on a phone, placing a drying rack</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>P1_1 §P1-H1</t>
+          <t>00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -21606,17 +21653,17 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryHex.js</t>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/UA-1/ (no game files)</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Round trip at 1,000 tiles; tipi 1 (18, -2) in tile (2, 0); debug dots sit in tile centres</t>
+          <t>Real renders and real CSS, phone and desktop</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark approves the look before UA-2 lands; partner sees buildings and motifs</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -21626,14 +21673,14 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>PLN-31</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>P1-H2</t>
+          <t>UA-2</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
@@ -21641,7 +21688,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
@@ -21649,32 +21696,32 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Occupancy, collision by circles</t>
+          <t>Design tokens + components + UI gallery</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>P1_1 §P1-H2</t>
+          <t>00_UI_AND_ART_PLAN §3</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>P1-H1</t>
+          <t>UA-1</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryHexOccupancy.js</t>
+          <t>new css/sanctuary-ui.css; new tools/ui-gallery.html; vendor/fonts</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>The pond tile and its 6 neighbours read water; tile (2, 0) lists tipi 1; rebuild &lt;= 1 ms</t>
+          <t>axe contrast check passes; 64 px targets measured; text works at 200 %</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark (visible)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -21684,14 +21731,14 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>PLN-31</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>P1-H3</t>
+          <t>UA-3</t>
         </is>
       </c>
       <c r="B11" s="19" t="n">
@@ -21699,7 +21746,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -21707,32 +21754,32 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillageRules.canPlace (protocol signature, icons, slope rule)</t>
+          <t>Icons v1: 9 picture reasons, tray, tabs (SVG sprite + WebGL reasons atlas)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>P1_1 §P1-H3; protocol §3</t>
+          <t>00_UI_AND_ART_PLAN §3; P1_3 §P1-T3</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>P1-H2</t>
+          <t>UA-1</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryVillageRules.js</t>
+          <t>new Assets/ui/icons.svg; Assets/ui/reasons.png + reasons.json</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Refuses water, tipis, the lodge disk and slopes with the right icon; &lt;= 0.1 ms a call</t>
+          <t>Readable at 32 px; meaning never by colour alone</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -21742,14 +21789,14 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>PLN-31</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>P1-D0</t>
+          <t>P1-H1</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
@@ -21757,7 +21804,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -21765,12 +21812,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>SanctuarySave: one save writer with sections, autosave, save code</t>
+          <t>Hex math module</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>PH1_SEAT_B item 1; protocol §3</t>
+          <t>P1_1 §P1-H1</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -21780,12 +21827,12 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuarySave.js; SanctuaryControls.js</t>
+          <t>new js/sanctuary/SanctuaryHex.js</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Sections round-trip; the previous save is kept; QuotaExceededError caught</t>
+          <t>Round trip at 1,000 tiles; tipi 1 (18, -2) in tile (2, 0); debug dots sit in tile centres</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -21800,14 +21847,14 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>PLN-32</t>
+          <t>PLN-31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>P1-D1</t>
+          <t>P1-H2</t>
         </is>
       </c>
       <c r="B13" s="19" t="n">
@@ -21815,7 +21862,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
@@ -21823,27 +21870,27 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BUILDING_TYPES data</t>
+          <t>Occupancy, collision by circles</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>P1_2 §P1-D1</t>
+          <t>P1_1 §P1-H2</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>P1-D0</t>
+          <t>P1-H1</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/data/buildingTypes.js</t>
+          <t>new js/sanctuary/SanctuaryHexOccupancy.js</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>typeDef('tipi').tiers[0].platformM === 4.7; disabled types never shown</t>
+          <t>The pond tile and its 6 neighbours read water; tile (2, 0) lists tipi 1; rebuild &lt;= 1 ms</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -21858,14 +21905,14 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>PLN-32</t>
+          <t>PLN-31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>P1-D2</t>
+          <t>P1-H3</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
@@ -21873,7 +21920,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
@@ -21881,34 +21928,34 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>strings.en.js + t(), with an approved flag per entry</t>
+          <t>SanctuaryVillageRules.canPlace (protocol signature, icons, slope rule)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>P1_2 §P1-D2</t>
+          <t>P1_1 §P1-H3; protocol §3</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
+          <t>P1-H2</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>new js/sanctuary/SanctuaryVillageRules.js</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Refuses water, tipis, the lodge disk and slopes with the right icon; &lt;= 0.1 ms a call</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>new js/sanctuary/data/strings.en.js</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>grep finds no builder sentence left in code</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -21916,14 +21963,14 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>PLN-32</t>
+          <t>PLN-31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>P1-D3</t>
+          <t>P1-D0</t>
         </is>
       </c>
       <c r="B15" s="19" t="n">
@@ -21939,27 +21986,27 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildings registry (VB1-P10)</t>
+          <t>SanctuarySave: one save writer with sections, autosave, save code</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>P1_2 §P1-D3</t>
+          <t>PH1_SEAT_B item 1; protocol §3</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>P1-D1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryBuildings.js</t>
+          <t>new js/sanctuary/SanctuarySave.js; SanctuaryControls.js</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Map 1 lists 3 tipis + dock + pool; placing or deleting a tipi updates the list</t>
+          <t>Sections round-trip; the previous save is kept; QuotaExceededError caught</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -21981,7 +22028,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>P1-D4</t>
+          <t>P1-D1</t>
         </is>
       </c>
       <c r="B16" s="19" t="n">
@@ -21997,27 +22044,27 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Save v2 (additive) + tests 1-7</t>
+          <t>BUILDING_TYPES data</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>P1_2 §P1-D4</t>
+          <t>P1_2 §P1-D1</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>P1-D0, P1-D3</t>
+          <t>P1-D0</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>SanctuarySave.js; tests/v4-village-save.spec.js</t>
+          <t>new js/sanctuary/data/buildingTypes.js</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Tests 1-7 pass; a save from ac6f316 loads with nothing lost</t>
+          <t>typeDef('tipi').tiers[0].platformM === 4.7; disabled types never shown</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -22039,7 +22086,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>VB1-P9</t>
+          <t>P1-D2</t>
         </is>
       </c>
       <c r="B17" s="19" t="n">
@@ -22055,27 +22102,27 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Autosave + remember the map</t>
+          <t>strings.en.js + t(), with an approved flag per entry</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P9</t>
+          <t>P1_2 §P1-D2</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>P1-D0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryToolPalette.js (load() map restore only)</t>
+          <t>new js/sanctuary/data/strings.en.js</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Place items, switch to map 3, reload without SAVE: items and map 3 are back</t>
+          <t>grep finds no builder sentence left in code</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -22097,7 +22144,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>P1-D5</t>
+          <t>P1-D3</t>
         </is>
       </c>
       <c r="B18" s="19" t="n">
@@ -22113,12 +22160,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Door facing from data; report east</t>
+          <t>SanctuaryBuildings registry (VB1-P10)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>P1_2 §P1-D5</t>
+          <t>P1_2 §P1-D3</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -22128,12 +22175,12 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/data/buildingTypes.js</t>
+          <t>new js/sanctuary/SanctuaryBuildings.js</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Report gives the east vector and today's tipi door directions; nothing re-turned</t>
+          <t>Map 1 lists 3 tipis + dock + pool; placing or deleting a tipi updates the list</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -22155,7 +22202,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>P1-T5</t>
+          <t>P1-D4</t>
         </is>
       </c>
       <c r="B19" s="19" t="n">
@@ -22163,7 +22210,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -22171,32 +22218,32 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>60° turns; tipis don't turn</t>
+          <t>Save v2 (additive) + tests 1-7</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>P1_3 §P1-T5</t>
+          <t>P1_2 §P1-D4</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>VB1-W6</t>
+          <t>P1-D0, P1-D3</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>SanctuarySelect.js (ROT_STEP_RAD = PI/3)</t>
+          <t>SanctuarySave.js; tests/v4-village-save.spec.js</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>No ↻ for tipis; 6 taps make a full turn</t>
+          <t>Tests 1-7 pass; a save from ac6f316 loads with nothing lost</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>OD-10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -22206,14 +22253,14 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>PLN-33</t>
+          <t>PLN-32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>P1-T1</t>
+          <t>VB1-P9</t>
         </is>
       </c>
       <c r="B20" s="19" t="n">
@@ -22221,7 +22268,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -22229,32 +22276,32 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Fixed tray (64 px, finger-up, keys); W6's bar docks into it</t>
+          <t>Autosave + remember the map</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>P1_3 §P1-T1</t>
+          <t>village-builder-phase1-prompt P9</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>VB1-W6</t>
+          <t>P1-D0</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryPlaceTray.js; SanctuarySelect.js</t>
+          <t>SanctuaryToolPalette.js (load() map restore only)</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Sizes measured; keyboard-only placement; FND-49 probe passes</t>
+          <t>Place items, switch to map 3, reload without SAVE: items and map 3 are back</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>OD-11; Mark (visible)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -22264,14 +22311,14 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>PLN-33</t>
+          <t>PLN-32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VB1-P5</t>
+          <t>P1-D5</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
@@ -22279,7 +22326,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -22287,27 +22334,27 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Ghost, tap-tap-tick and picture reasons (P1-T2, P1-T3)</t>
+          <t>Door facing from data; report east</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P5; P1_3 §P1-T2, P1-T3</t>
+          <t>P1_2 §P1-D5</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>P1-H3, P1-T1</t>
+          <t>P1-D1</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryPlaceIcons.js; ghost; SanctuaryClickToMove.js (Village View branch)</t>
+          <t>js/sanctuary/data/buildingTypes.js</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>A tipi placed with three taps on the phone 3x profile; every refusal shows its picture</t>
+          <t>Report gives the east vector and today's tipi door directions; nothing re-turned</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -22322,14 +22369,14 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>PLN-33</t>
+          <t>PLN-32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>VB1-P6</t>
+          <t>UA-4</t>
         </is>
       </c>
       <c r="B22" s="19" t="n">
@@ -22337,7 +22384,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -22345,32 +22392,32 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Undo, 20 steps, + undo chip (P1-T4)</t>
+          <t>Phase 1 skin: tray, undo chip, ghost tints, lodge ring (Seats C and A wire it)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P6; P1_3 §P1-T4</t>
+          <t>00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>VB1-W5</t>
+          <t>UA-2, UA-3</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryMutations.js; SanctuaryPlaceTray.js</t>
+          <t>css/sanctuary-ui.css (classes, tints)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Place, move, delete, then undo x3: back to the start</t>
+          <t>Screenshots on phone-3x and desktop; FND-49 probes pass; fps unchanged</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark (visible)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -22380,14 +22427,14 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>PLN-33</t>
+          <t>PLN-42, PLN-33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VB1-P2-3-8-11</t>
+          <t>P1-T5</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
@@ -22403,32 +22450,32 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Clear, Generate (fixed seed), caps, Village View hint</t>
+          <t>60° turns; tipis don't turn</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P2, P3, P8, P11</t>
+          <t>P1_3 §P1-T5</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>P1-H3, P1-D2</t>
+          <t>VB1-W6</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryMutations.js; SanctuaryToolPalette.js (buttons only)</t>
+          <t>SanctuarySelect.js (ROT_STEP_RAD = PI/3)</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Generate twice: identical, nothing in the pond, dock, tipis or pad; the 201st rock is refused</t>
+          <t>No ↻ for tipis; 6 taps make a full turn</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-10</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -22445,7 +22492,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>P1-T6-8</t>
+          <t>P1-T1</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
@@ -22461,32 +22508,32 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Next/previous spot, zoom while placing, reduced motion</t>
+          <t>Fixed tray (64 px, finger-up, keys); W6's bar docks into it</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>P1_3 §P1-T6, T7, T8</t>
+          <t>P1_3 §P1-T1</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>P1-T1, P1-H1</t>
+          <t>VB1-W6, UA-4</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryPlaceTray.js; SanctuaryControls.js (zoom only)</t>
+          <t>new js/sanctuary/SanctuaryPlaceTray.js; SanctuarySelect.js</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Tab + Enter placement; tiles &gt;= 64 CSS px while placing; nothing eases under reduced motion</t>
+          <t>Sizes measured; keyboard-only placement; FND-49 probe passes</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-11; Mark (visible)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -22503,7 +22550,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>P1-H5</t>
+          <t>VB1-P5</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
@@ -22511,7 +22558,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -22519,27 +22566,27 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Map layouts as data</t>
+          <t>Ghost, tap-tap-tick and picture reasons (P1-T2, P1-T3)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>P1_1 §P1-H5</t>
+          <t>village-builder-phase1-prompt P5; P1_3 §P1-T2, P1-T3</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>VB1-W3</t>
+          <t>P1-H3, P1-T1, UA-3, UA-4</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/data/mapLayouts.js; SanctuaryTipis.js (anchor lookup only)</t>
+          <t>new js/sanctuary/SanctuaryPlaceIcons.js; ghost; SanctuaryClickToMove.js (Village View branch)</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Tipi positions and yaws identical on all 5 maps</t>
+          <t>A tipi placed with three taps on the phone 3x profile; every refusal shows its picture</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -22554,14 +22601,14 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>PLN-31</t>
+          <t>PLN-33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>P1-H4</t>
+          <t>VB1-P6</t>
         </is>
       </c>
       <c r="B26" s="19" t="n">
@@ -22569,7 +22616,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -22577,32 +22624,32 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Reserve Yellow Butterfly's lodge ground + faint ring</t>
+          <t>Undo, 20 steps, + undo chip (P1-T4)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>P1_1 §P1-H4</t>
+          <t>village-builder-phase1-prompt P6; P1_3 §P1-T4</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>P1-H3, P1-H5</t>
+          <t>VB1-W5</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>mapLayouts.js; SanctuaryVillageRules.js; ring helper</t>
+          <t>SanctuaryMutations.js; SanctuaryPlaceTray.js</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Ring shows in Village View on maps 1 and 2; tree, rock and tipi refused inside, flower allowed</t>
+          <t>Place, move, delete, then undo x3: back to the start</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>OD-03 (default in use)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -22612,14 +22659,14 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>PLN-31</t>
+          <t>PLN-33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>VB1-P7</t>
+          <t>VB1-P2-3-8-11</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
@@ -22627,7 +22674,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -22635,32 +22682,32 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Hills are real ground</t>
+          <t>Clear, Generate (fixed seed), caps, Village View hint</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P7</t>
+          <t>village-builder-phase1-prompt P2, P3, P8, P11</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>P1-H3</t>
+          <t>P1-H3, P1-D2</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryGround.js (height + terrain update only); MoldGrowHill.js</t>
+          <t>SanctuaryMutations.js; SanctuaryToolPalette.js (buttons only)</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Walk over a hill smoothly; trees sit on the slope; the grass follows</t>
+          <t>Generate twice: identical, nothing in the pond, dock, tipis or pad; the 201st rock is refused</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Grass owner + Compassion holder sign off</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -22670,14 +22717,14 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>PLN-31</t>
+          <t>PLN-33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>R-P1</t>
+          <t>P1-T6-8</t>
         </is>
       </c>
       <c r="B28" s="19" t="n">
@@ -22685,7 +22732,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -22693,32 +22740,32 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Land Phase 1 in order; phase test; Mark plays it</t>
+          <t>Next/previous spot, zoom while placing, reduced motion</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>prompts/REVIEWER_R.md</t>
+          <t>P1_3 §P1-T6, T7, T8</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>all Phase 1 items</t>
+          <t>P1-T1, P1-H1</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>tools/decision-engine/build_engine.py (rows only)</t>
+          <t>SanctuaryPlaceTray.js; SanctuaryControls.js (zoom only)</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Phone 3x holds 60 fps in Village View; every Phase 1 'Proves it' passes</t>
+          <t>Tab + Enter placement; tiles &gt;= 64 CSS px while placing; nothing eases under reduced motion</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Mark plays it</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -22728,22 +22775,22 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>PLN-31, PLN-32, PLN-33, PLN-41</t>
+          <t>PLN-33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>P2-B1</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>2</v>
+          <t>P1-H5</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -22751,32 +22798,32 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Fishery F0-F2: tree registry, one inventory with wood, villager clicks, chop, logs, carry</t>
+          <t>Map layouts as data</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B1; fishery-quest-spec F0-F2</t>
+          <t>P1_1 §P1-H5</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>VB1-W3</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>new SanctuaryTrees.js, SanctuaryChop.js; SanctuaryInventory.js; SanctuaryClickToMove.js (talk and tree clicks)</t>
+          <t>new js/sanctuary/data/mapLayouts.js; SanctuaryTipis.js (anchor lookup only)</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Fishery F0-F2 proofs; 10 chopped trees add &lt;= 4 draw calls</t>
+          <t>Tipi positions and yaws identical on all 5 maps</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Compassion holder: read-only pond-tree hook</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -22786,18 +22833,18 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>PLN-34</t>
+          <t>PLN-31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>P2-F1</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
-        <v>2</v>
+          <t>P1-H4</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -22809,32 +22856,32 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Play-time clock (evening = the moon button or 8 play-minutes)</t>
+          <t>Reserve Yellow Butterfly's lodge ground + faint ring</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F1</t>
+          <t>P1_1 §P1-H4</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>P1-H3, P1-H5, UA-4</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryClock.js</t>
+          <t>mapLayouts.js; SanctuaryVillageRules.js; ring helper</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>A hidden tab advances nothing; the same actions give the same ticks</t>
+          <t>Ring shows in Village View on maps 1 and 2; tree, rock and tipi refused inside, flower allowed</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>OD-18</t>
+          <t>OD-03 (default in use)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -22844,18 +22891,18 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>P2-F2</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>2</v>
+          <t>VB1-P7</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -22867,32 +22914,32 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Food data + SanctuaryFood store</t>
+          <t>Hills are real ground</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F2</t>
+          <t>village-builder-phase1-prompt P7</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>P2-F1</t>
+          <t>P1-H3</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/data/{items,crops,recipes}.js; js/sanctuary/SanctuaryFood.js</t>
+          <t>js/sanctuary/SanctuaryGround.js (height + terrain update only); MoldGrowHill.js</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Unit tests for plant, grow, harvest, dry, cook and store</t>
+          <t>Walk over a hill smoothly; trees sit on the slope; the grass follows</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grass owner + Compassion holder sign off</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -22902,22 +22949,22 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>P2-K1</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="n">
-        <v>2</v>
+          <t>UA-Q1</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -22925,34 +22972,34 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Light villager rig (&lt;= 2,500 tris, 25-30 bones, clips) (M3)</t>
+          <t>Phase 1 visual QA, before R's phase test</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K1; P2_5 §3.8</t>
+          <t>00_UI_AND_ART_PLAN §7</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
+          <t>all Phase 1 items</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>new js/sanctuary/SanctuaryVillagerRig.js; Assets/villager/</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>No pop at screen edges; counts in the commit; placeholder never shipped</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>OD-25; asset from Mark or an artist; partner (clothing)</t>
-        </is>
-      </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
@@ -22960,22 +23007,22 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>P2-K3-4</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="n">
-        <v>2</v>
+          <t>R-P1</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -22983,32 +23030,32 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Villager brain (7 states, play-time step, seeded RNG); home and wander</t>
+          <t>Land Phase 1 in order; phase test; Mark plays it</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K3, K4</t>
+          <t>prompts/REVIEWER_R.md</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>P2-F1, P1-H2</t>
+          <t>all Phase 1 items</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryVillagers.js</t>
+          <t>tools/decision-engine/build_engine.py (rows only)</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>The same seed gives the same wander after a reload; nobody walks into the pond or the lodge ring</t>
+          <t>Phone 3x holds 60 fps in Village View; every Phase 1 'Proves it' passes</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark plays it</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -23018,14 +23065,14 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-31, PLN-32, PLN-33, PLN-41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>P2-K5-6</t>
+          <t>P2-B1</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -23033,7 +23080,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -23041,32 +23088,32 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Hex paths and work slots (claim / release)</t>
+          <t>Fishery F0-F2: tree registry, one inventory with wood, villager clicks, chop, logs, carry</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K5, K6</t>
+          <t>P2_1 §P2-B1; fishery-quest-spec F0-F2</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>P2-K3-4</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryVillagerPaths.js</t>
+          <t>new SanctuaryTrees.js, SanctuaryChop.js; SanctuaryInventory.js; SanctuaryClickToMove.js (talk and tree clicks)</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>A path across the village in &lt;= 1 ms; two plans never share a slot</t>
+          <t>Fishery F0-F2 proofs; 10 chopped trees add &lt;= 4 draw calls</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Compassion holder: read-only pond-tree hook</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -23076,14 +23123,14 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>P2-K2-10</t>
+          <t>P2-F1</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -23091,7 +23138,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -23099,32 +23146,32 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Hero villagers cross-fade to walk; seatAt / seatOnGround</t>
+          <t>Play-time clock (evening = the moon button or 8 play-minutes)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K2, K10</t>
+          <t>P2_4 §P2-F1</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>P2-K1</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryTipiNpcs.js (seating API only)</t>
+          <t>new js/sanctuary/SanctuaryClock.js</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Red Eagle Girl walks, hammers and sits again; nobody floats after a take-down</t>
+          <t>A hidden tab advances nothing; the same actions give the same ticks</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>OD-14</t>
+          <t>OD-18</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -23134,14 +23181,14 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>P2-B3</t>
+          <t>P2-F2</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -23149,7 +23196,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -23157,32 +23204,32 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Quests and requests as data; wish baskets (fishery F3, P2-F7)</t>
+          <t>Food data + SanctuaryFood store</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B3; P2_4 §P2-F7; fishery-quest-spec F3</t>
+          <t>P2_4 §P2-F2</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>P2-B1</t>
+          <t>P2-F1</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>new SanctuaryQuests.js, quests/*.js, SanctuaryQuestMarkers.js, SanctuaryDialogue.js</t>
+          <t>new js/sanctuary/data/{items,crops,recipes}.js; js/sanctuary/SanctuaryFood.js</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>The 2-tree loop works from a fresh save; no wish expires with a penalty</t>
+          <t>Unit tests for plant, grow, harvest, dry, cook and store</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Partner + Mark (dialogue, names)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -23192,14 +23239,14 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>PLN-34</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>UA-6</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -23207,7 +23254,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -23215,32 +23262,32 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Parts library + shared village atlas + plan material + aStage reveal</t>
+          <t>Villager art brief + test proxy for Seat D (M3)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §2, §4, §5</t>
+          <t>P2_5 §3.8; 00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>UA-1</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/buildings/parts.js; Assets/village/atlas_*.png</t>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/UA-6/ (brief); Assets/villager/ (test proxy only)</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>One material for every Tier-1 building; 2 draw calls while building, 1 when built</t>
+          <t>The proxy never ships</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Mark sees the atlas</t>
+          <t>OD-25; partner (clothing, hair)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -23250,14 +23297,14 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>PLN-40</t>
+          <t>PLN-42, PLN-35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -23265,7 +23312,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -23273,32 +23320,32 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Drying rack model (20 hooks, 4 stages)</t>
+          <t>Parts library + shared village atlas + plan material + aStage reveal</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.1</t>
+          <t>P2_5 §2, §4, §5</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/buildings/dryingRack.js</t>
+          <t>new js/sanctuary/buildings/models/parts.js; Assets/village/atlas_*.png; Assets/village/PROVENANCE.md; new tools/model-gallery.html</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>&lt;= 1,500 tris, &lt;= 3 draw calls; fish turn silver to gold</t>
+          <t>One material for every Tier-1 building; 2 draw calls while building, 1 when built</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Partner + Mark</t>
+          <t>Mark sees the atlas</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -23315,7 +23362,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>P2-B2</t>
+          <t>UA-5</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -23323,7 +23370,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -23331,32 +23378,32 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Lifecycle plan → building → built → taken down; drying rack (fishery F4)</t>
+          <t>Item pictures, portrait frames, smoke / steam / flame sprites</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B2; fishery-quest-spec F4</t>
+          <t>00_UI_AND_ART_PLAN §3, §5</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>P2-B3, M2, P1-H3</t>
+          <t>UA-2, M1</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>new SanctuaryBuildingLifecycle.js; buildings/dryingRack.js</t>
+          <t>Assets/ui/items/*.png; Assets/ui/ (portrait frames); Assets/village/ (effects atlas)</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Plan, move, build, take down (full refund), rebuild, undo; reload resumes at every step</t>
+          <t>One atlas each; card budget kept</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Mark (visible)</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -23366,14 +23413,14 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>PLN-34</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -23381,7 +23428,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -23389,12 +23436,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Cooking fire, food cache, garden bed and play area models</t>
+          <t>Drying rack model (20 hooks, 4 stages)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.2-3.5</t>
+          <t>P2_5 §3.1</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -23404,17 +23451,17 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/buildings/{cookingFire,foodCache,garden,playArea}.js</t>
+          <t>js/sanctuary/buildings/models/dryingRack.js</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Each &lt;= 1,500 tris and &lt;= 3 draw calls, with its slots and 4 stages</t>
+          <t>&lt;= 1,500 tris, &lt;= 3 draw calls; fish turn silver to gold</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Partner + Mark (play-area games especially)</t>
+          <t>Partner + Mark</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -23431,7 +23478,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>P2-K1</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -23439,7 +23486,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -23447,32 +23494,32 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Lighter home tipi for player-built homes (&lt;= 8,000 tris, plain cover)</t>
+          <t>Light villager rig (&lt;= 2,500 tris, 25-30 bones, clips) (M3)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.6</t>
+          <t>P2_2 §P2-K1; P2_5 §3.8</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>UA-6</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Assets/Tipi.home/tipi_t1_home.glb + .mobile.glb; buildingTypes.js</t>
+          <t>new js/sanctuary/SanctuaryVillagerRig.js; Assets/villager/</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Same silhouette, &lt;= 8,000 tris; the 3 starting tipis unchanged</t>
+          <t>No pop at screen edges; counts in the commit; placeholder never shipped</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>OD-24; Mark (visible) + partner (cover)</t>
+          <t>OD-25; asset from Mark, an artist or Seat U; partner (clothing)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -23482,14 +23529,14 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>PLN-40</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>P2-F4-6</t>
+          <t>P2-K3-4</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -23497,7 +23544,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
@@ -23505,27 +23552,27 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Drying rack, food cache and cooking fire behaviour; one shared smoke system</t>
+          <t>Villager brain (7 states, play-time step, seeded RNG); home and wander</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F4, F5, F6</t>
+          <t>P2_2 §P2-K3, K4</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>P2-F2, P2-B2, M4</t>
+          <t>P2-F1, P1-H2</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>building modules; new js/sanctuary/SanctuarySmoke.js</t>
+          <t>new js/sanctuary/SanctuaryVillagers.js</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>An empty cache still gives an evening meal; all smoke costs 1 draw call</t>
+          <t>The same seed gives the same wander after a reload; nobody walks into the pond or the lodge ring</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -23540,14 +23587,14 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>P2-B5</t>
+          <t>P2-K5-6</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -23555,7 +23602,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -23563,32 +23610,32 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>12-building cap; Tier-1 checklist → unlocks.tier2; tree regrowth (fishery F5-F6)</t>
+          <t>Hex paths and work slots (claim / release)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B5; fishery-quest-spec F5-F6</t>
+          <t>P2_2 §P2-K5, K6</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>P2-B2</t>
+          <t>P2-K3-4</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildings.js; SanctuarySave sections</t>
+          <t>new js/sanctuary/SanctuaryVillagerPaths.js</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>13th building refused; the unlock survives a take-down; trees regrow after 10 play-minutes</t>
+          <t>A path across the village in &lt;= 1 ms; two plans never share a slot</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>OD-04, OD-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -23598,14 +23645,14 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>PLN-34</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>P2-F3</t>
+          <t>P2-K2-10</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -23613,7 +23660,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
@@ -23621,32 +23668,32 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Garden: 10 hills, crops in their own rows, instanced plants, plot picking</t>
+          <t>Hero villagers cross-fade to walk; seatAt / seatOnGround</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F3</t>
+          <t>P2_2 §P2-K2, K10</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>P2-F2, M4</t>
+          <t>P2-K1</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryGarden.js</t>
+          <t>SanctuaryTipiNpcs.js (seating API only)</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>&lt;= 8 draw calls; 10 taps harvest 10 hills on phone 3x</t>
+          <t>Red Eagle Girl walks, hammers and sits again; nobody floats after a take-down</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>OD-16</t>
+          <t>OD-14</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -23656,14 +23703,14 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>P2-F8</t>
+          <t>P2-B3</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -23671,7 +23718,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -23679,32 +23726,32 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Story seasons and moons; seasonal events as data, off until approved</t>
+          <t>Quests and requests as data; wish baskets (fishery F3, P2-F7)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F8</t>
+          <t>P2_1 §P2-B3; P2_4 §P2-F7; fishery-quest-spec F3</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>P2-F1</t>
+          <t>P2-B1</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/data/seasons.js; SanctuaryClock.js</t>
+          <t>new SanctuaryQuests.js, quests/*.js, SanctuaryQuestMarkers.js, SanctuaryDialogue.js</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Full cache + yes: winter feast, snow, spring; no: autumn stays</t>
+          <t>The 2-tree loop works from a fresh save; no wish expires with a penalty</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>OD-17, OD-19, OD-20; partner (moon names)</t>
+          <t>Partner + Mark (dialogue, names)</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -23714,14 +23761,14 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-34</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>P2-F9</t>
+          <t>P2-B2</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -23729,7 +23776,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
@@ -23737,32 +23784,32 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Hearts that never fall + found-things list</t>
+          <t>Lifecycle plan → building → built → taken down; drying rack (fishery F4)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F9</t>
+          <t>P2_1 §P2-B2; fishery-quest-spec F4</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>P2-F2</t>
+          <t>P2-B3, M2, P1-H3</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryHearts.js</t>
+          <t>new SanctuaryBuildingLifecycle.js; js/sanctuary/buildings/dryingRack.js (behaviour, with Seat U's createModel)</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>No heart count ever drops; milestones add life to the village</t>
+          <t>Plan, move, build, take down (full refund), rebuild, undo; reload resumes at every step</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark (visible)</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -23772,14 +23819,14 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>P2-F10</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -23787,7 +23834,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -23795,32 +23842,32 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Save v3 food sections + v2 → v3 migration</t>
+          <t>Cooking fire, food cache, garden bed and play area models</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F10</t>
+          <t>P2_5 §3.2-3.5</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>P1-D0</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Seat A modules (SanctuarySave.register)</t>
+          <t>js/sanctuary/buildings/models/{cookingFire,foodCache,garden,playArea}.js (+ the crop meshes for Seat A)</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>A v2 save loads with empty stores; reload resumes at every step</t>
+          <t>Each &lt;= 1,500 tris and &lt;= 3 draw calls, with its slots and 4 stages</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>OD-21, OD-22</t>
+          <t>Partner + Mark (play-area games especially)</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -23830,14 +23877,14 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-40</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>P2-K7-9</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -23845,7 +23892,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
@@ -23853,32 +23900,32 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Who comes; carrying logs; hammer-synced reveal; finishing moments</t>
+          <t>Lighter home tipi for player-built homes (&lt;= 8,000 tris, plain cover)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K7, K8, K9</t>
+          <t>P2_5 §3.6</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>P2-B2, P2-K5-6</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js (site.addWork hook agreed with Seat B)</t>
+          <t>Assets/Tipi.home/tipi_t1_home.glb + .mobile.glb; buildingTypes.js</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>4 visible stages; help-hammer finishes sooner; 8 s self-build fallback works</t>
+          <t>Same silhouette, &lt;= 8,000 tris; the 3 starting tipis unchanged</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-24; Mark (visible) + partner (cover)</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -23888,14 +23935,14 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-40</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>P2-K12-13</t>
+          <t>P2-F4-6</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -23903,7 +23950,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -23911,32 +23958,32 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Friendship hearts (no decay); families of 2-3 arrive (cap 20)</t>
+          <t>Drying rack, food cache and cooking fire behaviour; one shared smoke system</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K12, K13</t>
+          <t>P2_4 §P2-F4, F5, F6</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>P2-K3-4</t>
+          <t>P2-F2, P2-B2, M4, UA-5</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js + data</t>
+          <t>js/sanctuary/buildings/&lt;type&gt;.js (behaviour); new js/sanctuary/SanctuarySmoke.js (Seat U's sprites)</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Hearts never drop; a family arrives after a tipi is built</t>
+          <t>An empty cache still gives an evening meal; all smoke costs 1 draw call</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Partner (names)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -23946,14 +23993,14 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>P2-K11</t>
+          <t>P2-B5</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -23961,7 +24008,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
@@ -23969,32 +24016,32 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Villager save section (logical state only)</t>
+          <t>12-building cap; Tier-1 checklist → unlocks.tier2; tree regrowth (fishery F5-F6)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K11</t>
+          <t>P2_1 §P2-B5; fishery-quest-spec F5-F6</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>P1-D0</t>
+          <t>P2-B2</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js</t>
+          <t>SanctuaryBuildings.js; SanctuarySave sections</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Reload never loses, doubles or floats a villager</t>
+          <t>13th building refused; the unlock survives a take-down; trees regrow after 10 play-minutes</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-04, OD-06</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -24004,14 +24051,14 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-34</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5</t>
+          <t>P2-F3</t>
         </is>
       </c>
       <c r="B51" s="20" t="n">
@@ -24019,7 +24066,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -24027,32 +24074,32 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Build drawer shell, tabs, top bar, overflow menu</t>
+          <t>Garden: 10 hills, crops in their own rows, instanced plants, plot picking</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U1, U5</t>
+          <t>P2_4 §P2-F3</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>P2-F2, M4</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryBuildDrawer.js</t>
+          <t>new js/sanctuary/SanctuaryGarden.js</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Every old button has a home; FND-49 probe passes</t>
+          <t>&lt;= 8 draw calls; 10 taps harvest 10 hills on phone 3x</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>OD-13</t>
+          <t>OD-16</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -24062,14 +24109,14 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>PLN-36</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>P2-U4</t>
+          <t>P2-F8</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
@@ -24077,7 +24124,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
@@ -24085,32 +24132,32 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Look and contrast (measured colours, gold borders, focus ring, high contrast)</t>
+          <t>Story seasons and moons; seasonal events as data, off until approved</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U4</t>
+          <t>P2_4 §P2-F8</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5</t>
+          <t>P2-F1</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>drawer CSS</t>
+          <t>new js/sanctuary/data/seasons.js; SanctuaryClock.js</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Automated contrast check passes; screenshots normal and high contrast</t>
+          <t>Full cache + yes: winter feast, snow, spring; no: autumn stays</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Mark (visible)</t>
+          <t>OD-17, OD-19, OD-20; partner (moon names)</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -24120,14 +24167,14 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>PLN-36</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>P2-F9</t>
         </is>
       </c>
       <c r="B53" s="20" t="n">
@@ -24135,7 +24182,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
@@ -24143,27 +24190,27 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Card thumbnails from the final models</t>
+          <t>Hearts that never fall + found-things list</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §6</t>
+          <t>P2_4 §P2-F9</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>M2, M4</t>
+          <t>P2-F2</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Assets/ui/cards/*.png</t>
+          <t>new js/sanctuary/SanctuaryHearts.js</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>128 px @2x, &lt;= 20 KB each, all under 250 KB</t>
+          <t>No heart count ever drops; milestones add life to the village</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
@@ -24178,14 +24225,14 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>PLN-40</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>P2-U2-3</t>
+          <t>P2-F10</t>
         </is>
       </c>
       <c r="B54" s="20" t="n">
@@ -24193,7 +24240,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
@@ -24201,32 +24248,32 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Cards, info card, wish-basket chips</t>
+          <t>Save v3 food sections + v2 → v3 migration</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U2, U3; P2_4 §P2-F7</t>
+          <t>P2_4 §P2-F10</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5, P2-B3, M8</t>
+          <t>P1-D0</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>drawer; Assets/ui/cards/*.png</t>
+          <t>Seat A modules (SanctuarySave.register)</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>A screen reader reads each card's name, state and cost</t>
+          <t>A v2 save loads with empty stores; reload resumes at every step</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-21, OD-22</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -24236,14 +24283,14 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>PLN-36</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>P2-U6-8</t>
+          <t>P2-K7-9</t>
         </is>
       </c>
       <c r="B55" s="20" t="n">
@@ -24251,7 +24298,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -24259,27 +24306,27 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Announcer, voice labels, one-switch scan, reduced motion, little-helper mode</t>
+          <t>Who comes; carrying logs; hammer-synced reveal; finishing moments</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U6, U7, U8</t>
+          <t>P2_2 §P2-K7, K8, K9</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5</t>
+          <t>P2-B2, P2-K5-6</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryAnnouncer.js; drawer</t>
+          <t>SanctuaryVillagers.js (site.addWork hook agreed with Seat B)</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver and TalkBack walkthroughs; Switch Control places a drying rack</t>
+          <t>4 visible stages; help-hammer finishes sooner; 8 s self-build fallback works</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
@@ -24294,14 +24341,14 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>PLN-36</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>P2-U9</t>
+          <t>P2-K12-13</t>
         </is>
       </c>
       <c r="B56" s="20" t="n">
@@ -24309,7 +24356,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
@@ -24317,32 +24364,32 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Accessible building list replaces BuildingPanelUI</t>
+          <t>Friendship hearts (no decay); families of 2-3 arrive (cap 20)</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U9</t>
+          <t>P2_2 §P2-K12, K13</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>P1-D3</t>
+          <t>P2-K3-4</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>drawer (retire js/v2/BuildingPanelUI.js after parity)</t>
+          <t>SanctuaryVillagers.js + data</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>The list updates at once when a building is added or taken down</t>
+          <t>Hearts never drop; a family arrives after a tipi is built</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Partner (names)</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -24352,14 +24399,14 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>PLN-36</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>P2-U10</t>
+          <t>P2-K11</t>
         </is>
       </c>
       <c r="B57" s="20" t="n">
@@ -24367,7 +24414,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
@@ -24375,32 +24422,32 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Journal pages + grown-up save-code screen</t>
+          <t>Villager save section (logical state only)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U10</t>
+          <t>P2_2 §P2-K11</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>P2-F9, P1-D0</t>
+          <t>P1-D0</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>drawer</t>
+          <t>SanctuaryVillagers.js</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Pages fill as things are found; the save code round-trips</t>
+          <t>Reload never loses, doubles or floats a villager</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>OD-22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -24410,14 +24457,14 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>PLN-36</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>R-P2</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B58" s="20" t="n">
@@ -24425,7 +24472,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
@@ -24433,32 +24480,32 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Land Phase 2 in order; phase test; Mark plays it</t>
+          <t>Card thumbnails from the final models</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>prompts/REVIEWER_R.md</t>
+          <t>P2_5 §6</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>all Phase 2 items</t>
+          <t>M2, M4, M5</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>tools/decision-engine/build_engine.py (rows only)</t>
+          <t>Assets/ui/cards/*.png</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>20 villagers and every Tier-1 building: phone 3x holds 60 fps</t>
+          <t>128 px @2x, &lt;= 20 KB each, all under 250 KB</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Mark plays it; partner signs off names, dialogue and models</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -24468,22 +24515,22 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>PLN-34, PLN-35, PLN-36, PLN-37, PLN-40, PLN-41</t>
+          <t>PLN-40</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>P3-L5-7</t>
-        </is>
-      </c>
-      <c r="B59" s="21" t="n">
-        <v>3</v>
+          <t>P2-U1-5</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
@@ -24491,32 +24538,32 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>multiplier() drives slots; only the level is saved</t>
+          <t>Build drawer shell, tabs, top bar, overflow menu</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L5, L7</t>
+          <t>P2_3 §P2-U1, U5</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Phase 2</t>
+          <t>Phase 1, UA-2</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildings.js; building modules</t>
+          <t>new js/sanctuary/SanctuaryBuildDrawer.js</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>P1 save tests 1, 3 and 4 still pass</t>
+          <t>Every old button has a home; FND-49 probe passes</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>OD-02, OD-05</t>
+          <t>OD-13</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -24526,22 +24573,22 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-36</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6</t>
-        </is>
-      </c>
-      <c r="B60" s="21" t="n">
-        <v>3</v>
+          <t>P2-U4</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
@@ -24549,32 +24596,32 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Add a level (2, 2, 3, 3, 4, 4, 5, 5, 6 wood); full refund on take-down</t>
+          <t>Look and contrast (measured colours, gold borders, focus ring, high contrast)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L1, L6</t>
+          <t>P2_3 §P2-U4</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>P3-L5-7</t>
+          <t>P2-U1-5</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildingLifecycle.js</t>
+          <t>css/sanctuary-ui.css; drawer</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Level 1 → 10 costs 34 wood; the refund includes every level</t>
+          <t>Automated contrast check passes; screenshots normal and high contrast</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark (visible)</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -24584,22 +24631,22 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-36</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>P3-L3</t>
-        </is>
-      </c>
-      <c r="B61" s="21" t="n">
-        <v>3</v>
+          <t>P2-U2-3</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
@@ -24607,32 +24654,32 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Level props: one InstancedMesh per prop kind, 9 per building (M6)</t>
+          <t>Cards, info card, wish-basket chips</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L3; P2_5 §3</t>
+          <t>P2_3 §P2-U2, U3; P2_4 §P2-F7</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6, M1</t>
+          <t>P2-U1-5, P2-B3, M8, UA-5</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryBuildingProps.js</t>
+          <t>drawer; Assets/ui/cards/*.png</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>12 buildings at level 10 add &lt;= 9 draw calls</t>
+          <t>A screen reader reads each card's name, state and cost</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Mark (visible)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -24642,22 +24689,22 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-36</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>P3-L4</t>
-        </is>
-      </c>
-      <c r="B62" s="21" t="n">
-        <v>3</v>
+          <t>P2-U6-8</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
@@ -24665,27 +24712,27 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>One-second level celebration (+ reduced-motion version)</t>
+          <t>Announcer, voice labels, one-switch scan, reduced motion, little-helper mode</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L4</t>
+          <t>P2_3 §P2-U6, U7, U8</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6</t>
+          <t>P2-U1-5</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildingLifecycle.js</t>
+          <t>new js/sanctuary/SanctuaryAnnouncer.js; drawer</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Video with and without reduced motion; no allocations</t>
+          <t>VoiceOver and TalkBack walkthroughs; Switch Control places a drying rack</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -24700,22 +24747,22 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-36</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>P3-L2</t>
-        </is>
-      </c>
-      <c r="B63" s="21" t="n">
-        <v>3</v>
+          <t>P2-U9</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -24723,27 +24770,27 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Plain bead strip (two rows of five) + Add a level button</t>
+          <t>Accessible building list replaces BuildingPanelUI</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L2</t>
+          <t>P2_3 §P2-U9</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6</t>
+          <t>P1-D3</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>drawer</t>
+          <t>drawer (retire js/v2/BuildingPanelUI.js after parity)</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Level 7 reads as five and two at a glance</t>
+          <t>The list updates at once when a building is added or taken down</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -24758,22 +24805,22 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>P3-Y1-2</t>
-        </is>
-      </c>
-      <c r="B64" s="21" t="n">
-        <v>3</v>
+          <t>P2-U10</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
@@ -24781,32 +24828,32 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Checklist silhouettes; one invitation; Raise the big lodge button; skip control</t>
+          <t>Journal pages + grown-up save-code screen</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y1, Y2</t>
+          <t>P2_3 §P2-U10</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>P2-B5</t>
+          <t>P2-F9, P1-D0</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>drawer; SanctuaryDialogue.js</t>
+          <t>drawer</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>One invitation per save; the button follows the wood count</t>
+          <t>Pages fill as things are found; the save code round-trips</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>OD-04</t>
+          <t>OD-22</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
@@ -24816,22 +24863,22 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-36</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="B65" s="21" t="n">
-        <v>3</v>
+          <t>UA-Q2</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
@@ -24839,32 +24886,32 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Lodge model (&lt;= 40k tris, &lt;= 3 draw calls, plain sewn-hide cover)</t>
+          <t>Phase 2 visual QA, before R's phase test</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.7; P3_2 §P3-Y3</t>
+          <t>00_UI_AND_ART_PLAN §7</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>all Phase 2 items</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Assets/lodge/*.glb</t>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Tris, draw calls and phone memory in the commit</t>
+          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>OD-03, OD-25; partner + Mark</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -24874,22 +24921,22 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>P3-Y4-5</t>
-        </is>
-      </c>
-      <c r="B66" s="21" t="n">
-        <v>3</v>
+          <t>R-P2</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
@@ -24897,32 +24944,32 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>The swap (rim check, flat disk, shared GLB kept) + re-seat Yellow Butterfly</t>
+          <t>Land Phase 2 in order; phase test; Mark plays it</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y4, Y5</t>
+          <t>prompts/REVIEWER_R.md</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>M7, P2-K2-10</t>
+          <t>all Phase 2 items</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryTipis.js; ground hook; SanctuaryTipiNpcs.js</t>
+          <t>tools/decision-engine/build_engine.py (rows only)</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>No terrain through the platform on either layout; she sits at the new door after a reload</t>
+          <t>20 villagers and every Tier-1 building: phone 3x holds 60 fps</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Mark (pad and braziers inside the footprint)</t>
+          <t>Mark plays it; partner signs off names, dialogue and models</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -24932,14 +24979,14 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-34, PLN-35, PLN-36, PLN-37, PLN-40, PLN-41</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>P3-Y8-9</t>
+          <t>P3-L5-7</t>
         </is>
       </c>
       <c r="B67" s="21" t="n">
@@ -24947,7 +24994,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -24955,32 +25002,32 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Take down and move with the 8.0 m reservation; tiers 3-10 as data validation</t>
+          <t>multiplier() drives slots; only the level is saved</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y8, Y9</t>
+          <t>P3_1 §P3-L5, L7</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>P3-Y4-5</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildingLifecycle.js; SanctuaryVillageRules.js; buildingTypes.js</t>
+          <t>SanctuaryBuildings.js; building modules</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Rebuild elsewhere and raise again: it always fits; a fake tier-3 row changes no save</t>
+          <t>P1 save tests 1, 3 and 4 still pass</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>OD-15</t>
+          <t>OD-02, OD-05</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -24990,14 +25037,14 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-38</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>P3-Y6</t>
+          <t>P3-L1-6</t>
         </is>
       </c>
       <c r="B68" s="21" t="n">
@@ -25005,7 +25052,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
@@ -25013,32 +25060,32 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Raising celebration (&lt;= 10 s, skippable, cuts under reduced motion)</t>
+          <t>Add a level (2, 2, 3, 3, 4, 4, 5, 5, 6 wood); full refund on take-down</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y6</t>
+          <t>P3_1 §P3-L1, L6</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>P3-Y4-5, P2-K7-9</t>
+          <t>P3-L5-7</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryLodgeCelebration.js</t>
+          <t>SanctuaryBuildingLifecycle.js</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Skipping at any moment gives the same end state; a reload mid-way gives a built lodge</t>
+          <t>Level 1 → 10 costs 34 wood; the refund includes every level</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Partner + advisors (who raises it, any music)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -25048,14 +25095,14 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-38</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>P3-Y7</t>
+          <t>P3-L2</t>
         </is>
       </c>
       <c r="B69" s="21" t="n">
@@ -25063,7 +25110,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
@@ -25071,27 +25118,27 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Gathering place at the lodge's fire circle</t>
+          <t>Plain bead strip (two rows of five) + Add a level button</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y7</t>
+          <t>P3_1 §P3-L2</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>P3-Y6</t>
+          <t>P3-L1-6</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js</t>
+          <t>drawer</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Evening screenshot; still within 20 villagers</t>
+          <t>Level 7 reads as five and two at a glance</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -25106,14 +25153,14 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-38</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>R-P3</t>
+          <t>P3-Y1-2</t>
         </is>
       </c>
       <c r="B70" s="21" t="n">
@@ -25121,7 +25168,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
@@ -25129,49 +25176,629 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
+          <t>Checklist silhouettes; one invitation; Raise the big lodge button; skip control</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>P3_2 §P3-Y1, Y2</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>P2-B5</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>drawer; SanctuaryDialogue.js</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>One invitation per save; the button follows the wood count</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>OD-04</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>PLN-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>P3-L3</t>
+        </is>
+      </c>
+      <c r="B71" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Level props: one InstancedMesh per prop kind, 9 per building (M6)</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>P3_1 §P3-L3; P2_5 §3</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>P3-L1-6, M1</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>new js/sanctuary/SanctuaryBuildingProps.js; js/sanctuary/buildings/models/props.js</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>12 buildings at level 10 add &lt;= 9 draw calls</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Mark (visible)</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>PLN-38</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>UA-7</t>
+        </is>
+      </c>
+      <c r="B72" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Celebration visuals: the lodge raising (P3-Y6) and the level glow (P3-L4)</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>P3_2 §P3-Y6; P3_1 §P3-L4; 00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>UA-5</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>js/sanctuary/ (effects module, agreed with Seats B and D); Assets/village/ (effects atlas)</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>&lt;= 10 s, skippable, reduced-motion version</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Partner + advisors</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>PLN-42, PLN-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>P3-L4</t>
+        </is>
+      </c>
+      <c r="B73" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>One-second level celebration (+ reduced-motion version)</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>P3_1 §P3-L4</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>P3-L1-6, UA-7</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>SanctuaryBuildingLifecycle.js</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Video with and without reduced motion; no allocations</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>PLN-38</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Lodge model (&lt;= 40k tris, &lt;= 3 draw calls, plain sewn-hide cover)</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>P2_5 §3.7; P3_2 §P3-Y3</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Assets/lodge/*.glb</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Tris, draw calls and phone memory in the commit</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>OD-03, OD-25; partner + Mark</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>PLN-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>P3-Y4-5</t>
+        </is>
+      </c>
+      <c r="B75" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>The swap (rim check, flat disk, shared GLB kept) + re-seat Yellow Butterfly</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>P3_2 §P3-Y4, Y5</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>M7, P2-K2-10</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>SanctuaryTipis.js; ground hook; SanctuaryTipiNpcs.js</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>No terrain through the platform on either layout; she sits at the new door after a reload</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Mark (pad and braziers inside the footprint)</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>PLN-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>P3-Y8-9</t>
+        </is>
+      </c>
+      <c r="B76" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Take down and move with the 8.0 m reservation; tiers 3-10 as data validation</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>P3_2 §P3-Y8, Y9</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>P3-Y4-5</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>SanctuaryBuildingLifecycle.js; SanctuaryVillageRules.js; buildingTypes.js</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Rebuild elsewhere and raise again: it always fits; a fake tier-3 row changes no save</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>OD-15</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>PLN-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>P3-Y6</t>
+        </is>
+      </c>
+      <c r="B77" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Raising celebration (&lt;= 10 s, skippable, cuts under reduced motion)</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>P3_2 §P3-Y6</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>P3-Y4-5, P2-K7-9, UA-7</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>new js/sanctuary/SanctuaryLodgeCelebration.js</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Skipping at any moment gives the same end state; a reload mid-way gives a built lodge</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Partner + advisors (who raises it, any music)</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>PLN-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>P3-Y7</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Gathering place at the lodge's fire circle</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>P3_2 §P3-Y7</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>P3-Y6</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>SanctuaryVillagers.js</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Evening screenshot; still within 20 villagers</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>PLN-39</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>UA-Q3</t>
+        </is>
+      </c>
+      <c r="B79" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Phase 3 visual QA, before R's phase test</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>00_UI_AND_ART_PLAN §7</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>all Phase 3 items</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>PLN-42</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>R-P3</t>
+        </is>
+      </c>
+      <c r="B80" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
           <t>Land Phase 3 in order; phase test; Mark plays it</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>prompts/REVIEWER_R.md</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>all Phase 3 items</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>tools/decision-engine/build_engine.py (rows only)</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>The lodge and every building at level 10: phone 3x holds 60 fps</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>Mark plays it</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>PLN-38, PLN-39, PLN-41</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L70"/>
+  <autoFilter ref="A4:L80"/>
   <dataValidations count="1">
-    <dataValidation sqref="K5:K70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="K5:K80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not started,In progress,Blocked,Awaiting approval,Done (code) — verify in browser,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -25232,7 +25859,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>467b9e9</t>
+          <t>a88d9b2</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -25587,7 +26214,7 @@
         </is>
       </c>
       <c r="B27" s="11">
-        <f>COUNTIF('64_Next_Plan'!$K$5:$K$70,"Done*")&amp;" of "&amp;COUNTA('64_Next_Plan'!$A$5:$A$70)</f>
+        <f>COUNTIF('64_Next_Plan'!$K$5:$K$80,"Done*")&amp;" of "&amp;COUNTA('64_Next_Plan'!$A$5:$A$80)</f>
         <v/>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -25706,7 +26333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -25835,7 +26462,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Hex grid, placement rules, map layouts, hills; clock, food store, garden, seasons, hearts; the lodge swap</t>
+          <t>Hex grid, placement rules, map layouts, hills; clock, food store, garden growth, seasons, hearts; the lodge swap (with Seat U's model)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -25877,7 +26504,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Building data, strings, registry, save system; chopping, quests, lifecycle, rack, cache, fire and the models; levels</t>
+          <t>Building data, strings, registry, save system; chopping, quests, lifecycle, rack / cache / fire behaviour (with Seat U's models); level rules</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -25909,7 +26536,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Input &amp; UI</t>
+          <t>Input &amp; placement</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -25919,7 +26546,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Coder pack W3-W6, select, tray, ghost, undo; Build drawer and journal; beads, checklist, info card</t>
+          <t>Coder pack W3-W6, select, tray, ghost, undo, next spot, zoom (wired to Seat U's skin); later, input plumbing on request (ground relay, keys, switch)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -25929,12 +26556,12 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>claude/village-phases/prompts/PH2_SEAT_C_DRAWER.md</t>
+          <t>claude/village-phases/prompts/PH2_SEAT_C_DRAWER.md (input support)</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>claude/village-phases/prompts/PH3_ALL_SEATS.md (Seat C)</t>
+          <t>claude/village-phases/prompts/PH3_ALL_SEATS.md (Seat C: input support)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -25961,7 +26588,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Villager rig, brains, paths, slots, keepers, families; the lodge celebration</t>
+          <t>Villager rig code, brains, paths, slots, keepers, families; the lodge celebration's choreography (with Seat U's look)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -25985,8 +26612,50 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>UI &amp; art</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>A new AI: a master coder who is also the UI designer and artist</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Everything the child sees: design tokens and components, icons and pictures, the village atlas and every model, the Build drawer, journal and Phase 3 UI; visual QA before each phase test</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>claude/village-phases/prompts/MASTER_CODER_UI_ART.md</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>claude/village-phases/prompts/MASTER_CODER_UI_ART.md</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>claude/village-phases/prompts/MASTER_CODER_UI_ART.md</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>css/sanctuary-ui.css; Assets/ui/icons.svg, reasons.png + .json; Assets/ui/cards, items; js/sanctuary/buildings/models/&lt;type&gt;.js createModel()</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H9"/>
+  <autoFilter ref="A4:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26771,7 +27440,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>In code now from shared parts and one village texture; artist models drop in later through data</t>
+          <t>In code now (Seat U) from shared parts and one village texture; artist models drop in later through data</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -26835,7 +27504,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Mark's call: himself, an artist he knows, or a paid and credited Native artist</t>
+          <t>Mark's call: himself, an artist he knows, a paid and credited Native artist, or Seat U in code (partner-reviewed); Seat U's art brief and test proxy meanwhile</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -28177,7 +28846,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit 467b9e9</t>
+          <t>Activation order in index.html · evidence re-located at build · commit a88d9b2</t>
         </is>
       </c>
     </row>
@@ -32714,7 +33383,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>373 lines, 13.8 KB. update() at L357 (0 lines). Writes 2 globals.</t>
+          <t>378 lines, 14.2 KB. update() at L362 (0 lines). Writes 2 globals.</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -32730,7 +33399,7 @@
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryMutations; __sanctuaryTopDownHeight; _v4ToggleJournal; _v4TogglePanel; localStorage</t>
+          <t>SanctuaryMutations; __sanctuaryAvatar; __sanctuaryTopDownHeight; _v4ToggleJournal; _v4TogglePanel; localStorage</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -32745,16 +33414,16 @@
       <c r="T22" s="5" t="inlineStr"/>
       <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28 refactor(pip): remove SVG moondial iframe, render top-down PIP canvas in wrapper</t>
+          <t>2026-10-22 feat(camera): Village View keeps the avatar centred (Mark)</t>
         </is>
       </c>
       <c r="X22" s="5" t="inlineStr"/>
       <c r="Y22" s="6" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23">
@@ -34200,7 +34869,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>412 lines, 19.6 KB. update() at L150 (224 lines). Per-frame hazards: alloc_three×2, dom_query×1. Writes 1 globals.</t>
+          <t>424 lines, 20.4 KB. update() at L150 (236 lines). Per-frame hazards: alloc_three×2, dom_query×1. Writes 1 globals.</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -34216,7 +34885,7 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>__sanctuaryAvatar; __sanctuaryJoystickInput; __sanctuaryLookDrag; __sanctuaryZoomFactor; _v4CancelClickToMove; _v4InputSuppressed; addEventListener; removeEventListener</t>
+          <t>__sanctuaryAvatar; __sanctuaryJoystickInput; __sanctuaryLookDrag; __sanctuaryTopDownHeight; __sanctuaryZoomFactor; _v4CancelClickToMove; _v4InputSuppressed; addEventListener; removeEventListener</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr"/>
@@ -34231,11 +34900,11 @@
       </c>
       <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W40" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 feat(controls): A/D turn, Shift+A/D strafe, run after 2 s of walking, real jump (Mark)</t>
+          <t>2026-10-22 feat(camera): Village View keeps the avatar centred (Mark)</t>
         </is>
       </c>
       <c r="X40" s="5" t="inlineStr">
@@ -34244,7 +34913,7 @@
         </is>
       </c>
       <c r="Y40" s="6" t="n">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="41">
@@ -58041,23 +58710,23 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>window.AnuUniverse</t>
+          <t>window.__sanctuaryAvatar</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>MOD-054, MOD-097</t>
+          <t>MOD-011</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>MOD-002, MOD-017, MOD-026, MOD-035, MOD-064, MOD-065, MOD-091, MOD-093, MOD-096, MOD-106</t>
+          <t>MOD-010, MOD-016, MOD-018, MOD-024, MOD-026, MOD-030, MOD-036, MOD-042, MOD-043, MOD-048, MOD-049, MOD-051</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -58074,23 +58743,23 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>window.SanctuaryMutations</t>
+          <t>window.AnuUniverse</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>MOD-038</t>
+          <t>MOD-054, MOD-097</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>MOD-003, MOD-004, MOD-005, MOD-006, MOD-007, MOD-008, MOD-009, MOD-016, MOD-018, MOD-030, MOD-045</t>
+          <t>MOD-002, MOD-017, MOD-026, MOD-035, MOD-064, MOD-065, MOD-091, MOD-093, MOD-096, MOD-106</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -58107,7 +58776,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryAvatar</t>
+          <t>window.SanctuaryMutations</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -58118,12 +58787,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>MOD-011</t>
+          <t>MOD-038</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>MOD-010, MOD-016, MOD-024, MOD-026, MOD-030, MOD-036, MOD-042, MOD-043, MOD-048, MOD-049, MOD-051</t>
+          <t>MOD-003, MOD-004, MOD-005, MOD-006, MOD-007, MOD-008, MOD-009, MOD-016, MOD-018, MOD-030, MOD-045</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -59040,7 +59709,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>window._v2InputSuppressed</t>
+          <t>window.__sanctuaryTopDownHeight</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -59051,12 +59720,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>MOD-026</t>
+          <t>MOD-053</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>MOD-016, MOD-022</t>
+          <t>MOD-018, MOD-036</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -59073,7 +59742,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>window._v4InputSuppressed</t>
+          <t>window._v2InputSuppressed</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -59089,7 +59758,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>MOD-022, MOD-036</t>
+          <t>MOD-016, MOD-022</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -59106,24 +59775,28 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>window.webkitAudioContext</t>
+          <t>window._v4InputSuppressed</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>MOD-026</t>
+        </is>
+      </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>MOD-010, MOD-024, MOD-026</t>
+          <t>MOD-022, MOD-036</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Read-only here (written elsewhere/HTML)</t>
+          <t>Cross-module (written by one, read by another)</t>
         </is>
       </c>
     </row>
@@ -59135,28 +59808,24 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>window.Orchestrator</t>
+          <t>window.webkitAudioContext</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>MOD-064</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>MOD-054</t>
+          <t>MOD-010, MOD-024, MOD-026</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Cross-module (written by one, read by another)</t>
+          <t>Read-only here (written elsewhere/HTML)</t>
         </is>
       </c>
     </row>
@@ -59168,24 +59837,28 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>window.ThreeIconManager</t>
+          <t>window.Orchestrator</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>MOD-064</t>
+        </is>
+      </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>MOD-054, MOD-106</t>
+          <t>MOD-054</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Read-only here (written elsewhere/HTML)</t>
+          <t>Cross-module (written by one, read by another)</t>
         </is>
       </c>
     </row>
@@ -59197,7 +59870,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>window.WorldPhysics</t>
+          <t>window.ThreeIconManager</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -59209,7 +59882,7 @@
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>MOD-094, MOD-095</t>
+          <t>MOD-054, MOD-106</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -59226,28 +59899,24 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>window.__interestedFish</t>
+          <t>window.WorldPhysics</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>MOD-026</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>MOD-024</t>
+          <t>MOD-094, MOD-095</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Cross-module (written by one, read by another)</t>
+          <t>Read-only here (written elsewhere/HTML)</t>
         </is>
       </c>
     </row>
@@ -59259,7 +59928,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>window.__regenerateBraziers</t>
+          <t>window.__interestedFish</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -59270,12 +59939,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>MOD-012</t>
+          <t>MOD-026</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>MOD-045</t>
+          <t>MOD-024</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -59292,7 +59961,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>window.__regenerateDock</t>
+          <t>window.__regenerateBraziers</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
@@ -59303,7 +59972,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>MOD-021</t>
+          <t>MOD-012</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -59325,7 +59994,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>window.__regenerateTipiNpcs</t>
+          <t>window.__regenerateDock</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
@@ -59336,7 +60005,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>MOD-043</t>
+          <t>MOD-021</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -59358,7 +60027,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>window.__regenerateTipis</t>
+          <t>window.__regenerateTipiNpcs</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
@@ -59369,7 +60038,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>MOD-044</t>
+          <t>MOD-043</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -59391,24 +60060,28 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryFishCount</t>
+          <t>window.__regenerateTipis</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>MOD-024, MOD-026</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr"/>
+          <t>MOD-044</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>MOD-045</t>
+        </is>
+      </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Write-only</t>
+          <t>Cross-module (written by one, read by another)</t>
         </is>
       </c>
     </row>
@@ -59420,28 +60093,24 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryFishingSpawnRipple</t>
+          <t>window.__sanctuaryFishCount</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>MOD-026</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>MOD-024</t>
-        </is>
-      </c>
+          <t>MOD-024, MOD-026</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Cross-module (written by one, read by another)</t>
+          <t>Write-only</t>
         </is>
       </c>
     </row>
@@ -59453,24 +60122,28 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryFrogOnLily</t>
+          <t>window.__sanctuaryFishingSpawnRipple</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>MOD-024, MOD-029</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr"/>
+          <t>MOD-026</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>MOD-024</t>
+        </is>
+      </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Write-only</t>
+          <t>Cross-module (written by one, read by another)</t>
         </is>
       </c>
     </row>
@@ -59482,28 +60155,24 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryFrogs</t>
+          <t>window.__sanctuaryFrogOnLily</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>MOD-029</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>MOD-024</t>
-        </is>
-      </c>
+          <t>MOD-024, MOD-029</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Cross-module (written by one, read by another)</t>
+          <t>Write-only</t>
         </is>
       </c>
     </row>
@@ -59515,24 +60184,28 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryJoystickInput</t>
+          <t>window.__sanctuaryFrogs</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>MOD-029</t>
+        </is>
+      </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>MOD-022, MOD-036</t>
+          <t>MOD-024</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Read-only here (written elsewhere/HTML)</t>
+          <t>Cross-module (written by one, read by another)</t>
         </is>
       </c>
     </row>
@@ -59544,28 +60217,24 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryLilyPads</t>
+          <t>window.__sanctuaryJoystickInput</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>MOD-040</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>MOD-029</t>
+          <t>MOD-022, MOD-036</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Cross-module (written by one, read by another)</t>
+          <t>Read-only here (written elsewhere/HTML)</t>
         </is>
       </c>
     </row>
@@ -59577,7 +60246,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryLookDrag</t>
+          <t>window.__sanctuaryLilyPads</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
@@ -59588,12 +60257,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>MOD-022</t>
+          <t>MOD-040</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>MOD-036</t>
+          <t>MOD-029</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -59610,7 +60279,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryMuted</t>
+          <t>window.__sanctuaryLookDrag</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
@@ -59621,12 +60290,12 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>MOD-010</t>
+          <t>MOD-022</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>MOD-048</t>
+          <t>MOD-036</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -59643,7 +60312,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryPipLite</t>
+          <t>window.__sanctuaryMuted</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
@@ -59654,12 +60323,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>MOD-024</t>
+          <t>MOD-010</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>MOD-064</t>
+          <t>MOD-048</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -59676,7 +60345,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuarySpawnBabyFish</t>
+          <t>window.__sanctuaryPipLite</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
@@ -59692,7 +60361,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>MOD-026</t>
+          <t>MOD-064</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -59709,7 +60378,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryTipi1PlatMesh</t>
+          <t>window.__sanctuarySpawnBabyFish</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
@@ -59720,12 +60389,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>MOD-044</t>
+          <t>MOD-024</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>MOD-043</t>
+          <t>MOD-026</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -59742,7 +60411,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryTipi2PlatMesh</t>
+          <t>window.__sanctuaryTipi1PlatMesh</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
@@ -59775,7 +60444,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryTipi3Anchor</t>
+          <t>window.__sanctuaryTipi2PlatMesh</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
@@ -59791,7 +60460,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>MOD-012</t>
+          <t>MOD-043</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -59808,7 +60477,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryTipi3Yaw</t>
+          <t>window.__sanctuaryTipi3Anchor</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
@@ -59841,7 +60510,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryTipi4PlatMesh</t>
+          <t>window.__sanctuaryTipi3Yaw</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
@@ -59857,7 +60526,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>MOD-043</t>
+          <t>MOD-012</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -59874,7 +60543,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>window.__sanctuaryTopDownHeight</t>
+          <t>window.__sanctuaryTipi4PlatMesh</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
@@ -59885,12 +60554,12 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>MOD-053</t>
+          <t>MOD-044</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>MOD-018</t>
+          <t>MOD-043</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">

--- a/docs/decision-engine/Decision_Engine.xlsx
+++ b/docs/decision-engine/Decision_Engine.xlsx
@@ -48,9 +48,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'61_Decision_Log'!$A$4:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'62_Review_Playbook'!$A$4:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'63_Attempts_Ledger'!$A$4:$I$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'64_Next_Plan'!$A$4:$L$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'64_Next_Plan'!$A$4:$L$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'65_Team_Seats'!$A$4:$H$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'66_Owner_Decisions'!$A$4:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'66_Owner_Decisions'!$A$4:$F$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'70_Session_Log'!$A$4:$E$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'90_Glossary'!$A$4:$B$17</definedName>
   </definedNames>
@@ -623,7 +623,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit a88d9b2. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
+          <t>Layered map of the live system for AI and humans. Read top-down: each level is more exact than the last. Built 2026-10-22 at commit 190e626. Zero-trust: 'Assumed' = comments/docs, 'Verified' = measured.</t>
         </is>
       </c>
     </row>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Built at commit a88d9b2.</t>
+          <t>Built at commit 190e626.</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Three style frames: Village View with the Tier-1 set (code-built prototypes), the Build drawer on a phone, placing a drying rack</t>
+          <t>Three style frames, starting from the design's boards: Village View with the Tier-1 set (code-built prototypes), the Build modal on a phone, placing a drying rack</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 skin: tray, undo chip, ghost tints, lodge ring (Seats C and A wire it)</t>
+          <t>Phase 1 skin: tray, undo chip, ghost tints, lodge ring (C wires the ghost tints, A the ring; the tray and chip are panel HTML, UA-8)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -22434,7 +22434,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>P1-T5</t>
+          <t>UA-8</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
@@ -22442,7 +22442,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -22450,32 +22450,32 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>60° turns; tipis don't turn</t>
+          <t>The builder moves into the panel (DEC-35): modal controller and announcer; Village View top bar, request chips and dock (walking HUD hidden in Village View); Build modal with today's tools; My village with today's list; tray, undo chip and zoom as panel HTML that isn't modal</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>P1_3 §P1-T5</t>
+          <t>00_UI_AND_ART_PLAN §9; P2_3 Layout; design 'Village Builder UI'</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>VB1-W6</t>
+          <t>UA-2, UA-3</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>SanctuarySelect.js (ROT_STEP_RAD = PI/3)</t>
+          <t>SacredGame.Panel.html (3 lines: link, script, mount div); new js/panel/sa-village-ui.js; css/sanctuary-ui.css</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>No ↻ for tipis; 6 taps make a full turn</t>
+          <t>The 11-point modal check (plan §9) on every modal; keyboard-only and VoiceOver walkthroughs; FND-49 probes pass; fps unchanged; screenshots match the design</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>OD-10</t>
+          <t>Mark (visible); DEC-35, OD-26</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -22485,14 +22485,14 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>PLN-33</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>P1-T1</t>
+          <t>P1-T5</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
@@ -22508,32 +22508,32 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Fixed tray (64 px, finger-up, keys); W6's bar docks into it</t>
+          <t>60° turns; tipis don't turn</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>P1_3 §P1-T1</t>
+          <t>P1_3 §P1-T5</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>VB1-W6, UA-4</t>
+          <t>VB1-W6</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryPlaceTray.js; SanctuarySelect.js</t>
+          <t>SanctuarySelect.js (ROT_STEP_RAD = PI/3)</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Sizes measured; keyboard-only placement; FND-49 probe passes</t>
+          <t>No ↻ for tipis; 6 taps make a full turn</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>OD-11; Mark (visible)</t>
+          <t>OD-10</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -22550,7 +22550,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>VB1-P5</t>
+          <t>P1-T1</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
@@ -22566,32 +22566,32 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Ghost, tap-tap-tick and picture reasons (P1-T2, P1-T3)</t>
+          <t>Tray behaviour through the builder bridge (VB_TRAY in, VB_PLACING out); the tray is Seat U's panel HTML (DEC-35); W6's bar becomes its Move / Turn / Delete / Done; the game-page builder boxes retire after parity</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P5; P1_3 §P1-T2, P1-T3</t>
+          <t>P1_3 §P1-T1; 00_UI_AND_ART_PLAN §9</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>P1-H3, P1-T1, UA-3, UA-4</t>
+          <t>VB1-W6, UA-4, UA-8</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryPlaceIcons.js; ghost; SanctuaryClickToMove.js (Village View branch)</t>
+          <t>new js/sanctuary/SanctuaryBuilderBridge.js; new js/sanctuary/SanctuaryPlaceTray.js (logic only, no DOM); SanctuarySelect.js; then SanctuaryToolPalette.js, js/v2/BuildingPanelUI.js, SanctuaryControls.js (DOM retired after parity)</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>A tipi placed with three taps on the phone 3x profile; every refusal shows its picture</t>
+          <t>Sizes measured; keyboard-only placement; FND-49 probe passes; while a panel modal is open the relay sends nothing</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-11, OD-26; Mark (visible)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -22608,7 +22608,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>VB1-P6</t>
+          <t>VB1-P5</t>
         </is>
       </c>
       <c r="B26" s="19" t="n">
@@ -22624,27 +22624,27 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Undo, 20 steps, + undo chip (P1-T4)</t>
+          <t>Ghost, tap-tap-tick and picture reasons (P1-T2, P1-T3)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P6; P1_3 §P1-T4</t>
+          <t>village-builder-phase1-prompt P5; P1_3 §P1-T2, P1-T3</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>VB1-W5</t>
+          <t>P1-H3, P1-T1, UA-3, UA-4</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryMutations.js; SanctuaryPlaceTray.js</t>
+          <t>new js/sanctuary/SanctuaryPlaceIcons.js; ghost; SanctuaryClickToMove.js (Village View branch)</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Place, move, delete, then undo x3: back to the start</t>
+          <t>A tipi placed with three taps on the phone 3x profile; every refusal shows its picture</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -22666,7 +22666,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>VB1-P2-3-8-11</t>
+          <t>VB1-P6</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
@@ -22682,27 +22682,27 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Clear, Generate (fixed seed), caps, Village View hint</t>
+          <t>Undo, 20 steps, + undo chip (P1-T4)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P2, P3, P8, P11</t>
+          <t>village-builder-phase1-prompt P6; P1_3 §P1-T4</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>P1-H3, P1-D2</t>
+          <t>VB1-W5</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryMutations.js; SanctuaryToolPalette.js (buttons only)</t>
+          <t>SanctuaryMutations.js; SanctuaryPlaceTray.js</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Generate twice: identical, nothing in the pond, dock, tipis or pad; the 201st rock is refused</t>
+          <t>Place, move, delete, then undo x3: back to the start</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -22724,7 +22724,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>P1-T6-8</t>
+          <t>VB1-P2-3-8-11</t>
         </is>
       </c>
       <c r="B28" s="19" t="n">
@@ -22740,27 +22740,27 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Next/previous spot, zoom while placing, reduced motion</t>
+          <t>Clear, Generate (fixed seed), caps, Village View hint</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>P1_3 §P1-T6, T7, T8</t>
+          <t>village-builder-phase1-prompt P2, P3, P8, P11</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>P1-T1, P1-H1</t>
+          <t>P1-H3, P1-D2</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryPlaceTray.js; SanctuaryControls.js (zoom only)</t>
+          <t>SanctuaryMutations.js; SanctuaryToolPalette.js (logic only: the buttons are in Seat U's Build modal, VB_TOOL)</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Tab + Enter placement; tiles &gt;= 64 CSS px while placing; nothing eases under reduced motion</t>
+          <t>Generate twice: identical, nothing in the pond, dock, tipis or pad; the 201st rock is refused</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -22782,7 +22782,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>P1-H5</t>
+          <t>P1-T6-8</t>
         </is>
       </c>
       <c r="B29" s="19" t="n">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -22798,27 +22798,27 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Map layouts as data</t>
+          <t>Next/previous spot, zoom while placing, reduced motion</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>P1_1 §P1-H5</t>
+          <t>P1_3 §P1-T6, T7, T8</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>VB1-W3</t>
+          <t>P1-T1, P1-H1</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/data/mapLayouts.js; SanctuaryTipis.js (anchor lookup only)</t>
+          <t>SanctuaryPlaceTray.js; SanctuaryControls.js (zoom only; Seat U's panel buttons post VB_ZOOM)</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Tipi positions and yaws identical on all 5 maps</t>
+          <t>Tab + Enter placement; tiles &gt;= 64 CSS px while placing; nothing eases under reduced motion</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -22833,14 +22833,14 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>PLN-31</t>
+          <t>PLN-33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>P1-H4</t>
+          <t>P1-H5</t>
         </is>
       </c>
       <c r="B30" s="19" t="n">
@@ -22856,32 +22856,32 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Reserve Yellow Butterfly's lodge ground + faint ring</t>
+          <t>Map layouts as data</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>P1_1 §P1-H4</t>
+          <t>P1_1 §P1-H5</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>P1-H3, P1-H5, UA-4</t>
+          <t>VB1-W3</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>mapLayouts.js; SanctuaryVillageRules.js; ring helper</t>
+          <t>new js/sanctuary/data/mapLayouts.js; SanctuaryTipis.js (anchor lookup only)</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Ring shows in Village View on maps 1 and 2; tree, rock and tipi refused inside, flower allowed</t>
+          <t>Tipi positions and yaws identical on all 5 maps</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>OD-03 (default in use)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -22898,7 +22898,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>VB1-P7</t>
+          <t>P1-H4</t>
         </is>
       </c>
       <c r="B31" s="19" t="n">
@@ -22914,32 +22914,32 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Hills are real ground</t>
+          <t>Reserve Yellow Butterfly's lodge ground + faint ring</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>village-builder-phase1-prompt P7</t>
+          <t>P1_1 §P1-H4</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>P1-H3</t>
+          <t>P1-H3, P1-H5, UA-4</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/SanctuaryGround.js (height + terrain update only); MoldGrowHill.js</t>
+          <t>mapLayouts.js; SanctuaryVillageRules.js; ring helper</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Walk over a hill smoothly; trees sit on the slope; the grass follows</t>
+          <t>Ring shows in Village View on maps 1 and 2; tree, rock and tipi refused inside, flower allowed</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Grass owner + Compassion holder sign off</t>
+          <t>OD-03 (default in use)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -22956,7 +22956,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>UA-Q1</t>
+          <t>VB1-P7</t>
         </is>
       </c>
       <c r="B32" s="19" t="n">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -22972,32 +22972,32 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 visual QA, before R's phase test</t>
+          <t>Hills are real ground</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>00_UI_AND_ART_PLAN §7</t>
+          <t>village-builder-phase1-prompt P7</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>all Phase 1 items</t>
+          <t>P1-H3</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
+          <t>js/sanctuary/SanctuaryGround.js (height + terrain update only); MoldGrowHill.js</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
+          <t>Walk over a hill smoothly; trees sit on the slope; the grass follows</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Grass owner + Compassion holder sign off</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -23007,14 +23007,14 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>PLN-42</t>
+          <t>PLN-31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>R-P1</t>
+          <t>UA-Q1</t>
         </is>
       </c>
       <c r="B33" s="19" t="n">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -23030,12 +23030,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Land Phase 1 in order; phase test; Mark plays it</t>
+          <t>Phase 1 visual QA, before R's phase test</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>prompts/REVIEWER_R.md</t>
+          <t>00_UI_AND_ART_PLAN §7</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -23045,17 +23045,17 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>tools/decision-engine/build_engine.py (rows only)</t>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Phone 3x holds 60 fps in Village View; every Phase 1 'Proves it' passes</t>
+          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Mark plays it</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -23065,22 +23065,22 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>PLN-31, PLN-32, PLN-33, PLN-41</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>P2-B1</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="n">
-        <v>2</v>
+          <t>R-P1</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -23088,32 +23088,32 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Fishery F0-F2: tree registry, one inventory with wood, villager clicks, chop, logs, carry</t>
+          <t>Land Phase 1 in order; phase test; Mark plays it</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B1; fishery-quest-spec F0-F2</t>
+          <t>prompts/REVIEWER_R.md</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>all Phase 1 items</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>new SanctuaryTrees.js, SanctuaryChop.js; SanctuaryInventory.js; SanctuaryClickToMove.js (talk and tree clicks)</t>
+          <t>tools/decision-engine/build_engine.py (rows only)</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Fishery F0-F2 proofs; 10 chopped trees add &lt;= 4 draw calls</t>
+          <t>Phone 3x holds 60 fps in Village View; every Phase 1 'Proves it' passes</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Compassion holder: read-only pond-tree hook</t>
+          <t>Mark plays it</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -23123,14 +23123,14 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>PLN-34</t>
+          <t>PLN-31, PLN-32, PLN-33, PLN-41</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>P2-F1</t>
+          <t>P2-B1</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -23146,12 +23146,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Play-time clock (evening = the moon button or 8 play-minutes)</t>
+          <t>Fishery F0-F2: tree registry, one inventory with wood, villager clicks, chop, logs, carry</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F1</t>
+          <t>P2_1 §P2-B1; fishery-quest-spec F0-F2</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -23161,17 +23161,17 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryClock.js</t>
+          <t>new SanctuaryTrees.js, SanctuaryChop.js; SanctuaryInventory.js; SanctuaryClickToMove.js (talk and tree clicks)</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>A hidden tab advances nothing; the same actions give the same ticks</t>
+          <t>Fishery F0-F2 proofs; 10 chopped trees add &lt;= 4 draw calls</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>OD-18</t>
+          <t>Compassion holder: read-only pond-tree hook</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -23181,14 +23181,14 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>P2-F2</t>
+          <t>P2-F1</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -23204,32 +23204,32 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Food data + SanctuaryFood store</t>
+          <t>Play-time clock (evening = the moon button or 8 play-minutes)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F2</t>
+          <t>P2_4 §P2-F1</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>P2-F1</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/data/{items,crops,recipes}.js; js/sanctuary/SanctuaryFood.js</t>
+          <t>new js/sanctuary/SanctuaryClock.js</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Unit tests for plant, grow, harvest, dry, cook and store</t>
+          <t>A hidden tab advances nothing; the same actions give the same ticks</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-18</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -23246,7 +23246,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>UA-6</t>
+          <t>P2-F2</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -23262,32 +23262,32 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Villager art brief + test proxy for Seat D (M3)</t>
+          <t>Food data + SanctuaryFood store</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.8; 00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
+          <t>P2_4 §P2-F2</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>UA-1</t>
+          <t>P2-F1</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/UA-6/ (brief); Assets/villager/ (test proxy only)</t>
+          <t>new js/sanctuary/data/{items,crops,recipes}.js; js/sanctuary/SanctuaryFood.js</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>The proxy never ships</t>
+          <t>Unit tests for plant, grow, harvest, dry, cook and store</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>OD-25; partner (clothing, hair)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -23297,14 +23297,14 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>PLN-42, PLN-35</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>UA-6</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -23320,32 +23320,32 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Parts library + shared village atlas + plan material + aStage reveal</t>
+          <t>Villager art brief + test proxy for Seat D (M3)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §2, §4, §5</t>
+          <t>P2_5 §3.8; 00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>UA-1</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/buildings/models/parts.js; Assets/village/atlas_*.png; Assets/village/PROVENANCE.md; new tools/model-gallery.html</t>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/UA-6/ (brief); Assets/villager/ (test proxy only)</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>One material for every Tier-1 building; 2 draw calls while building, 1 when built</t>
+          <t>The proxy never ships</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Mark sees the atlas</t>
+          <t>OD-25; partner (clothing, hair)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -23355,14 +23355,14 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>PLN-40</t>
+          <t>PLN-42, PLN-35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>UA-5</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -23378,32 +23378,32 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Item pictures, portrait frames, smoke / steam / flame sprites</t>
+          <t>Parts library + shared village atlas + plan material + aStage reveal</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>00_UI_AND_ART_PLAN §3, §5</t>
+          <t>P2_5 §2, §4, §5</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>UA-2, M1</t>
+          <t>Phase 1</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Assets/ui/items/*.png; Assets/ui/ (portrait frames); Assets/village/ (effects atlas)</t>
+          <t>new js/sanctuary/buildings/models/parts.js; Assets/village/atlas_*.png; Assets/village/PROVENANCE.md; new tools/model-gallery.html</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>One atlas each; card budget kept</t>
+          <t>One material for every Tier-1 building; 2 draw calls while building, 1 when built</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Mark sees the atlas</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -23413,14 +23413,14 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>PLN-42</t>
+          <t>PLN-40</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>UA-5</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -23436,32 +23436,32 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Drying rack model (20 hooks, 4 stages)</t>
+          <t>Item pictures, portrait frames, smoke / steam / flame sprites</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.1</t>
+          <t>00_UI_AND_ART_PLAN §3, §5</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>UA-2, M1</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/buildings/models/dryingRack.js</t>
+          <t>Assets/ui/items/*.png; Assets/ui/ (portrait frames); Assets/village/ (effects atlas)</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>&lt;= 1,500 tris, &lt;= 3 draw calls; fish turn silver to gold</t>
+          <t>One atlas each; card budget kept</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Partner + Mark</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -23471,14 +23471,14 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>PLN-40</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>P2-K1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
@@ -23494,32 +23494,32 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Light villager rig (&lt;= 2,500 tris, 25-30 bones, clips) (M3)</t>
+          <t>Drying rack model (20 hooks, 4 stages)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K1; P2_5 §3.8</t>
+          <t>P2_5 §3.1</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>UA-6</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryVillagerRig.js; Assets/villager/</t>
+          <t>js/sanctuary/buildings/models/dryingRack.js</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>No pop at screen edges; counts in the commit; placeholder never shipped</t>
+          <t>&lt;= 1,500 tris, &lt;= 3 draw calls; fish turn silver to gold</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>OD-25; asset from Mark, an artist or Seat U; partner (clothing)</t>
+          <t>Partner + Mark</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -23529,14 +23529,14 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-40</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>P2-K3-4</t>
+          <t>P2-K1</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -23552,32 +23552,32 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Villager brain (7 states, play-time step, seeded RNG); home and wander</t>
+          <t>Light villager rig (&lt;= 2,500 tris, 25-30 bones, clips) (M3)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K3, K4</t>
+          <t>P2_2 §P2-K1; P2_5 §3.8</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>P2-F1, P1-H2</t>
+          <t>UA-6</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryVillagers.js</t>
+          <t>new js/sanctuary/SanctuaryVillagerRig.js; Assets/villager/</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>The same seed gives the same wander after a reload; nobody walks into the pond or the lodge ring</t>
+          <t>No pop at screen edges; counts in the commit; placeholder never shipped</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-25; asset from Mark, an artist or Seat U; partner (clothing)</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>P2-K5-6</t>
+          <t>P2-K3-4</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -23610,27 +23610,27 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Hex paths and work slots (claim / release)</t>
+          <t>Villager brain (7 states, play-time step, seeded RNG); home and wander</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K5, K6</t>
+          <t>P2_2 §P2-K3, K4</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>P2-K3-4</t>
+          <t>P2-F1, P1-H2</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryVillagerPaths.js</t>
+          <t>new js/sanctuary/SanctuaryVillagers.js</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>A path across the village in &lt;= 1 ms; two plans never share a slot</t>
+          <t>The same seed gives the same wander after a reload; nobody walks into the pond or the lodge ring</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -23652,7 +23652,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>P2-K2-10</t>
+          <t>P2-K5-6</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -23668,32 +23668,32 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Hero villagers cross-fade to walk; seatAt / seatOnGround</t>
+          <t>Hex paths and work slots (claim / release)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K2, K10</t>
+          <t>P2_2 §P2-K5, K6</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>P2-K1</t>
+          <t>P2-K3-4</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryTipiNpcs.js (seating API only)</t>
+          <t>new js/sanctuary/SanctuaryVillagerPaths.js</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Red Eagle Girl walks, hammers and sits again; nobody floats after a take-down</t>
+          <t>A path across the village in &lt;= 1 ms; two plans never share a slot</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>OD-14</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -23710,7 +23710,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>P2-B3</t>
+          <t>P2-K2-10</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -23718,7 +23718,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -23726,32 +23726,32 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Quests and requests as data; wish baskets (fishery F3, P2-F7)</t>
+          <t>Hero villagers cross-fade to walk; seatAt / seatOnGround</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B3; P2_4 §P2-F7; fishery-quest-spec F3</t>
+          <t>P2_2 §P2-K2, K10</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>P2-B1</t>
+          <t>P2-K1</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>new SanctuaryQuests.js, quests/*.js, SanctuaryQuestMarkers.js, SanctuaryDialogue.js</t>
+          <t>SanctuaryTipiNpcs.js (seating API only)</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>The 2-tree loop works from a fresh save; no wish expires with a penalty</t>
+          <t>Red Eagle Girl walks, hammers and sits again; nobody floats after a take-down</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Partner + Mark (dialogue, names)</t>
+          <t>OD-14</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -23761,14 +23761,14 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>PLN-34</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>P2-B2</t>
+          <t>P2-B3</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -23784,32 +23784,32 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Lifecycle plan → building → built → taken down; drying rack (fishery F4)</t>
+          <t>Quests and requests as data; wish baskets (fishery F3, P2-F7)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B2; fishery-quest-spec F4</t>
+          <t>P2_1 §P2-B3; P2_4 §P2-F7; fishery-quest-spec F3</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>P2-B3, M2, P1-H3</t>
+          <t>P2-B1</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>new SanctuaryBuildingLifecycle.js; js/sanctuary/buildings/dryingRack.js (behaviour, with Seat U's createModel)</t>
+          <t>new SanctuaryQuests.js, quests/*.js, SanctuaryQuestMarkers.js, SanctuaryDialogue.js</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Plan, move, build, take down (full refund), rebuild, undo; reload resumes at every step</t>
+          <t>The 2-tree loop works from a fresh save; no wish expires with a penalty</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Mark (visible)</t>
+          <t>Partner + Mark (dialogue, names)</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -23826,7 +23826,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>P2-B2</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -23842,32 +23842,32 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Cooking fire, food cache, garden bed and play area models</t>
+          <t>Lifecycle plan → building → built → taken down; drying rack (fishery F4)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.2-3.5</t>
+          <t>P2_1 §P2-B2; fishery-quest-spec F4</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>P2-B3, M2, P1-H3</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/buildings/models/{cookingFire,foodCache,garden,playArea}.js (+ the crop meshes for Seat A)</t>
+          <t>new SanctuaryBuildingLifecycle.js; js/sanctuary/buildings/dryingRack.js (behaviour, with Seat U's createModel)</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Each &lt;= 1,500 tris and &lt;= 3 draw calls, with its slots and 4 stages</t>
+          <t>Plan, move, build, take down (full refund), rebuild, undo; reload resumes at every step</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Partner + Mark (play-area games especially)</t>
+          <t>Mark (visible)</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -23877,14 +23877,14 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>PLN-40</t>
+          <t>PLN-34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -23900,12 +23900,12 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Lighter home tipi for player-built homes (&lt;= 8,000 tris, plain cover)</t>
+          <t>Cooking fire, food cache, garden bed and play area models</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.6</t>
+          <t>P2_5 §3.2-3.5</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -23915,17 +23915,17 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Assets/Tipi.home/tipi_t1_home.glb + .mobile.glb; buildingTypes.js</t>
+          <t>js/sanctuary/buildings/models/{cookingFire,foodCache,garden,playArea}.js (+ the crop meshes for Seat A)</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Same silhouette, &lt;= 8,000 tris; the 3 starting tipis unchanged</t>
+          <t>Each &lt;= 1,500 tris and &lt;= 3 draw calls, with its slots and 4 stages</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>OD-24; Mark (visible) + partner (cover)</t>
+          <t>Partner + Mark (play-area games especially)</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -23942,7 +23942,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>P2-F4-6</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
@@ -23958,32 +23958,32 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Drying rack, food cache and cooking fire behaviour; one shared smoke system</t>
+          <t>Lighter home tipi for player-built homes (&lt;= 8,000 tris, plain cover)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F4, F5, F6</t>
+          <t>P2_5 §3.6</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>P2-F2, P2-B2, M4, UA-5</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/buildings/&lt;type&gt;.js (behaviour); new js/sanctuary/SanctuarySmoke.js (Seat U's sprites)</t>
+          <t>Assets/Tipi.home/tipi_t1_home.glb + .mobile.glb; buildingTypes.js</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>An empty cache still gives an evening meal; all smoke costs 1 draw call</t>
+          <t>Same silhouette, &lt;= 8,000 tris; the 3 starting tipis unchanged</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-24; Mark (visible) + partner (cover)</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -23993,14 +23993,14 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-40</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>P2-B5</t>
+          <t>P2-F4-6</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -24016,32 +24016,32 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>12-building cap; Tier-1 checklist → unlocks.tier2; tree regrowth (fishery F5-F6)</t>
+          <t>Drying rack, food cache and cooking fire behaviour; one shared smoke system</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>P2_1 §P2-B5; fishery-quest-spec F5-F6</t>
+          <t>P2_4 §P2-F4, F5, F6</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>P2-B2</t>
+          <t>P2-F2, P2-B2, M4, UA-5</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildings.js; SanctuarySave sections</t>
+          <t>js/sanctuary/buildings/&lt;type&gt;.js (behaviour); new js/sanctuary/SanctuarySmoke.js (Seat U's sprites)</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>13th building refused; the unlock survives a take-down; trees regrow after 10 play-minutes</t>
+          <t>An empty cache still gives an evening meal; all smoke costs 1 draw call</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>OD-04, OD-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -24051,14 +24051,14 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>PLN-34</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>P2-F3</t>
+          <t>P2-B5</t>
         </is>
       </c>
       <c r="B51" s="20" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -24074,32 +24074,32 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Garden: 10 hills, crops in their own rows, instanced plants, plot picking</t>
+          <t>12-building cap; Tier-1 checklist → unlocks.tier2; tree regrowth (fishery F5-F6)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F3</t>
+          <t>P2_1 §P2-B5; fishery-quest-spec F5-F6</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>P2-F2, M4</t>
+          <t>P2-B2</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryGarden.js</t>
+          <t>SanctuaryBuildings.js; SanctuarySave sections</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>&lt;= 8 draw calls; 10 taps harvest 10 hills on phone 3x</t>
+          <t>13th building refused; the unlock survives a take-down; trees regrow after 10 play-minutes</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>OD-16</t>
+          <t>OD-04, OD-06</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -24109,14 +24109,14 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>PLN-37</t>
+          <t>PLN-34</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>P2-F8</t>
+          <t>P2-F3</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
@@ -24132,32 +24132,32 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Story seasons and moons; seasonal events as data, off until approved</t>
+          <t>Garden: 10 hills, crops in their own rows, instanced plants, plot picking</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F8</t>
+          <t>P2_4 §P2-F3</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>P2-F1</t>
+          <t>P2-F2, M4</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/data/seasons.js; SanctuaryClock.js</t>
+          <t>new js/sanctuary/SanctuaryGarden.js</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Full cache + yes: winter feast, snow, spring; no: autumn stays</t>
+          <t>&lt;= 8 draw calls; 10 taps harvest 10 hills on phone 3x</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>OD-17, OD-19, OD-20; partner (moon names)</t>
+          <t>OD-16</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -24174,7 +24174,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>P2-F9</t>
+          <t>P2-F8</t>
         </is>
       </c>
       <c r="B53" s="20" t="n">
@@ -24190,32 +24190,32 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Hearts that never fall + found-things list</t>
+          <t>Story seasons and moons; seasonal events as data, off until approved</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F9</t>
+          <t>P2_4 §P2-F8</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>P2-F2</t>
+          <t>P2-F1</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryHearts.js</t>
+          <t>new js/sanctuary/data/seasons.js; SanctuaryClock.js</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>No heart count ever drops; milestones add life to the village</t>
+          <t>Full cache + yes: winter feast, snow, spring; no: autumn stays</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-17, OD-19, OD-20; partner (moon names)</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -24232,7 +24232,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>P2-F10</t>
+          <t>P2-F9</t>
         </is>
       </c>
       <c r="B54" s="20" t="n">
@@ -24248,32 +24248,32 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Save v3 food sections + v2 → v3 migration</t>
+          <t>Hearts that never fall + found-things list</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>P2_4 §P2-F10</t>
+          <t>P2_4 §P2-F9</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>P1-D0</t>
+          <t>P2-F2</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>Seat A modules (SanctuarySave.register)</t>
+          <t>new js/sanctuary/SanctuaryHearts.js</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>A v2 save loads with empty stores; reload resumes at every step</t>
+          <t>No heart count ever drops; milestones add life to the village</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>OD-21, OD-22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -24290,7 +24290,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>P2-K7-9</t>
+          <t>P2-F10</t>
         </is>
       </c>
       <c r="B55" s="20" t="n">
@@ -24298,7 +24298,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
@@ -24306,32 +24306,32 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Who comes; carrying logs; hammer-synced reveal; finishing moments</t>
+          <t>Save v3 food sections + v2 → v3 migration</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K7, K8, K9</t>
+          <t>P2_4 §P2-F10</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>P2-B2, P2-K5-6</t>
+          <t>P1-D0</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js (site.addWork hook agreed with Seat B)</t>
+          <t>Seat A modules (SanctuarySave.register)</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>4 visible stages; help-hammer finishes sooner; 8 s self-build fallback works</t>
+          <t>A v2 save loads with empty stores; reload resumes at every step</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-21, OD-22</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -24341,14 +24341,14 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>PLN-35</t>
+          <t>PLN-37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>P2-K12-13</t>
+          <t>P2-K7-9</t>
         </is>
       </c>
       <c r="B56" s="20" t="n">
@@ -24364,32 +24364,32 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Friendship hearts (no decay); families of 2-3 arrive (cap 20)</t>
+          <t>Who comes; carrying logs; hammer-synced reveal; finishing moments</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K12, K13</t>
+          <t>P2_2 §P2-K7, K8, K9</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>P2-K3-4</t>
+          <t>P2-B2, P2-K5-6</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js + data</t>
+          <t>SanctuaryVillagers.js (site.addWork hook agreed with Seat B)</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Hearts never drop; a family arrives after a tipi is built</t>
+          <t>4 visible stages; help-hammer finishes sooner; 8 s self-build fallback works</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Partner (names)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>P2-K11</t>
+          <t>P2-K12-13</t>
         </is>
       </c>
       <c r="B57" s="20" t="n">
@@ -24422,32 +24422,32 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Villager save section (logical state only)</t>
+          <t>Friendship hearts (no decay); families of 2-3 arrive (cap 20)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>P2_2 §P2-K11</t>
+          <t>P2_2 §P2-K12, K13</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>P1-D0</t>
+          <t>P2-K3-4</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js</t>
+          <t>SanctuaryVillagers.js + data</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Reload never loses, doubles or floats a villager</t>
+          <t>Hearts never drop; a family arrives after a tipi is built</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Partner (names)</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -24464,7 +24464,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>P2-K11</t>
         </is>
       </c>
       <c r="B58" s="20" t="n">
@@ -24472,7 +24472,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
@@ -24480,27 +24480,27 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Card thumbnails from the final models</t>
+          <t>Villager save section (logical state only)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §6</t>
+          <t>P2_2 §P2-K11</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>M2, M4, M5</t>
+          <t>P1-D0</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Assets/ui/cards/*.png</t>
+          <t>SanctuaryVillagers.js</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>128 px @2x, &lt;= 20 KB each, all under 250 KB</t>
+          <t>Reload never loses, doubles or floats a villager</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
@@ -24515,14 +24515,14 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>PLN-40</t>
+          <t>PLN-35</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="B59" s="20" t="n">
@@ -24538,32 +24538,32 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Build drawer shell, tabs, top bar, overflow menu</t>
+          <t>Card thumbnails from the final models</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U1, U5</t>
+          <t>P2_5 §6</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Phase 1, UA-2</t>
+          <t>M2, M4, M5</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryBuildDrawer.js</t>
+          <t>Assets/ui/cards/*.png</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Every old button has a home; FND-49 probe passes</t>
+          <t>128 px @2x, &lt;= 20 KB each, all under 250 KB</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>OD-13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -24573,14 +24573,14 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>PLN-36</t>
+          <t>PLN-40</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>P2-U4</t>
+          <t>P2-U1-5</t>
         </is>
       </c>
       <c r="B60" s="20" t="n">
@@ -24596,32 +24596,32 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Look and contrast (measured colours, gold borders, focus ring, high contrast)</t>
+          <t>The Build modal grows real tabs and cards; the More modal (all panel modals, DEC-35)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U4</t>
+          <t>P2_3 §P2-U1, U5; 00_UI_AND_ART_PLAN §9</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5</t>
+          <t>Phase 1, UA-8</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>css/sanctuary-ui.css; drawer</t>
+          <t>js/panel/sa-village-ui.js (no game-page DOM)</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Automated contrast check passes; screenshots normal and high contrast</t>
+          <t>Every old button has a home; the 11-point modal check passes; FND-49 probe passes</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Mark (visible)</t>
+          <t>OD-13</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -24638,7 +24638,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>P2-U2-3</t>
+          <t>P2-U4</t>
         </is>
       </c>
       <c r="B61" s="20" t="n">
@@ -24654,32 +24654,32 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Cards, info card, wish-basket chips</t>
+          <t>Look and contrast (measured colours, gold borders, focus ring, high contrast)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U2, U3; P2_4 §P2-F7</t>
+          <t>P2_3 §P2-U4</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5, P2-B3, M8, UA-5</t>
+          <t>P2-U1-5</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>drawer; Assets/ui/cards/*.png</t>
+          <t>css/sanctuary-ui.css; the panel modals</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>A screen reader reads each card's name, state and cost</t>
+          <t>Automated contrast check passes; screenshots normal and high contrast</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mark (visible)</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -24696,7 +24696,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>P2-U6-8</t>
+          <t>P2-U2-3</t>
         </is>
       </c>
       <c r="B62" s="20" t="n">
@@ -24712,27 +24712,27 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Announcer, voice labels, one-switch scan, reduced motion, little-helper mode</t>
+          <t>Cards, a building's card (panel modal), wish-basket chips</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U6, U7, U8</t>
+          <t>P2_3 §P2-U2, U3; P2_4 §P2-F7</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>P2-U1-5</t>
+          <t>P2-U1-5, P2-B3, M8, UA-5</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryAnnouncer.js; drawer</t>
+          <t>the Build modal; Assets/ui/cards/*.png</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>VoiceOver and TalkBack walkthroughs; Switch Control places a drying rack</t>
+          <t>A screen reader reads each card's name, state and cost</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
@@ -24754,7 +24754,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>P2-U9</t>
+          <t>P2-U6-8</t>
         </is>
       </c>
       <c r="B63" s="20" t="n">
@@ -24770,27 +24770,27 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Accessible building list replaces BuildingPanelUI</t>
+          <t>Announcer, voice labels, one-switch scan, reduced motion, little-helper mode</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U9</t>
+          <t>P2_3 §P2-U6, U7, U8</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>P1-D3</t>
+          <t>P2-U1-5</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>drawer (retire js/v2/BuildingPanelUI.js after parity)</t>
+          <t>the panel's one announcer (js/panel/sa-village-ui.js; the game sends VB_SAY); the modals</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>The list updates at once when a building is added or taken down</t>
+          <t>VoiceOver and TalkBack walkthroughs; Switch Control places a drying rack</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>P2-U10</t>
+          <t>P2-U9</t>
         </is>
       </c>
       <c r="B64" s="20" t="n">
@@ -24828,32 +24828,32 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Journal pages + grown-up save-code screen</t>
+          <t>My village (panel modal) replaces BuildingPanelUI's list</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>P2_3 §P2-U10</t>
+          <t>P2_3 §P2-U9</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>P2-F9, P1-D0</t>
+          <t>P1-D3</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>drawer</t>
+          <t>the My village modal (js/v2/BuildingPanelUI.js's DOM retires after parity)</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Pages fill as things are found; the save code round-trips</t>
+          <t>The list updates at once when a building is added or taken down</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>OD-22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
@@ -24870,7 +24870,7 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>UA-Q2</t>
+          <t>P2-U10</t>
         </is>
       </c>
       <c r="B65" s="20" t="n">
@@ -24886,32 +24886,32 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 visual QA, before R's phase test</t>
+          <t>Journal pages + grown-up save-code screen</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>00_UI_AND_ART_PLAN §7</t>
+          <t>P2_3 §P2-U10</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>all Phase 2 items</t>
+          <t>P2-F9, P1-D0</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
+          <t>the Journal and More modals</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
+          <t>Pages fill as things are found; the save code round-trips</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-22</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -24921,14 +24921,14 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>PLN-42</t>
+          <t>PLN-36</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>R-P2</t>
+          <t>UA-Q2</t>
         </is>
       </c>
       <c r="B66" s="20" t="n">
@@ -24936,7 +24936,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
@@ -24944,12 +24944,12 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Land Phase 2 in order; phase test; Mark plays it</t>
+          <t>Phase 2 visual QA, before R's phase test</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>prompts/REVIEWER_R.md</t>
+          <t>00_UI_AND_ART_PLAN §7</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -24959,17 +24959,17 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>tools/decision-engine/build_engine.py (rows only)</t>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>20 villagers and every Tier-1 building: phone 3x holds 60 fps</t>
+          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Mark plays it; partner signs off names, dialogue and models</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -24979,22 +24979,22 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>PLN-34, PLN-35, PLN-36, PLN-37, PLN-40, PLN-41</t>
+          <t>PLN-42</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>P3-L5-7</t>
-        </is>
-      </c>
-      <c r="B67" s="21" t="n">
-        <v>3</v>
+          <t>R-P2</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>R</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
@@ -25002,32 +25002,32 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>multiplier() drives slots; only the level is saved</t>
+          <t>Land Phase 2 in order; phase test; Mark plays it</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L5, L7</t>
+          <t>prompts/REVIEWER_R.md</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Phase 2</t>
+          <t>all Phase 2 items</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildings.js; building modules</t>
+          <t>tools/decision-engine/build_engine.py (rows only)</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>P1 save tests 1, 3 and 4 still pass</t>
+          <t>20 villagers and every Tier-1 building: phone 3x holds 60 fps</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>OD-02, OD-05</t>
+          <t>Mark plays it; partner signs off names, dialogue and models</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -25037,14 +25037,14 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-34, PLN-35, PLN-36, PLN-37, PLN-40, PLN-41</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6</t>
+          <t>P3-L5-7</t>
         </is>
       </c>
       <c r="B68" s="21" t="n">
@@ -25060,32 +25060,32 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Add a level (2, 2, 3, 3, 4, 4, 5, 5, 6 wood); full refund on take-down</t>
+          <t>multiplier() drives slots; only the level is saved</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L1, L6</t>
+          <t>P3_1 §P3-L5, L7</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>P3-L5-7</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildingLifecycle.js</t>
+          <t>SanctuaryBuildings.js; building modules</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Level 1 → 10 costs 34 wood; the refund includes every level</t>
+          <t>P1 save tests 1, 3 and 4 still pass</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OD-02, OD-05</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -25102,7 +25102,7 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>P3-L2</t>
+          <t>P3-L1-6</t>
         </is>
       </c>
       <c r="B69" s="21" t="n">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
@@ -25118,27 +25118,27 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Plain bead strip (two rows of five) + Add a level button</t>
+          <t>Add a level (2, 2, 3, 3, 4, 4, 5, 5, 6 wood); full refund on take-down</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L2</t>
+          <t>P3_1 §P3-L1, L6</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6</t>
+          <t>P3-L5-7</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>drawer</t>
+          <t>SanctuaryBuildingLifecycle.js</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Level 7 reads as five and two at a glance</t>
+          <t>Level 1 → 10 costs 34 wood; the refund includes every level</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
@@ -25160,7 +25160,7 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>P3-Y1-2</t>
+          <t>P3-L2</t>
         </is>
       </c>
       <c r="B70" s="21" t="n">
@@ -25176,32 +25176,32 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Checklist silhouettes; one invitation; Raise the big lodge button; skip control</t>
+          <t>Plain bead strip (two rows of five) + Add a level button</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y1, Y2</t>
+          <t>P3_1 §P3-L2</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>P2-B5</t>
+          <t>P3-L1-6</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>drawer; SanctuaryDialogue.js</t>
+          <t>the building's card (panel modal); a panel overlay at VB_SELECTED's screen point</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>One invitation per save; the button follows the wood count</t>
+          <t>Level 7 reads as five and two at a glance</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>OD-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -25211,14 +25211,14 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-38</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>P3-L3</t>
+          <t>P3-Y1-2</t>
         </is>
       </c>
       <c r="B71" s="21" t="n">
@@ -25234,32 +25234,32 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Level props: one InstancedMesh per prop kind, 9 per building (M6)</t>
+          <t>Checklist silhouettes; one invitation; Raise the big lodge button; skip control</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L3; P2_5 §3</t>
+          <t>P3_2 §P3-Y1, Y2</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6, M1</t>
+          <t>P2-B5</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryBuildingProps.js; js/sanctuary/buildings/models/props.js</t>
+          <t>her card (panel modal); SanctuaryDialogue.js</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>12 buildings at level 10 add &lt;= 9 draw calls</t>
+          <t>One invitation per save; the button follows the wood count</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Mark (visible)</t>
+          <t>OD-04</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -25269,14 +25269,14 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-39</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>UA-7</t>
+          <t>P3-L3</t>
         </is>
       </c>
       <c r="B72" s="21" t="n">
@@ -25292,32 +25292,32 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Celebration visuals: the lodge raising (P3-Y6) and the level glow (P3-L4)</t>
+          <t>Level props: one InstancedMesh per prop kind, 9 per building (M6)</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y6; P3_1 §P3-L4; 00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
+          <t>P3_1 §P3-L3; P2_5 §3</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>UA-5</t>
+          <t>P3-L1-6, M1</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>js/sanctuary/ (effects module, agreed with Seats B and D); Assets/village/ (effects atlas)</t>
+          <t>new js/sanctuary/SanctuaryBuildingProps.js; js/sanctuary/buildings/models/props.js</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>&lt;= 10 s, skippable, reduced-motion version</t>
+          <t>12 buildings at level 10 add &lt;= 9 draw calls</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Partner + advisors</t>
+          <t>Mark (visible)</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -25327,14 +25327,14 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>PLN-42, PLN-39</t>
+          <t>PLN-38</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>P3-L4</t>
+          <t>UA-7</t>
         </is>
       </c>
       <c r="B73" s="21" t="n">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
@@ -25350,32 +25350,32 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>One-second level celebration (+ reduced-motion version)</t>
+          <t>Celebration visuals: the lodge raising (P3-Y6) and the level glow (P3-L4)</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>P3_1 §P3-L4</t>
+          <t>P3_2 §P3-Y6; P3_1 §P3-L4; 00_UI_AND_ART_PLAN §5; prompts/MASTER_CODER_UI_ART.md</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>P3-L1-6, UA-7</t>
+          <t>UA-5</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildingLifecycle.js</t>
+          <t>js/sanctuary/ (effects module, agreed with Seats B and D); Assets/village/ (effects atlas)</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Video with and without reduced motion; no allocations</t>
+          <t>&lt;= 10 s, skippable, reduced-motion version</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Partner + advisors</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
@@ -25385,14 +25385,14 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>PLN-38</t>
+          <t>PLN-42, PLN-39</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>P3-L4</t>
         </is>
       </c>
       <c r="B74" s="21" t="n">
@@ -25400,7 +25400,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
@@ -25408,32 +25408,32 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Lodge model (&lt;= 40k tris, &lt;= 3 draw calls, plain sewn-hide cover)</t>
+          <t>One-second level celebration (+ reduced-motion version)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>P2_5 §3.7; P3_2 §P3-Y3</t>
+          <t>P3_1 §P3-L4</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>P3-L1-6, UA-7</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>Assets/lodge/*.glb</t>
+          <t>SanctuaryBuildingLifecycle.js</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Tris, draw calls and phone memory in the commit</t>
+          <t>Video with and without reduced motion; no allocations</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>OD-03, OD-25; partner + Mark</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -25443,14 +25443,14 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>PLN-39</t>
+          <t>PLN-38</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>P3-Y4-5</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="B75" s="21" t="n">
@@ -25458,7 +25458,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -25466,32 +25466,32 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>The swap (rim check, flat disk, shared GLB kept) + re-seat Yellow Butterfly</t>
+          <t>Lodge model (&lt;= 40k tris, &lt;= 3 draw calls, plain sewn-hide cover)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y4, Y5</t>
+          <t>P2_5 §3.7; P3_2 §P3-Y3</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>M7, P2-K2-10</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryTipis.js; ground hook; SanctuaryTipiNpcs.js</t>
+          <t>Assets/lodge/*.glb</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>No terrain through the platform on either layout; she sits at the new door after a reload</t>
+          <t>Tris, draw calls and phone memory in the commit</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Mark (pad and braziers inside the footprint)</t>
+          <t>OD-03, OD-25; partner + Mark</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
@@ -25508,7 +25508,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>P3-Y8-9</t>
+          <t>P3-Y4-5</t>
         </is>
       </c>
       <c r="B76" s="21" t="n">
@@ -25524,32 +25524,32 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Take down and move with the 8.0 m reservation; tiers 3-10 as data validation</t>
+          <t>The swap (rim check, flat disk, shared GLB kept) + re-seat Yellow Butterfly</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y8, Y9</t>
+          <t>P3_2 §P3-Y4, Y5</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>P3-Y4-5</t>
+          <t>M7, P2-K2-10</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryBuildingLifecycle.js; SanctuaryVillageRules.js; buildingTypes.js</t>
+          <t>SanctuaryTipis.js; ground hook; SanctuaryTipiNpcs.js</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Rebuild elsewhere and raise again: it always fits; a fake tier-3 row changes no save</t>
+          <t>No terrain through the platform on either layout; she sits at the new door after a reload</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>OD-15</t>
+          <t>Mark (pad and braziers inside the footprint)</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -25566,7 +25566,7 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>P3-Y6</t>
+          <t>P3-Y8-9</t>
         </is>
       </c>
       <c r="B77" s="21" t="n">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
@@ -25582,32 +25582,32 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Raising celebration (&lt;= 10 s, skippable, cuts under reduced motion)</t>
+          <t>Take down and move with the 8.0 m reservation; tiers 3-10 as data validation</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y6</t>
+          <t>P3_2 §P3-Y8, Y9</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>P3-Y4-5, P2-K7-9, UA-7</t>
+          <t>P3-Y4-5</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>new js/sanctuary/SanctuaryLodgeCelebration.js</t>
+          <t>SanctuaryBuildingLifecycle.js; SanctuaryVillageRules.js; buildingTypes.js</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Skipping at any moment gives the same end state; a reload mid-way gives a built lodge</t>
+          <t>Rebuild elsewhere and raise again: it always fits; a fake tier-3 row changes no save</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Partner + advisors (who raises it, any music)</t>
+          <t>OD-15</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -25624,7 +25624,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>P3-Y7</t>
+          <t>P3-Y6</t>
         </is>
       </c>
       <c r="B78" s="21" t="n">
@@ -25640,32 +25640,32 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Gathering place at the lodge's fire circle</t>
+          <t>Raising celebration (&lt;= 10 s, skippable, cuts under reduced motion)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>P3_2 §P3-Y7</t>
+          <t>P3_2 §P3-Y6</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>P3-Y6</t>
+          <t>P3-Y4-5, P2-K7-9, UA-7</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>SanctuaryVillagers.js</t>
+          <t>new js/sanctuary/SanctuaryLodgeCelebration.js</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Evening screenshot; still within 20 villagers</t>
+          <t>Skipping at any moment gives the same end state; a reload mid-way gives a built lodge</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Partner + advisors (who raises it, any music)</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -25682,7 +25682,7 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>UA-Q3</t>
+          <t>P3-Y7</t>
         </is>
       </c>
       <c r="B79" s="21" t="n">
@@ -25690,7 +25690,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
@@ -25698,27 +25698,27 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Phase 3 visual QA, before R's phase test</t>
+          <t>Gathering place at the lodge's fire circle</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>00_UI_AND_ART_PLAN §7</t>
+          <t>P3_2 §P3-Y7</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>all Phase 3 items</t>
+          <t>P3-Y6</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
+          <t>SanctuaryVillagers.js</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
+          <t>Evening screenshot; still within 20 villagers</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -25733,14 +25733,14 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>PLN-42</t>
+          <t>PLN-39</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>R-P3</t>
+          <t>UA-Q3</t>
         </is>
       </c>
       <c r="B80" s="21" t="n">
@@ -25748,7 +25748,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
@@ -25756,49 +25756,107 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
+          <t>Phase 3 visual QA, before R's phase test</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>00_UI_AND_ART_PLAN §7</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>all Phase 3 items</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>~/Downloads/SacredAdventures-handoff-2026-10-22/village-phases/review/</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Screenshot set (390x844 @3x, 360x740, 1280x800; normal, high contrast, reduced motion) + fps, draw calls, triangles</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>PLN-42</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>R-P3</t>
+        </is>
+      </c>
+      <c r="B81" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
           <t>Land Phase 3 in order; phase test; Mark plays it</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>prompts/REVIEWER_R.md</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>all Phase 3 items</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>tools/decision-engine/build_engine.py (rows only)</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>The lodge and every building at level 10: phone 3x holds 60 fps</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>Mark plays it</t>
         </is>
       </c>
-      <c r="K80" s="5" t="inlineStr">
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>PLN-38, PLN-39, PLN-41</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L80"/>
+  <autoFilter ref="A4:L81"/>
   <dataValidations count="1">
-    <dataValidation sqref="K5:K80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="K5:K81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not started,In progress,Blocked,Awaiting approval,Done (code) — verify in browser,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -25859,7 +25917,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>a88d9b2</t>
+          <t>190e626</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -26214,7 +26272,7 @@
         </is>
       </c>
       <c r="B27" s="11">
-        <f>COUNTIF('64_Next_Plan'!$K$5:$K$80,"Done*")&amp;" of "&amp;COUNTA('64_Next_Plan'!$A$5:$A$80)</f>
+        <f>COUNTIF('64_Next_Plan'!$K$5:$K$81,"Done*")&amp;" of "&amp;COUNTA('64_Next_Plan'!$A$5:$A$81)</f>
         <v/>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -26230,7 +26288,7 @@
         </is>
       </c>
       <c r="B28" s="11">
-        <f>COUNTIF('66_Owner_Decisions'!$D$5:$D$29,"Answered*")&amp;" of "&amp;COUNTA('66_Owner_Decisions'!$A$5:$A$29)</f>
+        <f>COUNTIF('66_Owner_Decisions'!$D$5:$D$30,"Answered*")&amp;" of "&amp;COUNTA('66_Owner_Decisions'!$A$5:$A$30)</f>
         <v/>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -26546,7 +26604,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Coder pack W3-W6, select, tray, ghost, undo, next spot, zoom (wired to Seat U's skin); later, input plumbing on request (ground relay, keys, switch)</t>
+          <t>Coder pack W3-W6, select, the tray's behaviour, ghost, undo, next spot, zoom: the game side of the builder bridge (VB_* messages) to Seat U's panel; later, input plumbing on request (ground relay, keys, switch)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -26630,7 +26688,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Everything the child sees: design tokens and components, icons and pictures, the village atlas and every model, the Build drawer, journal and Phase 3 UI; visual QA before each phase test</t>
+          <t>Everything the child sees: design tokens and components, icons and pictures, the village atlas and every model, every building panel as a panel HTML modal (DEC-35), the Village View bar, dock and tray, the journal and Phase 3 UI; visual QA before each phase test</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -26666,7 +26724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -27056,7 +27114,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>A fixed tray at the bottom of the screen</t>
+          <t>A fixed tray at the bottom of the screen (panel HTML, DEC-35)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -27523,8 +27581,40 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>OD-26</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>The placing tray under DEC-35: a modal, or panel HTML that isn't modal?</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Panel HTML that isn't modal (a labelled button group), so the child can still tap the village to pick a spot; every building panel is a modal</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Default in use; Mark to confirm</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>P1-T1, UA-8</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>DEC-35; claude/village-phases/00_UI_AND_ART_PLAN.md §9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F29"/>
+  <autoFilter ref="A4:F30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28846,7 +28936,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Activation order in index.html · evidence re-located at build · commit a88d9b2</t>
+          <t>Activation order in index.html · evidence re-located at build · commit 190e626</t>
         </is>
       </c>
     </row>
